--- a/artfynd/A 36371-2025 artfynd.xlsx
+++ b/artfynd/A 36371-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1609,6 +1609,1185 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>127173049</v>
+      </c>
+      <c r="B10" t="n">
+        <v>8447</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>426811</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6784566</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>127171567</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79014</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Finnsmyrtjärnen, Finnsmyrtjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>426720</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6784080</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>127172799</v>
+      </c>
+      <c r="B12" t="n">
+        <v>56849</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>426603</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6784539</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>127170657</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99456</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>222467</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Gräsull</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Eriophorum latifolium</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Hoppe</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>426723</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6784193</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>127170594</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79014</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>426782</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6784215</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>127172169</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57578</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100001</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Duvhök</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Astur gentilis</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>426655</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6784424</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Kretsande strax ovan trädtoppar.</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>127170509</v>
+      </c>
+      <c r="B16" t="n">
+        <v>78772</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>426799</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6784266</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>127171900</v>
+      </c>
+      <c r="B17" t="n">
+        <v>78772</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>426568</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6784199</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>127170727</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79014</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>426699</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6784140</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>127170479</v>
+      </c>
+      <c r="B19" t="n">
+        <v>8447</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>426799</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6784267</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>127171905</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79632</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>426568</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6784199</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>127172960</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79014</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>426844</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6784752</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 36371-2025 artfynd.xlsx
+++ b/artfynd/A 36371-2025 artfynd.xlsx
@@ -1614,7 +1614,7 @@
         <v>127173049</v>
       </c>
       <c r="B10" t="n">
-        <v>8447</v>
+        <v>8450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
         <v>127171567</v>
       </c>
       <c r="B11" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>127172799</v>
       </c>
       <c r="B12" t="n">
-        <v>56849</v>
+        <v>56853</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         <v>127170657</v>
       </c>
       <c r="B13" t="n">
-        <v>99456</v>
+        <v>99460</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>127170594</v>
       </c>
       <c r="B14" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
         <v>127172169</v>
       </c>
       <c r="B15" t="n">
-        <v>57578</v>
+        <v>57582</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2211,7 +2211,7 @@
         <v>127170509</v>
       </c>
       <c r="B16" t="n">
-        <v>78772</v>
+        <v>78776</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2308,7 +2308,7 @@
         <v>127171900</v>
       </c>
       <c r="B17" t="n">
-        <v>78772</v>
+        <v>78776</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
         <v>127170727</v>
       </c>
       <c r="B18" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>127170479</v>
       </c>
       <c r="B19" t="n">
-        <v>8447</v>
+        <v>8450</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>127171905</v>
       </c>
       <c r="B20" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2696,7 +2696,7 @@
         <v>127172960</v>
       </c>
       <c r="B21" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 36371-2025 artfynd.xlsx
+++ b/artfynd/A 36371-2025 artfynd.xlsx
@@ -1708,45 +1708,50 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127171567</v>
+        <v>127172799</v>
       </c>
       <c r="B11" t="n">
-        <v>79018</v>
+        <v>56853</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Finnsmyrtjärnen, Finnsmyrtjärnen, Dlr</t>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>426720</v>
+        <v>426603</v>
       </c>
       <c r="R11" t="n">
-        <v>6784080</v>
+        <v>6784539</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1805,50 +1810,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127172799</v>
+        <v>127171567</v>
       </c>
       <c r="B12" t="n">
-        <v>56853</v>
+        <v>79018</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+          <t>Finnsmyrtjärnen, Finnsmyrtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>426603</v>
+        <v>426720</v>
       </c>
       <c r="R12" t="n">
-        <v>6784539</v>
+        <v>6784080</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1910,7 +1910,7 @@
         <v>127170657</v>
       </c>
       <c r="B13" t="n">
-        <v>99460</v>
+        <v>99461</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 36371-2025 artfynd.xlsx
+++ b/artfynd/A 36371-2025 artfynd.xlsx
@@ -1708,50 +1708,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127172799</v>
+        <v>127171567</v>
       </c>
       <c r="B11" t="n">
-        <v>56853</v>
+        <v>79020</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+          <t>Finnsmyrtjärnen, Finnsmyrtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>426603</v>
+        <v>426720</v>
       </c>
       <c r="R11" t="n">
-        <v>6784539</v>
+        <v>6784080</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1810,45 +1805,50 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127171567</v>
+        <v>127172799</v>
       </c>
       <c r="B12" t="n">
-        <v>79018</v>
+        <v>56855</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Finnsmyrtjärnen, Finnsmyrtjärnen, Dlr</t>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>426720</v>
+        <v>426603</v>
       </c>
       <c r="R12" t="n">
-        <v>6784080</v>
+        <v>6784539</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1910,7 +1910,7 @@
         <v>127170657</v>
       </c>
       <c r="B13" t="n">
-        <v>99461</v>
+        <v>99463</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>127170594</v>
       </c>
       <c r="B14" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
         <v>127172169</v>
       </c>
       <c r="B15" t="n">
-        <v>57582</v>
+        <v>57584</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2211,7 +2211,7 @@
         <v>127170509</v>
       </c>
       <c r="B16" t="n">
-        <v>78776</v>
+        <v>78778</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2308,7 +2308,7 @@
         <v>127171900</v>
       </c>
       <c r="B17" t="n">
-        <v>78776</v>
+        <v>78778</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
         <v>127170727</v>
       </c>
       <c r="B18" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>127171905</v>
       </c>
       <c r="B20" t="n">
-        <v>79636</v>
+        <v>79638</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2696,7 +2696,7 @@
         <v>127172960</v>
       </c>
       <c r="B21" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 36371-2025 artfynd.xlsx
+++ b/artfynd/A 36371-2025 artfynd.xlsx
@@ -1910,7 +1910,7 @@
         <v>127170657</v>
       </c>
       <c r="B13" t="n">
-        <v>99463</v>
+        <v>99469</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 36371-2025 artfynd.xlsx
+++ b/artfynd/A 36371-2025 artfynd.xlsx
@@ -1708,45 +1708,50 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127171567</v>
+        <v>127172799</v>
       </c>
       <c r="B11" t="n">
-        <v>79020</v>
+        <v>56858</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Finnsmyrtjärnen, Finnsmyrtjärnen, Dlr</t>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>426720</v>
+        <v>426603</v>
       </c>
       <c r="R11" t="n">
-        <v>6784080</v>
+        <v>6784539</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1805,50 +1810,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127172799</v>
+        <v>127171567</v>
       </c>
       <c r="B12" t="n">
-        <v>56855</v>
+        <v>79023</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+          <t>Finnsmyrtjärnen, Finnsmyrtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>426603</v>
+        <v>426720</v>
       </c>
       <c r="R12" t="n">
-        <v>6784539</v>
+        <v>6784080</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1910,7 +1910,7 @@
         <v>127170657</v>
       </c>
       <c r="B13" t="n">
-        <v>99469</v>
+        <v>99472</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>127170594</v>
       </c>
       <c r="B14" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
         <v>127172169</v>
       </c>
       <c r="B15" t="n">
-        <v>57584</v>
+        <v>57587</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2208,10 +2208,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127170509</v>
+        <v>127171900</v>
       </c>
       <c r="B16" t="n">
-        <v>78778</v>
+        <v>78781</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2239,14 +2239,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>426799</v>
+        <v>426568</v>
       </c>
       <c r="R16" t="n">
-        <v>6784266</v>
+        <v>6784199</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2305,10 +2305,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127171900</v>
+        <v>127170509</v>
       </c>
       <c r="B17" t="n">
-        <v>78778</v>
+        <v>78781</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2336,14 +2336,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>426568</v>
+        <v>426799</v>
       </c>
       <c r="R17" t="n">
-        <v>6784199</v>
+        <v>6784266</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2405,7 +2405,7 @@
         <v>127170727</v>
       </c>
       <c r="B18" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>127171905</v>
       </c>
       <c r="B20" t="n">
-        <v>79638</v>
+        <v>79641</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2696,7 +2696,7 @@
         <v>127172960</v>
       </c>
       <c r="B21" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 36371-2025 artfynd.xlsx
+++ b/artfynd/A 36371-2025 artfynd.xlsx
@@ -1711,7 +1711,7 @@
         <v>127172799</v>
       </c>
       <c r="B11" t="n">
-        <v>56858</v>
+        <v>56864</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>127171567</v>
       </c>
       <c r="B12" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         <v>127170657</v>
       </c>
       <c r="B13" t="n">
-        <v>99472</v>
+        <v>99480</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>127170594</v>
       </c>
       <c r="B14" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
         <v>127172169</v>
       </c>
       <c r="B15" t="n">
-        <v>57587</v>
+        <v>57593</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2208,10 +2208,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127171900</v>
+        <v>127170509</v>
       </c>
       <c r="B16" t="n">
-        <v>78781</v>
+        <v>78787</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2239,14 +2239,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>426568</v>
+        <v>426799</v>
       </c>
       <c r="R16" t="n">
-        <v>6784199</v>
+        <v>6784266</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2305,10 +2305,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127170509</v>
+        <v>127171900</v>
       </c>
       <c r="B17" t="n">
-        <v>78781</v>
+        <v>78787</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2336,14 +2336,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>426799</v>
+        <v>426568</v>
       </c>
       <c r="R17" t="n">
-        <v>6784266</v>
+        <v>6784199</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2405,7 +2405,7 @@
         <v>127170727</v>
       </c>
       <c r="B18" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>127171905</v>
       </c>
       <c r="B20" t="n">
-        <v>79641</v>
+        <v>79647</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2696,7 +2696,7 @@
         <v>127172960</v>
       </c>
       <c r="B21" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 36371-2025 artfynd.xlsx
+++ b/artfynd/A 36371-2025 artfynd.xlsx
@@ -1910,7 +1910,7 @@
         <v>127170657</v>
       </c>
       <c r="B13" t="n">
-        <v>99480</v>
+        <v>99481</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 36371-2025 artfynd.xlsx
+++ b/artfynd/A 36371-2025 artfynd.xlsx
@@ -1708,50 +1708,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127172799</v>
+        <v>127171567</v>
       </c>
       <c r="B11" t="n">
-        <v>56864</v>
+        <v>79029</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+          <t>Finnsmyrtjärnen, Finnsmyrtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>426603</v>
+        <v>426720</v>
       </c>
       <c r="R11" t="n">
-        <v>6784539</v>
+        <v>6784080</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1810,45 +1805,50 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127171567</v>
+        <v>127172799</v>
       </c>
       <c r="B12" t="n">
-        <v>79029</v>
+        <v>56864</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Finnsmyrtjärnen, Finnsmyrtjärnen, Dlr</t>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>426720</v>
+        <v>426603</v>
       </c>
       <c r="R12" t="n">
-        <v>6784080</v>
+        <v>6784539</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 36371-2025 artfynd.xlsx
+++ b/artfynd/A 36371-2025 artfynd.xlsx
@@ -1910,7 +1910,7 @@
         <v>127170657</v>
       </c>
       <c r="B13" t="n">
-        <v>99481</v>
+        <v>99482</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 36371-2025 artfynd.xlsx
+++ b/artfynd/A 36371-2025 artfynd.xlsx
@@ -1910,7 +1910,7 @@
         <v>127170657</v>
       </c>
       <c r="B13" t="n">
-        <v>99482</v>
+        <v>99483</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127170509</v>
+        <v>127171900</v>
       </c>
       <c r="B16" t="n">
         <v>78787</v>
@@ -2239,14 +2239,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>426799</v>
+        <v>426568</v>
       </c>
       <c r="R16" t="n">
-        <v>6784266</v>
+        <v>6784199</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2305,7 +2305,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127171900</v>
+        <v>127170509</v>
       </c>
       <c r="B17" t="n">
         <v>78787</v>
@@ -2336,14 +2336,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>426568</v>
+        <v>426799</v>
       </c>
       <c r="R17" t="n">
-        <v>6784199</v>
+        <v>6784266</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 36371-2025 artfynd.xlsx
+++ b/artfynd/A 36371-2025 artfynd.xlsx
@@ -2208,7 +2208,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127171900</v>
+        <v>127170509</v>
       </c>
       <c r="B16" t="n">
         <v>78787</v>
@@ -2239,14 +2239,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>426568</v>
+        <v>426799</v>
       </c>
       <c r="R16" t="n">
-        <v>6784199</v>
+        <v>6784266</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2305,7 +2305,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127170509</v>
+        <v>127171900</v>
       </c>
       <c r="B17" t="n">
         <v>78787</v>
@@ -2336,14 +2336,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>426799</v>
+        <v>426568</v>
       </c>
       <c r="R17" t="n">
-        <v>6784266</v>
+        <v>6784199</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 36371-2025 artfynd.xlsx
+++ b/artfynd/A 36371-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2693,10 +2693,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127172960</v>
+        <v>128418402</v>
       </c>
       <c r="B21" t="n">
-        <v>79029</v>
+        <v>78790</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2704,34 +2704,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>426844</v>
+        <v>426596</v>
       </c>
       <c r="R21" t="n">
-        <v>6784752</v>
+        <v>6784364</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2758,12 +2758,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2778,15 +2788,9335 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>128415015</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>426548</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6784175</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>128414172</v>
+      </c>
+      <c r="B23" t="n">
+        <v>78790</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>426541</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6784302</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>16:44</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>16:44</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>128414481</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79650</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>426524</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6784260</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>16:51</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>16:51</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>128411184</v>
+      </c>
+      <c r="B25" t="n">
+        <v>78791</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>426819</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6784515</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>128415595</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>426618</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6784050</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>17:13</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>17:13</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>128416106</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>426746</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6784096</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50 meter.</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>128414155</v>
+      </c>
+      <c r="B28" t="n">
+        <v>78791</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>426540</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6784305</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>16:44</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>16:44</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>128414801</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>426524</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6784260</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>16:54</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>16:54</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>128417228</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>426801</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6784284</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>18:12</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>18:12</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>128418215</v>
+      </c>
+      <c r="B31" t="n">
+        <v>78791</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>426655</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6784360</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>18:41</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>18:41</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>128413169</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>426555</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6784393</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>16:11</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>16:11</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>128413945</v>
+      </c>
+      <c r="B33" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>426498</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6784322</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>16:34</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>16:34</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>128414306</v>
+      </c>
+      <c r="B34" t="n">
+        <v>57670</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>426519</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6784286</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>16:47</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>16:47</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>128404649</v>
+      </c>
+      <c r="B35" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>426792</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6784434</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>10:46</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>10:46</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>128416349</v>
+      </c>
+      <c r="B36" t="n">
+        <v>78790</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>426792</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6784152</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>17:44</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>17:44</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>128412524</v>
+      </c>
+      <c r="B37" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>426466</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6784510</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>128404418</v>
+      </c>
+      <c r="B38" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>426715</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6784397</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>128414383</v>
+      </c>
+      <c r="B39" t="n">
+        <v>78791</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>426509</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6784270</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>16:49</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>16:49</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>128418198</v>
+      </c>
+      <c r="B40" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>426656</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6784360</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>128413197</v>
+      </c>
+      <c r="B41" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>426532</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6784390</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>128417709</v>
+      </c>
+      <c r="B42" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>426717</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6784350</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>128418704</v>
+      </c>
+      <c r="B43" t="n">
+        <v>78790</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>426573</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6784360</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>128418719</v>
+      </c>
+      <c r="B44" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>426571</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6784357</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>19:01</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>19:01</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>128415503</v>
+      </c>
+      <c r="B45" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>426605</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6784090</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>128413145</v>
+      </c>
+      <c r="B46" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>426534</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6784406</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>128416206</v>
+      </c>
+      <c r="B47" t="n">
+        <v>78790</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>426760</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6784153</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>17:38</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>17:38</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>128412596</v>
+      </c>
+      <c r="B48" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>426468</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6784486</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>128416262</v>
+      </c>
+      <c r="B49" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>426784</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6784159</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>128415767</v>
+      </c>
+      <c r="B50" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>426618</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6784050</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>128415549</v>
+      </c>
+      <c r="B51" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>426615</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6784068</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>17:12</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>17:12</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>128414874</v>
+      </c>
+      <c r="B52" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>426535</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6784210</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>16:57</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>16:57</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>128417096</v>
+      </c>
+      <c r="B53" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>426812</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6784257</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>18:09</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>18:09</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>128418647</v>
+      </c>
+      <c r="B54" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>426573</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6784376</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>18:59</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>18:59</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>128415267</v>
+      </c>
+      <c r="B55" t="n">
+        <v>78791</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>426604</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6784093</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>17:06</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>17:06</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>128413992</v>
+      </c>
+      <c r="B56" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>426519</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6784308</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>16:37</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>16:37</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>128418258</v>
+      </c>
+      <c r="B57" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>426632</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6784364</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>18:43</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>18:43</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>128415393</v>
+      </c>
+      <c r="B58" t="n">
+        <v>79650</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>426601</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6784100</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>128417675</v>
+      </c>
+      <c r="B59" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>426764</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6784308</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>128404480</v>
+      </c>
+      <c r="B60" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>426773</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6784434</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>128416385</v>
+      </c>
+      <c r="B61" t="n">
+        <v>79650</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>426796</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6784156</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>17:44</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>17:44</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>128414843</v>
+      </c>
+      <c r="B62" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>426521</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6784206</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>128414095</v>
+      </c>
+      <c r="B63" t="n">
+        <v>78791</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>426556</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6784312</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>16:41</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>16:41</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>128412109</v>
+      </c>
+      <c r="B64" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>426646</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6784678</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>128416277</v>
+      </c>
+      <c r="B65" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>426797</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6784155</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>17:41</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>17:41</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>128415117</v>
+      </c>
+      <c r="B66" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>426554</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6784161</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>17:02</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>17:02</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>128413333</v>
+      </c>
+      <c r="B67" t="n">
+        <v>78790</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>426459</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6784412</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>128413310</v>
+      </c>
+      <c r="B68" t="n">
+        <v>57670</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>426477</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6784397</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>128417436</v>
+      </c>
+      <c r="B69" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>426801</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6784284</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>128418292</v>
+      </c>
+      <c r="B70" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>426624</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6784361</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav på tallarna på en radie av 50 meter.</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>128417205</v>
+      </c>
+      <c r="B71" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>426813</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6784276</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>18:11</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>18:11</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>128415978</v>
+      </c>
+      <c r="B72" t="n">
+        <v>78790</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>426770</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6784113</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>128413213</v>
+      </c>
+      <c r="B73" t="n">
+        <v>78791</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>426524</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6784388</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>128414247</v>
+      </c>
+      <c r="B74" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>426535</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6784292</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>16:46</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>16:46</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>127172960</v>
+      </c>
+      <c r="B75" t="n">
+        <v>79029</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>426844</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6784752</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
           <t>Niklas Rehn</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
+      <c r="AX75" t="inlineStr">
         <is>
           <t>Niklas Rehn</t>
         </is>
       </c>
-      <c r="AY21" t="inlineStr"/>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>128410669</v>
+      </c>
+      <c r="B76" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>426922</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6784529</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>128409845</v>
+      </c>
+      <c r="B77" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>427064</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6784664</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>128406731</v>
+      </c>
+      <c r="B78" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>427073</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6784548</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>128408778</v>
+      </c>
+      <c r="B79" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>427123</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6784697</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>128408858</v>
+      </c>
+      <c r="B80" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>427123</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6784697</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>128416919</v>
+      </c>
+      <c r="B81" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>426842</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6784214</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>18:01</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>18:01</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>128410625</v>
+      </c>
+      <c r="B82" t="n">
+        <v>57670</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>426917</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6784579</v>
+      </c>
+      <c r="S82" t="n">
+        <v>15</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>128409945</v>
+      </c>
+      <c r="B83" t="n">
+        <v>78791</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>427084</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6784718</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>128404878</v>
+      </c>
+      <c r="B84" t="n">
+        <v>57670</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>426879</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6784490</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>128407168</v>
+      </c>
+      <c r="B85" t="n">
+        <v>78791</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>427096</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6784536</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>128416596</v>
+      </c>
+      <c r="B86" t="n">
+        <v>79650</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>426860</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6784152</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>128406999</v>
+      </c>
+      <c r="B87" t="n">
+        <v>78791</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>427083</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6784551</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>128416502</v>
+      </c>
+      <c r="B88" t="n">
+        <v>78791</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>426841</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6784169</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>17:49</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>17:49</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>128416791</v>
+      </c>
+      <c r="B89" t="n">
+        <v>78791</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>426835</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6784196</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>18:01</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>18:01</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>128417147</v>
+      </c>
+      <c r="B90" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>426829</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6784266</v>
+      </c>
+      <c r="S90" t="n">
+        <v>10</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>128423249</v>
+      </c>
+      <c r="B91" t="n">
+        <v>57670</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Fisklöstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>427097</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6784657</v>
+      </c>
+      <c r="S91" t="n">
+        <v>20</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>128417068</v>
+      </c>
+      <c r="B92" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>426830</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6784251</v>
+      </c>
+      <c r="S92" t="n">
+        <v>10</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>18:08</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>18:08</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>128406985</v>
+      </c>
+      <c r="B93" t="n">
+        <v>78790</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>427087</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6784548</v>
+      </c>
+      <c r="S93" t="n">
+        <v>10</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>128404859</v>
+      </c>
+      <c r="B94" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>426869</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6784461</v>
+      </c>
+      <c r="S94" t="n">
+        <v>10</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>128410027</v>
+      </c>
+      <c r="B95" t="n">
+        <v>91378</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>427093</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6784727</v>
+      </c>
+      <c r="S95" t="n">
+        <v>10</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF95" t="inlineStr"/>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>128410598</v>
+      </c>
+      <c r="B96" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>426922</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6784576</v>
+      </c>
+      <c r="S96" t="n">
+        <v>10</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>128410456</v>
+      </c>
+      <c r="B97" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>426882</v>
+      </c>
+      <c r="R97" t="n">
+        <v>6784648</v>
+      </c>
+      <c r="S97" t="n">
+        <v>10</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>128410868</v>
+      </c>
+      <c r="B98" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>426916</v>
+      </c>
+      <c r="R98" t="n">
+        <v>6784534</v>
+      </c>
+      <c r="S98" t="n">
+        <v>10</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>128405638</v>
+      </c>
+      <c r="B99" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>427026</v>
+      </c>
+      <c r="R99" t="n">
+        <v>6784560</v>
+      </c>
+      <c r="S99" t="n">
+        <v>10</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>128410908</v>
+      </c>
+      <c r="B100" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>426908</v>
+      </c>
+      <c r="R100" t="n">
+        <v>6784511</v>
+      </c>
+      <c r="S100" t="n">
+        <v>10</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>128411027</v>
+      </c>
+      <c r="B101" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>426858</v>
+      </c>
+      <c r="R101" t="n">
+        <v>6784514</v>
+      </c>
+      <c r="S101" t="n">
+        <v>10</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>128416713</v>
+      </c>
+      <c r="B102" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>426849</v>
+      </c>
+      <c r="R102" t="n">
+        <v>6784145</v>
+      </c>
+      <c r="S102" t="n">
+        <v>10</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>17:58</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>17:58</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>128408932</v>
+      </c>
+      <c r="B103" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>427081</v>
+      </c>
+      <c r="R103" t="n">
+        <v>6784657</v>
+      </c>
+      <c r="S103" t="n">
+        <v>10</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>128407898</v>
+      </c>
+      <c r="B104" t="n">
+        <v>78790</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>427062</v>
+      </c>
+      <c r="R104" t="n">
+        <v>6784591</v>
+      </c>
+      <c r="S104" t="n">
+        <v>10</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>128409925</v>
+      </c>
+      <c r="B105" t="n">
+        <v>79621</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>427082</v>
+      </c>
+      <c r="R105" t="n">
+        <v>6784715</v>
+      </c>
+      <c r="S105" t="n">
+        <v>10</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>128407848</v>
+      </c>
+      <c r="B106" t="n">
+        <v>78791</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>427064</v>
+      </c>
+      <c r="R106" t="n">
+        <v>6784585</v>
+      </c>
+      <c r="S106" t="n">
+        <v>10</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>128416606</v>
+      </c>
+      <c r="B107" t="n">
+        <v>78790</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>426859</v>
+      </c>
+      <c r="R107" t="n">
+        <v>6784153</v>
+      </c>
+      <c r="S107" t="n">
+        <v>10</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 36371-2025 artfynd.xlsx
+++ b/artfynd/A 36371-2025 artfynd.xlsx
@@ -2693,10 +2693,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128418402</v>
+        <v>128415595</v>
       </c>
       <c r="B21" t="n">
-        <v>78790</v>
+        <v>79032</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2704,21 +2704,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2728,10 +2728,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>426596</v>
+        <v>426618</v>
       </c>
       <c r="R21" t="n">
-        <v>6784364</v>
+        <v>6784050</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2763,7 +2763,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2773,7 +2773,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3014,10 +3014,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128414481</v>
+        <v>128418402</v>
       </c>
       <c r="B24" t="n">
-        <v>79650</v>
+        <v>78790</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3025,21 +3025,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3049,10 +3049,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>426524</v>
+        <v>426596</v>
       </c>
       <c r="R24" t="n">
-        <v>6784260</v>
+        <v>6784364</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3121,10 +3121,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128411184</v>
+        <v>128414481</v>
       </c>
       <c r="B25" t="n">
-        <v>78791</v>
+        <v>79650</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3132,34 +3132,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>426819</v>
+        <v>426524</v>
       </c>
       <c r="R25" t="n">
-        <v>6784515</v>
+        <v>6784260</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3191,7 +3191,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3201,7 +3201,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3228,10 +3228,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128415595</v>
+        <v>128411184</v>
       </c>
       <c r="B26" t="n">
-        <v>79032</v>
+        <v>78791</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3239,34 +3239,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>426618</v>
+        <v>426819</v>
       </c>
       <c r="R26" t="n">
-        <v>6784050</v>
+        <v>6784515</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3298,7 +3298,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3308,7 +3308,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3335,7 +3335,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128416106</v>
+        <v>128414801</v>
       </c>
       <c r="B27" t="n">
         <v>79032</v>
@@ -3366,14 +3366,14 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>426746</v>
+        <v>426524</v>
       </c>
       <c r="R27" t="n">
-        <v>6784096</v>
+        <v>6784260</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3405,7 +3405,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3415,12 +3415,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:35</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50 meter.</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3447,10 +3442,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128414155</v>
+        <v>128417228</v>
       </c>
       <c r="B28" t="n">
-        <v>78791</v>
+        <v>79032</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3458,34 +3453,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>426540</v>
+        <v>426801</v>
       </c>
       <c r="R28" t="n">
-        <v>6784305</v>
+        <v>6784284</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3517,7 +3512,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3527,7 +3522,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3554,7 +3549,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128414801</v>
+        <v>128416106</v>
       </c>
       <c r="B29" t="n">
         <v>79032</v>
@@ -3585,14 +3580,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>426524</v>
+        <v>426746</v>
       </c>
       <c r="R29" t="n">
-        <v>6784260</v>
+        <v>6784096</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3624,7 +3619,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3634,7 +3629,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50 meter.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3661,10 +3661,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128417228</v>
+        <v>128414155</v>
       </c>
       <c r="B30" t="n">
-        <v>79032</v>
+        <v>78791</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3672,34 +3672,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>426801</v>
+        <v>426540</v>
       </c>
       <c r="R30" t="n">
-        <v>6784284</v>
+        <v>6784305</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3731,7 +3731,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3768,10 +3768,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128418215</v>
+        <v>128414306</v>
       </c>
       <c r="B31" t="n">
-        <v>78791</v>
+        <v>57670</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3779,34 +3779,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>426655</v>
+        <v>426519</v>
       </c>
       <c r="R31" t="n">
-        <v>6784360</v>
+        <v>6784286</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3838,7 +3843,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3848,7 +3853,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4094,10 +4099,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128414306</v>
+        <v>128418215</v>
       </c>
       <c r="B34" t="n">
-        <v>57670</v>
+        <v>78791</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4105,39 +4110,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>426519</v>
+        <v>426655</v>
       </c>
       <c r="R34" t="n">
-        <v>6784286</v>
+        <v>6784360</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4206,10 +4206,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128404649</v>
+        <v>128416349</v>
       </c>
       <c r="B35" t="n">
-        <v>79032</v>
+        <v>78790</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4217,21 +4217,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4244,7 +4244,7 @@
         <v>426792</v>
       </c>
       <c r="R35" t="n">
-        <v>6784434</v>
+        <v>6784152</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4286,7 +4286,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4313,10 +4313,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128416349</v>
+        <v>128404649</v>
       </c>
       <c r="B36" t="n">
-        <v>78790</v>
+        <v>79032</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4324,21 +4324,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4351,7 +4351,7 @@
         <v>426792</v>
       </c>
       <c r="R36" t="n">
-        <v>6784152</v>
+        <v>6784434</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4383,7 +4383,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4393,7 +4393,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4746,10 +4746,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128418198</v>
+        <v>128418704</v>
       </c>
       <c r="B40" t="n">
-        <v>79032</v>
+        <v>78790</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4757,21 +4757,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4781,7 +4781,7 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>426656</v>
+        <v>426573</v>
       </c>
       <c r="R40" t="n">
         <v>6784360</v>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4853,7 +4853,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128413197</v>
+        <v>128418719</v>
       </c>
       <c r="B41" t="n">
         <v>79032</v>
@@ -4888,10 +4888,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>426532</v>
+        <v>426571</v>
       </c>
       <c r="R41" t="n">
-        <v>6784390</v>
+        <v>6784357</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4933,7 +4933,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4960,7 +4960,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128417709</v>
+        <v>128418198</v>
       </c>
       <c r="B42" t="n">
         <v>79032</v>
@@ -4991,14 +4991,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>426717</v>
+        <v>426656</v>
       </c>
       <c r="R42" t="n">
-        <v>6784350</v>
+        <v>6784360</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5030,7 +5030,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5040,7 +5040,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5067,10 +5067,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128418704</v>
+        <v>128413197</v>
       </c>
       <c r="B43" t="n">
-        <v>78790</v>
+        <v>79032</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5078,21 +5078,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5102,10 +5102,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>426573</v>
+        <v>426532</v>
       </c>
       <c r="R43" t="n">
-        <v>6784360</v>
+        <v>6784390</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5137,7 +5137,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5147,7 +5147,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5174,7 +5174,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128418719</v>
+        <v>128415503</v>
       </c>
       <c r="B44" t="n">
         <v>79032</v>
@@ -5209,10 +5209,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>426571</v>
+        <v>426605</v>
       </c>
       <c r="R44" t="n">
-        <v>6784357</v>
+        <v>6784090</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5244,7 +5244,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5254,7 +5254,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5281,7 +5281,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128415503</v>
+        <v>128417709</v>
       </c>
       <c r="B45" t="n">
         <v>79032</v>
@@ -5312,14 +5312,14 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>426605</v>
+        <v>426717</v>
       </c>
       <c r="R45" t="n">
-        <v>6784090</v>
+        <v>6784350</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5351,7 +5351,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5816,50 +5816,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128415767</v>
+        <v>128417096</v>
       </c>
       <c r="B50" t="n">
-        <v>8450</v>
+        <v>79032</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>426618</v>
+        <v>426812</v>
       </c>
       <c r="R50" t="n">
-        <v>6784050</v>
+        <v>6784257</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5891,7 +5886,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5901,7 +5896,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6035,7 +6030,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128414874</v>
+        <v>128415767</v>
       </c>
       <c r="B52" t="n">
         <v>8450</v>
@@ -6066,7 +6061,7 @@
       <c r="I52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -6075,10 +6070,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>426535</v>
+        <v>426618</v>
       </c>
       <c r="R52" t="n">
-        <v>6784210</v>
+        <v>6784050</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6110,7 +6105,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6120,7 +6115,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6147,45 +6142,50 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128417096</v>
+        <v>128414874</v>
       </c>
       <c r="B53" t="n">
-        <v>79032</v>
+        <v>8450</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>426812</v>
+        <v>426535</v>
       </c>
       <c r="R53" t="n">
-        <v>6784257</v>
+        <v>6784210</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6217,7 +6217,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6227,7 +6227,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6361,10 +6361,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128415267</v>
+        <v>128413992</v>
       </c>
       <c r="B55" t="n">
-        <v>78791</v>
+        <v>79032</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6372,21 +6372,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6396,10 +6396,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>426604</v>
+        <v>426519</v>
       </c>
       <c r="R55" t="n">
-        <v>6784093</v>
+        <v>6784308</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6441,7 +6441,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6468,10 +6468,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128413992</v>
+        <v>128415267</v>
       </c>
       <c r="B56" t="n">
-        <v>79032</v>
+        <v>78791</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6479,21 +6479,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6503,10 +6503,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>426519</v>
+        <v>426604</v>
       </c>
       <c r="R56" t="n">
-        <v>6784308</v>
+        <v>6784093</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6538,7 +6538,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6548,7 +6548,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6575,7 +6575,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128418258</v>
+        <v>128417675</v>
       </c>
       <c r="B57" t="n">
         <v>79032</v>
@@ -6606,14 +6606,14 @@
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>426632</v>
+        <v>426764</v>
       </c>
       <c r="R57" t="n">
-        <v>6784364</v>
+        <v>6784308</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6645,7 +6645,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6655,7 +6655,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6789,7 +6789,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128417675</v>
+        <v>128418258</v>
       </c>
       <c r="B59" t="n">
         <v>79032</v>
@@ -6820,14 +6820,14 @@
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>426764</v>
+        <v>426632</v>
       </c>
       <c r="R59" t="n">
-        <v>6784308</v>
+        <v>6784364</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6859,7 +6859,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6869,7 +6869,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6896,50 +6896,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128404480</v>
+        <v>128416385</v>
       </c>
       <c r="B60" t="n">
-        <v>8450</v>
+        <v>79650</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>426773</v>
+        <v>426796</v>
       </c>
       <c r="R60" t="n">
-        <v>6784434</v>
+        <v>6784156</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6971,7 +6966,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6981,7 +6976,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7008,45 +7003,50 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128416385</v>
+        <v>128404480</v>
       </c>
       <c r="B61" t="n">
-        <v>79650</v>
+        <v>8450</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>426796</v>
+        <v>426773</v>
       </c>
       <c r="R61" t="n">
-        <v>6784156</v>
+        <v>6784434</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7078,7 +7078,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7088,7 +7088,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7436,7 +7436,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128416277</v>
+        <v>128415117</v>
       </c>
       <c r="B65" t="n">
         <v>8450</v>
@@ -7472,14 +7472,14 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>426797</v>
+        <v>426554</v>
       </c>
       <c r="R65" t="n">
-        <v>6784155</v>
+        <v>6784161</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7511,7 +7511,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7521,7 +7521,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7548,7 +7548,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128415117</v>
+        <v>128416277</v>
       </c>
       <c r="B66" t="n">
         <v>8450</v>
@@ -7584,14 +7584,14 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>426554</v>
+        <v>426797</v>
       </c>
       <c r="R66" t="n">
-        <v>6784161</v>
+        <v>6784155</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7623,7 +7623,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7633,7 +7633,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7660,10 +7660,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128413333</v>
+        <v>128413310</v>
       </c>
       <c r="B67" t="n">
-        <v>78790</v>
+        <v>57670</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7671,34 +7671,39 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>426459</v>
+        <v>426477</v>
       </c>
       <c r="R67" t="n">
-        <v>6784412</v>
+        <v>6784397</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7730,7 +7735,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7740,7 +7745,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7767,10 +7772,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128413310</v>
+        <v>128413333</v>
       </c>
       <c r="B68" t="n">
-        <v>57670</v>
+        <v>78790</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7778,39 +7783,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>426477</v>
+        <v>426459</v>
       </c>
       <c r="R68" t="n">
-        <v>6784397</v>
+        <v>6784412</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7842,7 +7842,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7852,7 +7852,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7991,7 +7991,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128418292</v>
+        <v>128417205</v>
       </c>
       <c r="B70" t="n">
         <v>79032</v>
@@ -8022,14 +8022,14 @@
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>426624</v>
+        <v>426813</v>
       </c>
       <c r="R70" t="n">
-        <v>6784361</v>
+        <v>6784276</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8061,7 +8061,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8071,12 +8071,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>18:45</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav på tallarna på en radie av 50 meter.</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8103,7 +8098,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128417205</v>
+        <v>128418292</v>
       </c>
       <c r="B71" t="n">
         <v>79032</v>
@@ -8134,14 +8129,14 @@
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>426813</v>
+        <v>426624</v>
       </c>
       <c r="R71" t="n">
-        <v>6784276</v>
+        <v>6784361</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8173,7 +8168,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8183,7 +8178,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav på tallarna på en radie av 50 meter.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8852,38 +8852,38 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128406731</v>
+        <v>128410625</v>
       </c>
       <c r="B78" t="n">
-        <v>8450</v>
+        <v>57670</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="M78" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -8892,13 +8892,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>427073</v>
+        <v>426917</v>
       </c>
       <c r="R78" t="n">
-        <v>6784548</v>
+        <v>6784579</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8927,7 +8927,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8937,7 +8937,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8964,40 +8964,35 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128408778</v>
+        <v>128408858</v>
       </c>
       <c r="B79" t="n">
-        <v>8450</v>
+        <v>79032</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
@@ -9039,7 +9034,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9049,7 +9044,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9076,45 +9071,50 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128408858</v>
+        <v>128406731</v>
       </c>
       <c r="B80" t="n">
-        <v>79032</v>
+        <v>8450</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>427123</v>
+        <v>427073</v>
       </c>
       <c r="R80" t="n">
-        <v>6784697</v>
+        <v>6784548</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9146,7 +9146,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9156,7 +9156,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9295,38 +9295,38 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128410625</v>
+        <v>128408778</v>
       </c>
       <c r="B82" t="n">
-        <v>57670</v>
+        <v>8450</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="M82" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -9335,13 +9335,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>426917</v>
+        <v>427123</v>
       </c>
       <c r="R82" t="n">
-        <v>6784579</v>
+        <v>6784697</v>
       </c>
       <c r="S82" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9370,7 +9370,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9380,7 +9380,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9840,7 +9840,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128406999</v>
+        <v>128416502</v>
       </c>
       <c r="B87" t="n">
         <v>78791</v>
@@ -9875,10 +9875,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>427083</v>
+        <v>426841</v>
       </c>
       <c r="R87" t="n">
-        <v>6784551</v>
+        <v>6784169</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9910,7 +9910,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9920,7 +9920,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9947,7 +9947,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128416502</v>
+        <v>128406999</v>
       </c>
       <c r="B88" t="n">
         <v>78791</v>
@@ -9982,10 +9982,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>426841</v>
+        <v>427083</v>
       </c>
       <c r="R88" t="n">
-        <v>6784169</v>
+        <v>6784551</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10017,7 +10017,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10027,7 +10027,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10487,10 +10487,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128406985</v>
+        <v>128410027</v>
       </c>
       <c r="B93" t="n">
-        <v>78790</v>
+        <v>91380</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10498,34 +10498,41 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6446</v>
+        <v>5442</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>427087</v>
+        <v>427093</v>
       </c>
       <c r="R93" t="n">
-        <v>6784548</v>
+        <v>6784727</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10557,7 +10564,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10567,7 +10574,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10576,6 +10583,7 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -10594,50 +10602,45 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128404859</v>
+        <v>128406985</v>
       </c>
       <c r="B94" t="n">
-        <v>8450</v>
+        <v>78790</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>426869</v>
+        <v>427087</v>
       </c>
       <c r="R94" t="n">
-        <v>6784461</v>
+        <v>6784548</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10669,7 +10672,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10679,7 +10682,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10706,10 +10709,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128410027</v>
+        <v>128410456</v>
       </c>
       <c r="B95" t="n">
-        <v>91378</v>
+        <v>79032</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10717,41 +10720,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>427093</v>
+        <v>426882</v>
       </c>
       <c r="R95" t="n">
-        <v>6784727</v>
+        <v>6784648</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10783,7 +10779,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10793,7 +10789,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10802,7 +10798,6 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10933,45 +10928,50 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128410456</v>
+        <v>128404859</v>
       </c>
       <c r="B97" t="n">
-        <v>79032</v>
+        <v>8450</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>426882</v>
+        <v>426869</v>
       </c>
       <c r="R97" t="n">
-        <v>6784648</v>
+        <v>6784461</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11003,7 +11003,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11013,7 +11013,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11040,45 +11040,50 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128410868</v>
+        <v>128405638</v>
       </c>
       <c r="B98" t="n">
-        <v>79032</v>
+        <v>8450</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>426916</v>
+        <v>427026</v>
       </c>
       <c r="R98" t="n">
-        <v>6784534</v>
+        <v>6784560</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11110,7 +11115,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11120,7 +11125,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11147,50 +11152,45 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128405638</v>
+        <v>128410868</v>
       </c>
       <c r="B99" t="n">
-        <v>8450</v>
+        <v>79032</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>427026</v>
+        <v>426916</v>
       </c>
       <c r="R99" t="n">
-        <v>6784560</v>
+        <v>6784534</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11222,7 +11222,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11232,7 +11232,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11259,50 +11259,45 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128410908</v>
+        <v>128411027</v>
       </c>
       <c r="B100" t="n">
-        <v>8450</v>
+        <v>79032</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>426908</v>
+        <v>426858</v>
       </c>
       <c r="R100" t="n">
-        <v>6784511</v>
+        <v>6784514</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11334,7 +11329,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11344,7 +11339,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11371,45 +11366,50 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128411027</v>
+        <v>128410908</v>
       </c>
       <c r="B101" t="n">
-        <v>79032</v>
+        <v>8450</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>426858</v>
+        <v>426908</v>
       </c>
       <c r="R101" t="n">
-        <v>6784514</v>
+        <v>6784511</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11441,7 +11441,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11451,7 +11451,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11478,7 +11478,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128416713</v>
+        <v>128408932</v>
       </c>
       <c r="B102" t="n">
         <v>79032</v>
@@ -11513,10 +11513,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>426849</v>
+        <v>427081</v>
       </c>
       <c r="R102" t="n">
-        <v>6784145</v>
+        <v>6784657</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11548,7 +11548,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11558,7 +11558,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11585,7 +11585,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128408932</v>
+        <v>128416713</v>
       </c>
       <c r="B103" t="n">
         <v>79032</v>
@@ -11620,10 +11620,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>427081</v>
+        <v>426849</v>
       </c>
       <c r="R103" t="n">
-        <v>6784657</v>
+        <v>6784145</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11655,7 +11655,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11665,7 +11665,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11906,10 +11906,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128407848</v>
+        <v>128416606</v>
       </c>
       <c r="B106" t="n">
-        <v>78791</v>
+        <v>78790</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11917,21 +11917,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11941,10 +11941,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>427064</v>
+        <v>426859</v>
       </c>
       <c r="R106" t="n">
-        <v>6784585</v>
+        <v>6784153</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11976,7 +11976,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11986,7 +11986,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12013,10 +12013,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128416606</v>
+        <v>128407848</v>
       </c>
       <c r="B107" t="n">
-        <v>78790</v>
+        <v>78791</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12024,21 +12024,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12048,10 +12048,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>426859</v>
+        <v>427064</v>
       </c>
       <c r="R107" t="n">
-        <v>6784153</v>
+        <v>6784585</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12083,7 +12083,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12093,7 +12093,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD107" t="b">

--- a/artfynd/A 36371-2025 artfynd.xlsx
+++ b/artfynd/A 36371-2025 artfynd.xlsx
@@ -5709,45 +5709,50 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128416262</v>
+        <v>128415767</v>
       </c>
       <c r="B49" t="n">
-        <v>79032</v>
+        <v>8450</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>426784</v>
+        <v>426618</v>
       </c>
       <c r="R49" t="n">
-        <v>6784159</v>
+        <v>6784050</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5779,7 +5784,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5789,7 +5794,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5816,45 +5821,50 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128417096</v>
+        <v>128414874</v>
       </c>
       <c r="B50" t="n">
-        <v>79032</v>
+        <v>8450</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>426812</v>
+        <v>426535</v>
       </c>
       <c r="R50" t="n">
-        <v>6784257</v>
+        <v>6784210</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5886,7 +5896,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5896,7 +5906,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5923,7 +5933,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128415549</v>
+        <v>128416262</v>
       </c>
       <c r="B51" t="n">
         <v>79032</v>
@@ -5954,14 +5964,14 @@
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>426615</v>
+        <v>426784</v>
       </c>
       <c r="R51" t="n">
-        <v>6784068</v>
+        <v>6784159</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5993,7 +6003,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6003,7 +6013,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6030,50 +6040,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128415767</v>
+        <v>128417096</v>
       </c>
       <c r="B52" t="n">
-        <v>8450</v>
+        <v>79032</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>426618</v>
+        <v>426812</v>
       </c>
       <c r="R52" t="n">
-        <v>6784050</v>
+        <v>6784257</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6105,7 +6110,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6115,7 +6120,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6142,50 +6147,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128414874</v>
+        <v>128415549</v>
       </c>
       <c r="B53" t="n">
-        <v>8450</v>
+        <v>79032</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>426535</v>
+        <v>426615</v>
       </c>
       <c r="R53" t="n">
-        <v>6784210</v>
+        <v>6784068</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6217,7 +6217,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6227,7 +6227,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7660,50 +7660,50 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128413310</v>
+        <v>128417436</v>
       </c>
       <c r="B67" t="n">
-        <v>57670</v>
+        <v>8450</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>426477</v>
+        <v>426801</v>
       </c>
       <c r="R67" t="n">
-        <v>6784397</v>
+        <v>6784284</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7735,7 +7735,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7745,7 +7745,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7772,10 +7772,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128413333</v>
+        <v>128413310</v>
       </c>
       <c r="B68" t="n">
-        <v>78790</v>
+        <v>57670</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7783,34 +7783,39 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>426459</v>
+        <v>426477</v>
       </c>
       <c r="R68" t="n">
-        <v>6784412</v>
+        <v>6784397</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7842,7 +7847,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7852,7 +7857,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7879,50 +7884,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128417436</v>
+        <v>128413333</v>
       </c>
       <c r="B69" t="n">
-        <v>8450</v>
+        <v>78790</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>426801</v>
+        <v>426459</v>
       </c>
       <c r="R69" t="n">
-        <v>6784284</v>
+        <v>6784412</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7954,7 +7954,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7964,7 +7964,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8317,45 +8317,50 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128413213</v>
+        <v>128414247</v>
       </c>
       <c r="B73" t="n">
-        <v>78791</v>
+        <v>8450</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>426524</v>
+        <v>426535</v>
       </c>
       <c r="R73" t="n">
-        <v>6784388</v>
+        <v>6784292</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8387,7 +8392,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8397,7 +8402,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8424,50 +8429,45 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128414247</v>
+        <v>128413213</v>
       </c>
       <c r="B74" t="n">
-        <v>8450</v>
+        <v>78791</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>426535</v>
+        <v>426524</v>
       </c>
       <c r="R74" t="n">
-        <v>6784292</v>
+        <v>6784388</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8499,7 +8499,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8509,7 +8509,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -10487,10 +10487,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128410027</v>
+        <v>128406985</v>
       </c>
       <c r="B93" t="n">
-        <v>91380</v>
+        <v>78790</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10498,41 +10498,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>5442</v>
+        <v>6446</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>427093</v>
+        <v>427087</v>
       </c>
       <c r="R93" t="n">
-        <v>6784727</v>
+        <v>6784548</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10564,7 +10557,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10574,7 +10567,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10583,7 +10576,6 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -10602,10 +10594,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128406985</v>
+        <v>128410456</v>
       </c>
       <c r="B94" t="n">
-        <v>78790</v>
+        <v>79032</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10613,21 +10605,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10637,10 +10629,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>427087</v>
+        <v>426882</v>
       </c>
       <c r="R94" t="n">
-        <v>6784548</v>
+        <v>6784648</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10672,7 +10664,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10682,7 +10674,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10709,10 +10701,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128410456</v>
+        <v>128410027</v>
       </c>
       <c r="B95" t="n">
-        <v>79032</v>
+        <v>91380</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10720,34 +10712,41 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>426882</v>
+        <v>427093</v>
       </c>
       <c r="R95" t="n">
-        <v>6784648</v>
+        <v>6784727</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10779,7 +10778,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10789,7 +10788,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10798,6 +10797,7 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -11259,45 +11259,50 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128411027</v>
+        <v>128410908</v>
       </c>
       <c r="B100" t="n">
-        <v>79032</v>
+        <v>8450</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>426858</v>
+        <v>426908</v>
       </c>
       <c r="R100" t="n">
-        <v>6784514</v>
+        <v>6784511</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11329,7 +11334,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11339,7 +11344,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11366,50 +11371,45 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128410908</v>
+        <v>128411027</v>
       </c>
       <c r="B101" t="n">
-        <v>8450</v>
+        <v>79032</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>426908</v>
+        <v>426858</v>
       </c>
       <c r="R101" t="n">
-        <v>6784511</v>
+        <v>6784514</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11441,7 +11441,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11451,7 +11451,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11478,7 +11478,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128408932</v>
+        <v>128416713</v>
       </c>
       <c r="B102" t="n">
         <v>79032</v>
@@ -11513,10 +11513,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>427081</v>
+        <v>426849</v>
       </c>
       <c r="R102" t="n">
-        <v>6784657</v>
+        <v>6784145</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11548,7 +11548,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11558,7 +11558,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11585,7 +11585,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128416713</v>
+        <v>128408932</v>
       </c>
       <c r="B103" t="n">
         <v>79032</v>
@@ -11620,10 +11620,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>426849</v>
+        <v>427081</v>
       </c>
       <c r="R103" t="n">
-        <v>6784145</v>
+        <v>6784657</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11655,7 +11655,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11665,7 +11665,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD103" t="b">

--- a/artfynd/A 36371-2025 artfynd.xlsx
+++ b/artfynd/A 36371-2025 artfynd.xlsx
@@ -2696,7 +2696,7 @@
         <v>128415595</v>
       </c>
       <c r="B21" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         <v>128415015</v>
       </c>
       <c r="B22" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2910,7 +2910,7 @@
         <v>128414172</v>
       </c>
       <c r="B23" t="n">
-        <v>78790</v>
+        <v>78840</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3014,10 +3014,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128418402</v>
+        <v>128411184</v>
       </c>
       <c r="B24" t="n">
-        <v>78790</v>
+        <v>78841</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3025,34 +3025,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>426596</v>
+        <v>426819</v>
       </c>
       <c r="R24" t="n">
-        <v>6784364</v>
+        <v>6784515</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3121,10 +3121,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128414481</v>
+        <v>128418402</v>
       </c>
       <c r="B25" t="n">
-        <v>79650</v>
+        <v>78840</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3132,21 +3132,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3156,10 +3156,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>426524</v>
+        <v>426596</v>
       </c>
       <c r="R25" t="n">
-        <v>6784260</v>
+        <v>6784364</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3191,7 +3191,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3201,7 +3201,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3228,10 +3228,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128411184</v>
+        <v>128414481</v>
       </c>
       <c r="B26" t="n">
-        <v>78791</v>
+        <v>79702</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3239,34 +3239,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>426819</v>
+        <v>426524</v>
       </c>
       <c r="R26" t="n">
-        <v>6784515</v>
+        <v>6784260</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3298,7 +3298,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3308,7 +3308,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3335,10 +3335,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128414801</v>
+        <v>128414155</v>
       </c>
       <c r="B27" t="n">
-        <v>79032</v>
+        <v>78841</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3346,21 +3346,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3370,10 +3370,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>426524</v>
+        <v>426540</v>
       </c>
       <c r="R27" t="n">
-        <v>6784260</v>
+        <v>6784305</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3405,7 +3405,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3415,7 +3415,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3442,10 +3442,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128417228</v>
+        <v>128414801</v>
       </c>
       <c r="B28" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3473,14 +3473,14 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>426801</v>
+        <v>426524</v>
       </c>
       <c r="R28" t="n">
-        <v>6784284</v>
+        <v>6784260</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3512,7 +3512,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3522,7 +3522,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3552,7 +3552,7 @@
         <v>128416106</v>
       </c>
       <c r="B29" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3661,10 +3661,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128414155</v>
+        <v>128417228</v>
       </c>
       <c r="B30" t="n">
-        <v>78791</v>
+        <v>79083</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3672,34 +3672,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>426540</v>
+        <v>426801</v>
       </c>
       <c r="R30" t="n">
-        <v>6784305</v>
+        <v>6784284</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3731,7 +3731,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3771,7 +3771,7 @@
         <v>128414306</v>
       </c>
       <c r="B31" t="n">
-        <v>57670</v>
+        <v>57682</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3883,7 +3883,7 @@
         <v>128413169</v>
       </c>
       <c r="B32" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3987,50 +3987,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128413945</v>
+        <v>128418215</v>
       </c>
       <c r="B33" t="n">
-        <v>8450</v>
+        <v>78841</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>426498</v>
+        <v>426655</v>
       </c>
       <c r="R33" t="n">
-        <v>6784322</v>
+        <v>6784360</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4062,7 +4057,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4072,7 +4067,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4099,45 +4094,50 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128418215</v>
+        <v>128413945</v>
       </c>
       <c r="B34" t="n">
-        <v>78791</v>
+        <v>8450</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>426655</v>
+        <v>426498</v>
       </c>
       <c r="R34" t="n">
-        <v>6784360</v>
+        <v>6784322</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4209,7 +4209,7 @@
         <v>128416349</v>
       </c>
       <c r="B35" t="n">
-        <v>78790</v>
+        <v>78840</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4316,7 +4316,7 @@
         <v>128404649</v>
       </c>
       <c r="B36" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4423,7 +4423,7 @@
         <v>128412524</v>
       </c>
       <c r="B37" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4642,7 +4642,7 @@
         <v>128414383</v>
       </c>
       <c r="B39" t="n">
-        <v>78791</v>
+        <v>78841</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4749,7 +4749,7 @@
         <v>128418704</v>
       </c>
       <c r="B40" t="n">
-        <v>78790</v>
+        <v>78840</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4856,7 +4856,7 @@
         <v>128418719</v>
       </c>
       <c r="B41" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4963,7 +4963,7 @@
         <v>128418198</v>
       </c>
       <c r="B42" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
         <v>128413197</v>
       </c>
       <c r="B43" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5177,7 +5177,7 @@
         <v>128415503</v>
       </c>
       <c r="B44" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5284,7 +5284,7 @@
         <v>128417709</v>
       </c>
       <c r="B45" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5391,7 +5391,7 @@
         <v>128413145</v>
       </c>
       <c r="B46" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5498,7 +5498,7 @@
         <v>128416206</v>
       </c>
       <c r="B47" t="n">
-        <v>78790</v>
+        <v>78840</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5605,7 +5605,7 @@
         <v>128412596</v>
       </c>
       <c r="B48" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5936,7 +5936,7 @@
         <v>128416262</v>
       </c>
       <c r="B51" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6043,7 +6043,7 @@
         <v>128417096</v>
       </c>
       <c r="B52" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6150,7 +6150,7 @@
         <v>128415549</v>
       </c>
       <c r="B53" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6257,7 +6257,7 @@
         <v>128418647</v>
       </c>
       <c r="B54" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6364,7 +6364,7 @@
         <v>128413992</v>
       </c>
       <c r="B55" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6471,7 +6471,7 @@
         <v>128415267</v>
       </c>
       <c r="B56" t="n">
-        <v>78791</v>
+        <v>78841</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6578,7 +6578,7 @@
         <v>128417675</v>
       </c>
       <c r="B57" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6682,10 +6682,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128415393</v>
+        <v>128418258</v>
       </c>
       <c r="B58" t="n">
-        <v>79650</v>
+        <v>79083</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6693,21 +6693,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6717,10 +6717,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>426601</v>
+        <v>426632</v>
       </c>
       <c r="R58" t="n">
-        <v>6784100</v>
+        <v>6784364</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6752,7 +6752,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6762,7 +6762,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6789,10 +6789,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128418258</v>
+        <v>128415393</v>
       </c>
       <c r="B59" t="n">
-        <v>79032</v>
+        <v>79702</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6800,21 +6800,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6824,10 +6824,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>426632</v>
+        <v>426601</v>
       </c>
       <c r="R59" t="n">
-        <v>6784364</v>
+        <v>6784100</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6859,7 +6859,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6869,7 +6869,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6899,7 +6899,7 @@
         <v>128416385</v>
       </c>
       <c r="B60" t="n">
-        <v>79650</v>
+        <v>79702</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7118,7 +7118,7 @@
         <v>128414843</v>
       </c>
       <c r="B62" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7222,10 +7222,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128414095</v>
+        <v>128412109</v>
       </c>
       <c r="B63" t="n">
-        <v>78791</v>
+        <v>79083</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7233,21 +7233,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7257,10 +7257,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>426556</v>
+        <v>426646</v>
       </c>
       <c r="R63" t="n">
-        <v>6784312</v>
+        <v>6784678</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7292,7 +7292,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7302,7 +7302,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7329,10 +7329,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128412109</v>
+        <v>128414095</v>
       </c>
       <c r="B64" t="n">
-        <v>79032</v>
+        <v>78841</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7340,21 +7340,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7364,10 +7364,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>426646</v>
+        <v>426556</v>
       </c>
       <c r="R64" t="n">
-        <v>6784678</v>
+        <v>6784312</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7399,7 +7399,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7409,7 +7409,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7660,50 +7660,50 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128417436</v>
+        <v>128413310</v>
       </c>
       <c r="B67" t="n">
-        <v>8450</v>
+        <v>57682</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>426801</v>
+        <v>426477</v>
       </c>
       <c r="R67" t="n">
-        <v>6784284</v>
+        <v>6784397</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7735,7 +7735,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7745,7 +7745,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7772,10 +7772,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128413310</v>
+        <v>128413333</v>
       </c>
       <c r="B68" t="n">
-        <v>57670</v>
+        <v>78840</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7783,39 +7783,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>426477</v>
+        <v>426459</v>
       </c>
       <c r="R68" t="n">
-        <v>6784397</v>
+        <v>6784412</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7847,7 +7842,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7857,7 +7852,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7884,45 +7879,50 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128413333</v>
+        <v>128417436</v>
       </c>
       <c r="B69" t="n">
-        <v>78790</v>
+        <v>8450</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>426459</v>
+        <v>426801</v>
       </c>
       <c r="R69" t="n">
-        <v>6784412</v>
+        <v>6784284</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7954,7 +7954,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7964,7 +7964,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7994,7 +7994,7 @@
         <v>128417205</v>
       </c>
       <c r="B70" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8101,7 +8101,7 @@
         <v>128418292</v>
       </c>
       <c r="B71" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         <v>128415978</v>
       </c>
       <c r="B72" t="n">
-        <v>78790</v>
+        <v>78840</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8432,7 +8432,7 @@
         <v>128413213</v>
       </c>
       <c r="B74" t="n">
-        <v>78791</v>
+        <v>78841</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8636,7 +8636,7 @@
         <v>128410669</v>
       </c>
       <c r="B76" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8855,7 +8855,7 @@
         <v>128410625</v>
       </c>
       <c r="B78" t="n">
-        <v>57670</v>
+        <v>57682</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8967,7 +8967,7 @@
         <v>128408858</v>
       </c>
       <c r="B79" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9071,7 +9071,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128406731</v>
+        <v>128408778</v>
       </c>
       <c r="B80" t="n">
         <v>8450</v>
@@ -9102,7 +9102,7 @@
       <c r="I80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -9111,10 +9111,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>427073</v>
+        <v>427123</v>
       </c>
       <c r="R80" t="n">
-        <v>6784548</v>
+        <v>6784697</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9146,7 +9146,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9156,7 +9156,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9183,7 +9183,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128416919</v>
+        <v>128406731</v>
       </c>
       <c r="B81" t="n">
         <v>8450</v>
@@ -9223,10 +9223,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>426842</v>
+        <v>427073</v>
       </c>
       <c r="R81" t="n">
-        <v>6784214</v>
+        <v>6784548</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9258,7 +9258,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9268,7 +9268,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9295,7 +9295,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128408778</v>
+        <v>128416919</v>
       </c>
       <c r="B82" t="n">
         <v>8450</v>
@@ -9326,7 +9326,7 @@
       <c r="I82" t="inlineStr"/>
       <c r="M82" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -9335,10 +9335,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>427123</v>
+        <v>426842</v>
       </c>
       <c r="R82" t="n">
-        <v>6784697</v>
+        <v>6784214</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9370,7 +9370,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9380,7 +9380,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9407,10 +9407,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128409945</v>
+        <v>128404878</v>
       </c>
       <c r="B83" t="n">
-        <v>78791</v>
+        <v>57682</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9418,34 +9418,39 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>427084</v>
+        <v>426879</v>
       </c>
       <c r="R83" t="n">
-        <v>6784718</v>
+        <v>6784490</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9477,7 +9482,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9487,7 +9492,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9514,10 +9519,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128404878</v>
+        <v>128409945</v>
       </c>
       <c r="B84" t="n">
-        <v>57670</v>
+        <v>78841</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9525,39 +9530,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>426879</v>
+        <v>427084</v>
       </c>
       <c r="R84" t="n">
-        <v>6784490</v>
+        <v>6784718</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9589,7 +9589,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9599,7 +9599,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9629,7 +9629,7 @@
         <v>128407168</v>
       </c>
       <c r="B85" t="n">
-        <v>78791</v>
+        <v>78841</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9736,7 +9736,7 @@
         <v>128416596</v>
       </c>
       <c r="B86" t="n">
-        <v>79650</v>
+        <v>79702</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9840,10 +9840,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128416502</v>
+        <v>128406999</v>
       </c>
       <c r="B87" t="n">
-        <v>78791</v>
+        <v>78841</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9875,10 +9875,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>426841</v>
+        <v>427083</v>
       </c>
       <c r="R87" t="n">
-        <v>6784169</v>
+        <v>6784551</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9910,7 +9910,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9920,7 +9920,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9947,10 +9947,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128406999</v>
+        <v>128416502</v>
       </c>
       <c r="B88" t="n">
-        <v>78791</v>
+        <v>78841</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9982,10 +9982,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>427083</v>
+        <v>426841</v>
       </c>
       <c r="R88" t="n">
-        <v>6784551</v>
+        <v>6784169</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10017,7 +10017,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10027,7 +10027,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10057,7 +10057,7 @@
         <v>128416791</v>
       </c>
       <c r="B89" t="n">
-        <v>78791</v>
+        <v>78841</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10164,7 +10164,7 @@
         <v>128417147</v>
       </c>
       <c r="B90" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10268,10 +10268,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128423249</v>
+        <v>128417068</v>
       </c>
       <c r="B91" t="n">
-        <v>57670</v>
+        <v>79083</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10279,42 +10279,37 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Fisklöstjärnen, Dlr</t>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>427097</v>
+        <v>426830</v>
       </c>
       <c r="R91" t="n">
-        <v>6784657</v>
+        <v>6784251</v>
       </c>
       <c r="S91" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10343,7 +10338,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10353,7 +10348,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10380,10 +10375,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128417068</v>
+        <v>128423249</v>
       </c>
       <c r="B92" t="n">
-        <v>79032</v>
+        <v>57682</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10391,37 +10386,42 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+          <t>Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>426830</v>
+        <v>427097</v>
       </c>
       <c r="R92" t="n">
-        <v>6784251</v>
+        <v>6784657</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10460,7 +10460,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10490,7 +10490,7 @@
         <v>128406985</v>
       </c>
       <c r="B93" t="n">
-        <v>78790</v>
+        <v>78840</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10594,45 +10594,50 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128410456</v>
+        <v>128410598</v>
       </c>
       <c r="B94" t="n">
-        <v>79032</v>
+        <v>8450</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>426882</v>
+        <v>426922</v>
       </c>
       <c r="R94" t="n">
-        <v>6784648</v>
+        <v>6784576</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10664,7 +10669,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10674,7 +10679,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10701,52 +10706,50 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128410027</v>
+        <v>128404859</v>
       </c>
       <c r="B95" t="n">
-        <v>91380</v>
+        <v>8450</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>427093</v>
+        <v>426869</v>
       </c>
       <c r="R95" t="n">
-        <v>6784727</v>
+        <v>6784461</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10778,7 +10781,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10788,7 +10791,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10797,7 +10800,6 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10816,50 +10818,52 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128410598</v>
+        <v>128410027</v>
       </c>
       <c r="B96" t="n">
-        <v>8450</v>
+        <v>91472</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>426922</v>
+        <v>427093</v>
       </c>
       <c r="R96" t="n">
-        <v>6784576</v>
+        <v>6784727</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10891,7 +10895,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10901,7 +10905,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10910,6 +10914,7 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -10928,50 +10933,45 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128404859</v>
+        <v>128410456</v>
       </c>
       <c r="B97" t="n">
-        <v>8450</v>
+        <v>79083</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>426869</v>
+        <v>426882</v>
       </c>
       <c r="R97" t="n">
-        <v>6784461</v>
+        <v>6784648</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11003,7 +11003,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11013,7 +11013,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11040,50 +11040,45 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128405638</v>
+        <v>128410868</v>
       </c>
       <c r="B98" t="n">
-        <v>8450</v>
+        <v>79083</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>427026</v>
+        <v>426916</v>
       </c>
       <c r="R98" t="n">
-        <v>6784560</v>
+        <v>6784534</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11115,7 +11110,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11125,7 +11120,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11152,45 +11147,50 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128410868</v>
+        <v>128405638</v>
       </c>
       <c r="B99" t="n">
-        <v>79032</v>
+        <v>8450</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>426916</v>
+        <v>427026</v>
       </c>
       <c r="R99" t="n">
-        <v>6784534</v>
+        <v>6784560</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11222,7 +11222,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11232,7 +11232,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11259,50 +11259,45 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128410908</v>
+        <v>128411027</v>
       </c>
       <c r="B100" t="n">
-        <v>8450</v>
+        <v>79083</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>426908</v>
+        <v>426858</v>
       </c>
       <c r="R100" t="n">
-        <v>6784511</v>
+        <v>6784514</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11334,7 +11329,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11344,7 +11339,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11371,45 +11366,50 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128411027</v>
+        <v>128410908</v>
       </c>
       <c r="B101" t="n">
-        <v>79032</v>
+        <v>8450</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>426858</v>
+        <v>426908</v>
       </c>
       <c r="R101" t="n">
-        <v>6784514</v>
+        <v>6784511</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11441,7 +11441,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11451,7 +11451,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11481,7 +11481,7 @@
         <v>128416713</v>
       </c>
       <c r="B102" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11588,7 +11588,7 @@
         <v>128408932</v>
       </c>
       <c r="B103" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11692,10 +11692,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128407898</v>
+        <v>128409925</v>
       </c>
       <c r="B104" t="n">
-        <v>78790</v>
+        <v>79673</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11703,21 +11703,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11727,10 +11727,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>427062</v>
+        <v>427082</v>
       </c>
       <c r="R104" t="n">
-        <v>6784591</v>
+        <v>6784715</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11762,7 +11762,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11772,7 +11772,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11799,10 +11799,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128409925</v>
+        <v>128407898</v>
       </c>
       <c r="B105" t="n">
-        <v>79621</v>
+        <v>78840</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11810,21 +11810,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11834,10 +11834,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>427082</v>
+        <v>427062</v>
       </c>
       <c r="R105" t="n">
-        <v>6784715</v>
+        <v>6784591</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11869,7 +11869,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11879,7 +11879,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11909,7 +11909,7 @@
         <v>128416606</v>
       </c>
       <c r="B106" t="n">
-        <v>78790</v>
+        <v>78840</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12016,7 +12016,7 @@
         <v>128407848</v>
       </c>
       <c r="B107" t="n">
-        <v>78791</v>
+        <v>78841</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>

--- a/artfynd/A 36371-2025 artfynd.xlsx
+++ b/artfynd/A 36371-2025 artfynd.xlsx
@@ -3014,10 +3014,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128411184</v>
+        <v>128418402</v>
       </c>
       <c r="B24" t="n">
-        <v>78841</v>
+        <v>78840</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3025,34 +3025,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>426819</v>
+        <v>426596</v>
       </c>
       <c r="R24" t="n">
-        <v>6784515</v>
+        <v>6784364</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3121,10 +3121,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128418402</v>
+        <v>128414481</v>
       </c>
       <c r="B25" t="n">
-        <v>78840</v>
+        <v>79702</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3132,21 +3132,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3156,10 +3156,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>426596</v>
+        <v>426524</v>
       </c>
       <c r="R25" t="n">
-        <v>6784364</v>
+        <v>6784260</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3191,7 +3191,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3201,7 +3201,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3228,10 +3228,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128414481</v>
+        <v>128411184</v>
       </c>
       <c r="B26" t="n">
-        <v>79702</v>
+        <v>78841</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3239,34 +3239,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>426524</v>
+        <v>426819</v>
       </c>
       <c r="R26" t="n">
-        <v>6784260</v>
+        <v>6784515</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3298,7 +3298,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3308,7 +3308,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3335,10 +3335,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128414155</v>
+        <v>128414801</v>
       </c>
       <c r="B27" t="n">
-        <v>78841</v>
+        <v>79083</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3346,21 +3346,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3370,10 +3370,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>426540</v>
+        <v>426524</v>
       </c>
       <c r="R27" t="n">
-        <v>6784305</v>
+        <v>6784260</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3405,7 +3405,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3415,7 +3415,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3442,7 +3442,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128414801</v>
+        <v>128416106</v>
       </c>
       <c r="B28" t="n">
         <v>79083</v>
@@ -3473,14 +3473,14 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>426524</v>
+        <v>426746</v>
       </c>
       <c r="R28" t="n">
-        <v>6784260</v>
+        <v>6784096</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3512,7 +3512,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3522,7 +3522,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50 meter.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3549,7 +3554,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128416106</v>
+        <v>128417228</v>
       </c>
       <c r="B29" t="n">
         <v>79083</v>
@@ -3584,10 +3589,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>426746</v>
+        <v>426801</v>
       </c>
       <c r="R29" t="n">
-        <v>6784096</v>
+        <v>6784284</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3619,7 +3624,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3629,12 +3634,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:35</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50 meter.</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3661,10 +3661,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128417228</v>
+        <v>128414155</v>
       </c>
       <c r="B30" t="n">
-        <v>79083</v>
+        <v>78841</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3672,34 +3672,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>426801</v>
+        <v>426540</v>
       </c>
       <c r="R30" t="n">
-        <v>6784284</v>
+        <v>6784305</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3731,7 +3731,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3768,10 +3768,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128414306</v>
+        <v>128413169</v>
       </c>
       <c r="B31" t="n">
-        <v>57682</v>
+        <v>79083</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3779,39 +3779,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>426519</v>
+        <v>426555</v>
       </c>
       <c r="R31" t="n">
-        <v>6784286</v>
+        <v>6784393</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3843,7 +3838,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3853,7 +3848,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3880,10 +3875,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128413169</v>
+        <v>128418215</v>
       </c>
       <c r="B32" t="n">
-        <v>79083</v>
+        <v>78841</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3891,21 +3886,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3915,10 +3910,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>426555</v>
+        <v>426655</v>
       </c>
       <c r="R32" t="n">
-        <v>6784393</v>
+        <v>6784360</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3950,7 +3945,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3960,7 +3955,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3987,45 +3982,50 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128418215</v>
+        <v>128413945</v>
       </c>
       <c r="B33" t="n">
-        <v>78841</v>
+        <v>8450</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>426655</v>
+        <v>426498</v>
       </c>
       <c r="R33" t="n">
-        <v>6784360</v>
+        <v>6784322</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4057,7 +4057,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4094,38 +4094,38 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128413945</v>
+        <v>128414306</v>
       </c>
       <c r="B34" t="n">
-        <v>8450</v>
+        <v>57682</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>426498</v>
+        <v>426519</v>
       </c>
       <c r="R34" t="n">
-        <v>6784322</v>
+        <v>6784286</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4420,10 +4420,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128412524</v>
+        <v>128414383</v>
       </c>
       <c r="B37" t="n">
-        <v>79083</v>
+        <v>78841</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4431,21 +4431,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4455,10 +4455,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>426466</v>
+        <v>426509</v>
       </c>
       <c r="R37" t="n">
-        <v>6784510</v>
+        <v>6784270</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4490,7 +4490,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4639,10 +4639,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128414383</v>
+        <v>128412524</v>
       </c>
       <c r="B39" t="n">
-        <v>78841</v>
+        <v>79083</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4650,21 +4650,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4674,10 +4674,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>426509</v>
+        <v>426466</v>
       </c>
       <c r="R39" t="n">
-        <v>6784270</v>
+        <v>6784510</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4709,7 +4709,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4719,7 +4719,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5709,50 +5709,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128415767</v>
+        <v>128416262</v>
       </c>
       <c r="B49" t="n">
-        <v>8450</v>
+        <v>79083</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>426618</v>
+        <v>426784</v>
       </c>
       <c r="R49" t="n">
-        <v>6784050</v>
+        <v>6784159</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5784,7 +5779,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5794,7 +5789,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5821,50 +5816,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128414874</v>
+        <v>128417096</v>
       </c>
       <c r="B50" t="n">
-        <v>8450</v>
+        <v>79083</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>426535</v>
+        <v>426812</v>
       </c>
       <c r="R50" t="n">
-        <v>6784210</v>
+        <v>6784257</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5896,7 +5886,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5906,7 +5896,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5933,7 +5923,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128416262</v>
+        <v>128415549</v>
       </c>
       <c r="B51" t="n">
         <v>79083</v>
@@ -5964,14 +5954,14 @@
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>426784</v>
+        <v>426615</v>
       </c>
       <c r="R51" t="n">
-        <v>6784159</v>
+        <v>6784068</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6003,7 +5993,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6013,7 +6003,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6040,45 +6030,50 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128417096</v>
+        <v>128414874</v>
       </c>
       <c r="B52" t="n">
-        <v>79083</v>
+        <v>8450</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>426812</v>
+        <v>426535</v>
       </c>
       <c r="R52" t="n">
-        <v>6784257</v>
+        <v>6784210</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6110,7 +6105,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6120,7 +6115,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6147,45 +6142,50 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128415549</v>
+        <v>128415767</v>
       </c>
       <c r="B53" t="n">
-        <v>79083</v>
+        <v>8450</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>426615</v>
+        <v>426618</v>
       </c>
       <c r="R53" t="n">
-        <v>6784068</v>
+        <v>6784050</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6217,7 +6217,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6227,7 +6227,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6682,10 +6682,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128418258</v>
+        <v>128415393</v>
       </c>
       <c r="B58" t="n">
-        <v>79083</v>
+        <v>79702</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6693,21 +6693,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6717,10 +6717,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>426632</v>
+        <v>426601</v>
       </c>
       <c r="R58" t="n">
-        <v>6784364</v>
+        <v>6784100</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6752,7 +6752,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6762,7 +6762,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6789,10 +6789,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128415393</v>
+        <v>128418258</v>
       </c>
       <c r="B59" t="n">
-        <v>79702</v>
+        <v>79083</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6800,21 +6800,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6824,10 +6824,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>426601</v>
+        <v>426632</v>
       </c>
       <c r="R59" t="n">
-        <v>6784100</v>
+        <v>6784364</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6859,7 +6859,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6869,7 +6869,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7222,10 +7222,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128412109</v>
+        <v>128414095</v>
       </c>
       <c r="B63" t="n">
-        <v>79083</v>
+        <v>78841</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7233,21 +7233,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7257,10 +7257,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>426646</v>
+        <v>426556</v>
       </c>
       <c r="R63" t="n">
-        <v>6784678</v>
+        <v>6784312</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7292,7 +7292,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7302,7 +7302,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7329,10 +7329,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128414095</v>
+        <v>128412109</v>
       </c>
       <c r="B64" t="n">
-        <v>78841</v>
+        <v>79083</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7340,21 +7340,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7364,10 +7364,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>426556</v>
+        <v>426646</v>
       </c>
       <c r="R64" t="n">
-        <v>6784312</v>
+        <v>6784678</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7399,7 +7399,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7409,7 +7409,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7772,45 +7772,50 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128413333</v>
+        <v>128417436</v>
       </c>
       <c r="B68" t="n">
-        <v>78840</v>
+        <v>8450</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>426459</v>
+        <v>426801</v>
       </c>
       <c r="R68" t="n">
-        <v>6784412</v>
+        <v>6784284</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7842,7 +7847,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7852,7 +7857,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7879,50 +7884,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128417436</v>
+        <v>128413333</v>
       </c>
       <c r="B69" t="n">
-        <v>8450</v>
+        <v>78840</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>426801</v>
+        <v>426459</v>
       </c>
       <c r="R69" t="n">
-        <v>6784284</v>
+        <v>6784412</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7954,7 +7954,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7964,7 +7964,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8317,50 +8317,45 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128414247</v>
+        <v>128413213</v>
       </c>
       <c r="B73" t="n">
-        <v>8450</v>
+        <v>78841</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>426535</v>
+        <v>426524</v>
       </c>
       <c r="R73" t="n">
-        <v>6784292</v>
+        <v>6784388</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8392,7 +8387,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8402,7 +8397,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8429,45 +8424,50 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128413213</v>
+        <v>128414247</v>
       </c>
       <c r="B74" t="n">
-        <v>78841</v>
+        <v>8450</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>426524</v>
+        <v>426535</v>
       </c>
       <c r="R74" t="n">
-        <v>6784388</v>
+        <v>6784292</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8499,7 +8499,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8509,7 +8509,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8852,10 +8852,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128410625</v>
+        <v>128408858</v>
       </c>
       <c r="B78" t="n">
-        <v>57682</v>
+        <v>79083</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8863,42 +8863,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>426917</v>
+        <v>427123</v>
       </c>
       <c r="R78" t="n">
-        <v>6784579</v>
+        <v>6784697</v>
       </c>
       <c r="S78" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8927,7 +8922,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8937,7 +8932,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8964,45 +8959,50 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128408858</v>
+        <v>128416919</v>
       </c>
       <c r="B79" t="n">
-        <v>79083</v>
+        <v>8450</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>427123</v>
+        <v>426842</v>
       </c>
       <c r="R79" t="n">
-        <v>6784697</v>
+        <v>6784214</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9034,7 +9034,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9044,7 +9044,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9295,38 +9295,38 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128416919</v>
+        <v>128410625</v>
       </c>
       <c r="B82" t="n">
-        <v>8450</v>
+        <v>57682</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="M82" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -9335,13 +9335,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>426842</v>
+        <v>426917</v>
       </c>
       <c r="R82" t="n">
-        <v>6784214</v>
+        <v>6784579</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9370,7 +9370,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9380,7 +9380,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10594,50 +10594,45 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128410598</v>
+        <v>128410456</v>
       </c>
       <c r="B94" t="n">
-        <v>8450</v>
+        <v>79083</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>426922</v>
+        <v>426882</v>
       </c>
       <c r="R94" t="n">
-        <v>6784576</v>
+        <v>6784648</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10669,7 +10664,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10679,7 +10674,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10706,50 +10701,52 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128404859</v>
+        <v>128410027</v>
       </c>
       <c r="B95" t="n">
-        <v>8450</v>
+        <v>91472</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>426869</v>
+        <v>427093</v>
       </c>
       <c r="R95" t="n">
-        <v>6784461</v>
+        <v>6784727</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10781,7 +10778,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10791,7 +10788,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10800,6 +10797,7 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10818,52 +10816,50 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128410027</v>
+        <v>128404859</v>
       </c>
       <c r="B96" t="n">
-        <v>91472</v>
+        <v>8450</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>427093</v>
+        <v>426869</v>
       </c>
       <c r="R96" t="n">
-        <v>6784727</v>
+        <v>6784461</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10895,7 +10891,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10905,7 +10901,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10914,7 +10910,6 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -10933,45 +10928,50 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128410456</v>
+        <v>128410598</v>
       </c>
       <c r="B97" t="n">
-        <v>79083</v>
+        <v>8450</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>426882</v>
+        <v>426922</v>
       </c>
       <c r="R97" t="n">
-        <v>6784648</v>
+        <v>6784576</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11003,7 +11003,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11013,7 +11013,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11040,45 +11040,50 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128410868</v>
+        <v>128405638</v>
       </c>
       <c r="B98" t="n">
-        <v>79083</v>
+        <v>8450</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>426916</v>
+        <v>427026</v>
       </c>
       <c r="R98" t="n">
-        <v>6784534</v>
+        <v>6784560</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11110,7 +11115,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11120,7 +11125,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11147,50 +11152,45 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128405638</v>
+        <v>128410868</v>
       </c>
       <c r="B99" t="n">
-        <v>8450</v>
+        <v>79083</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>427026</v>
+        <v>426916</v>
       </c>
       <c r="R99" t="n">
-        <v>6784560</v>
+        <v>6784534</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11222,7 +11222,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11232,7 +11232,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11259,45 +11259,50 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128411027</v>
+        <v>128410908</v>
       </c>
       <c r="B100" t="n">
-        <v>79083</v>
+        <v>8450</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>426858</v>
+        <v>426908</v>
       </c>
       <c r="R100" t="n">
-        <v>6784514</v>
+        <v>6784511</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11329,7 +11334,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11339,7 +11344,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11366,50 +11371,45 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128410908</v>
+        <v>128411027</v>
       </c>
       <c r="B101" t="n">
-        <v>8450</v>
+        <v>79083</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>426908</v>
+        <v>426858</v>
       </c>
       <c r="R101" t="n">
-        <v>6784511</v>
+        <v>6784514</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11441,7 +11441,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11451,7 +11451,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD101" t="b">

--- a/artfynd/A 36371-2025 artfynd.xlsx
+++ b/artfynd/A 36371-2025 artfynd.xlsx
@@ -3875,10 +3875,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128418215</v>
+        <v>128414306</v>
       </c>
       <c r="B32" t="n">
-        <v>78841</v>
+        <v>57682</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3886,34 +3886,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>426655</v>
+        <v>426519</v>
       </c>
       <c r="R32" t="n">
-        <v>6784360</v>
+        <v>6784286</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3945,7 +3950,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3955,7 +3960,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3982,50 +3987,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128413945</v>
+        <v>128418215</v>
       </c>
       <c r="B33" t="n">
-        <v>8450</v>
+        <v>78841</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>426498</v>
+        <v>426655</v>
       </c>
       <c r="R33" t="n">
-        <v>6784322</v>
+        <v>6784360</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4057,7 +4057,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4094,38 +4094,38 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128414306</v>
+        <v>128413945</v>
       </c>
       <c r="B34" t="n">
-        <v>57682</v>
+        <v>8450</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>426519</v>
+        <v>426498</v>
       </c>
       <c r="R34" t="n">
-        <v>6784286</v>
+        <v>6784322</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -6896,45 +6896,50 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128416385</v>
+        <v>128404480</v>
       </c>
       <c r="B60" t="n">
-        <v>79702</v>
+        <v>8450</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>426796</v>
+        <v>426773</v>
       </c>
       <c r="R60" t="n">
-        <v>6784156</v>
+        <v>6784434</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6966,7 +6971,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6976,7 +6981,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7003,50 +7008,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128404480</v>
+        <v>128416385</v>
       </c>
       <c r="B61" t="n">
-        <v>8450</v>
+        <v>79702</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>426773</v>
+        <v>426796</v>
       </c>
       <c r="R61" t="n">
-        <v>6784434</v>
+        <v>6784156</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7078,7 +7078,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7088,7 +7088,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7222,10 +7222,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128414095</v>
+        <v>128412109</v>
       </c>
       <c r="B63" t="n">
-        <v>78841</v>
+        <v>79083</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7233,21 +7233,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7257,10 +7257,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>426556</v>
+        <v>426646</v>
       </c>
       <c r="R63" t="n">
-        <v>6784312</v>
+        <v>6784678</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7292,7 +7292,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7302,7 +7302,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7329,10 +7329,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128412109</v>
+        <v>128414095</v>
       </c>
       <c r="B64" t="n">
-        <v>79083</v>
+        <v>78841</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7340,21 +7340,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7364,10 +7364,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>426646</v>
+        <v>426556</v>
       </c>
       <c r="R64" t="n">
-        <v>6784678</v>
+        <v>6784312</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7399,7 +7399,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7409,7 +7409,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8317,45 +8317,50 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128413213</v>
+        <v>128414247</v>
       </c>
       <c r="B73" t="n">
-        <v>78841</v>
+        <v>8450</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>426524</v>
+        <v>426535</v>
       </c>
       <c r="R73" t="n">
-        <v>6784388</v>
+        <v>6784292</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8387,7 +8392,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8397,7 +8402,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8424,50 +8429,45 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128414247</v>
+        <v>128413213</v>
       </c>
       <c r="B74" t="n">
-        <v>8450</v>
+        <v>78841</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>426535</v>
+        <v>426524</v>
       </c>
       <c r="R74" t="n">
-        <v>6784292</v>
+        <v>6784388</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8499,7 +8499,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8509,7 +8509,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8633,45 +8633,50 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128410669</v>
+        <v>128409845</v>
       </c>
       <c r="B76" t="n">
-        <v>79083</v>
+        <v>8450</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>426922</v>
+        <v>427064</v>
       </c>
       <c r="R76" t="n">
-        <v>6784529</v>
+        <v>6784664</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8703,7 +8708,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8713,7 +8718,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8740,50 +8745,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128409845</v>
+        <v>128410669</v>
       </c>
       <c r="B77" t="n">
-        <v>8450</v>
+        <v>79083</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>427064</v>
+        <v>426922</v>
       </c>
       <c r="R77" t="n">
-        <v>6784664</v>
+        <v>6784529</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8815,7 +8815,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8825,7 +8825,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8852,35 +8852,40 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128408858</v>
+        <v>128408778</v>
       </c>
       <c r="B78" t="n">
-        <v>79083</v>
+        <v>8450</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
@@ -8922,7 +8927,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8932,7 +8937,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8959,7 +8964,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128416919</v>
+        <v>128406731</v>
       </c>
       <c r="B79" t="n">
         <v>8450</v>
@@ -8999,10 +9004,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>426842</v>
+        <v>427073</v>
       </c>
       <c r="R79" t="n">
-        <v>6784214</v>
+        <v>6784548</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9034,7 +9039,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9044,7 +9049,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9071,40 +9076,35 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128408778</v>
+        <v>128408858</v>
       </c>
       <c r="B80" t="n">
-        <v>8450</v>
+        <v>79083</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
@@ -9146,7 +9146,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9156,7 +9156,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9183,38 +9183,38 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128406731</v>
+        <v>128410625</v>
       </c>
       <c r="B81" t="n">
-        <v>8450</v>
+        <v>57682</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -9223,13 +9223,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>427073</v>
+        <v>426917</v>
       </c>
       <c r="R81" t="n">
-        <v>6784548</v>
+        <v>6784579</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9258,7 +9258,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9268,7 +9268,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9295,38 +9295,38 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128410625</v>
+        <v>128416919</v>
       </c>
       <c r="B82" t="n">
-        <v>57682</v>
+        <v>8450</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="M82" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -9335,13 +9335,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>426917</v>
+        <v>426842</v>
       </c>
       <c r="R82" t="n">
-        <v>6784579</v>
+        <v>6784214</v>
       </c>
       <c r="S82" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9370,7 +9370,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9380,7 +9380,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10487,10 +10487,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128406985</v>
+        <v>128410027</v>
       </c>
       <c r="B93" t="n">
-        <v>78840</v>
+        <v>91472</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10498,34 +10498,41 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6446</v>
+        <v>5442</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>427087</v>
+        <v>427093</v>
       </c>
       <c r="R93" t="n">
-        <v>6784548</v>
+        <v>6784727</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10557,7 +10564,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10567,7 +10574,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10576,6 +10583,7 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -10594,45 +10602,50 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128410456</v>
+        <v>128404859</v>
       </c>
       <c r="B94" t="n">
-        <v>79083</v>
+        <v>8450</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>426882</v>
+        <v>426869</v>
       </c>
       <c r="R94" t="n">
-        <v>6784648</v>
+        <v>6784461</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10664,7 +10677,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10674,7 +10687,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10701,52 +10714,50 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128410027</v>
+        <v>128410598</v>
       </c>
       <c r="B95" t="n">
-        <v>91472</v>
+        <v>8450</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>427093</v>
+        <v>426922</v>
       </c>
       <c r="R95" t="n">
-        <v>6784727</v>
+        <v>6784576</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10778,7 +10789,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10788,7 +10799,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10797,7 +10808,6 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10816,50 +10826,45 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128404859</v>
+        <v>128406985</v>
       </c>
       <c r="B96" t="n">
-        <v>8450</v>
+        <v>78840</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>426869</v>
+        <v>427087</v>
       </c>
       <c r="R96" t="n">
-        <v>6784461</v>
+        <v>6784548</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10891,7 +10896,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10901,7 +10906,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10928,50 +10933,45 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128410598</v>
+        <v>128410456</v>
       </c>
       <c r="B97" t="n">
-        <v>8450</v>
+        <v>79083</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>426922</v>
+        <v>426882</v>
       </c>
       <c r="R97" t="n">
-        <v>6784576</v>
+        <v>6784648</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11003,7 +11003,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11013,7 +11013,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11906,10 +11906,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128416606</v>
+        <v>128407848</v>
       </c>
       <c r="B106" t="n">
-        <v>78840</v>
+        <v>78841</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11917,21 +11917,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11941,10 +11941,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>426859</v>
+        <v>427064</v>
       </c>
       <c r="R106" t="n">
-        <v>6784153</v>
+        <v>6784585</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11976,7 +11976,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11986,7 +11986,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12013,10 +12013,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128407848</v>
+        <v>128416606</v>
       </c>
       <c r="B107" t="n">
-        <v>78841</v>
+        <v>78840</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12024,21 +12024,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12048,10 +12048,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>427064</v>
+        <v>426859</v>
       </c>
       <c r="R107" t="n">
-        <v>6784585</v>
+        <v>6784153</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12083,7 +12083,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12093,7 +12093,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD107" t="b">

--- a/artfynd/A 36371-2025 artfynd.xlsx
+++ b/artfynd/A 36371-2025 artfynd.xlsx
@@ -6896,50 +6896,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128404480</v>
+        <v>128416385</v>
       </c>
       <c r="B60" t="n">
-        <v>8450</v>
+        <v>79702</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>426773</v>
+        <v>426796</v>
       </c>
       <c r="R60" t="n">
-        <v>6784434</v>
+        <v>6784156</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6971,7 +6966,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6981,7 +6976,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7008,45 +7003,50 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128416385</v>
+        <v>128404480</v>
       </c>
       <c r="B61" t="n">
-        <v>79702</v>
+        <v>8450</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>426796</v>
+        <v>426773</v>
       </c>
       <c r="R61" t="n">
-        <v>6784156</v>
+        <v>6784434</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7078,7 +7078,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7088,7 +7088,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8852,40 +8852,35 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128408778</v>
+        <v>128408858</v>
       </c>
       <c r="B78" t="n">
-        <v>8450</v>
+        <v>79083</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
@@ -8927,7 +8922,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8937,7 +8932,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8964,38 +8959,38 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128406731</v>
+        <v>128410625</v>
       </c>
       <c r="B79" t="n">
-        <v>8450</v>
+        <v>57682</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="M79" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -9004,13 +8999,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>427073</v>
+        <v>426917</v>
       </c>
       <c r="R79" t="n">
-        <v>6784548</v>
+        <v>6784579</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9039,7 +9034,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9049,7 +9044,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9076,45 +9071,50 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128408858</v>
+        <v>128416919</v>
       </c>
       <c r="B80" t="n">
-        <v>79083</v>
+        <v>8450</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>427123</v>
+        <v>426842</v>
       </c>
       <c r="R80" t="n">
-        <v>6784697</v>
+        <v>6784214</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9146,7 +9146,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9156,7 +9156,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9183,38 +9183,38 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128410625</v>
+        <v>128408778</v>
       </c>
       <c r="B81" t="n">
-        <v>57682</v>
+        <v>8450</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -9223,13 +9223,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>426917</v>
+        <v>427123</v>
       </c>
       <c r="R81" t="n">
-        <v>6784579</v>
+        <v>6784697</v>
       </c>
       <c r="S81" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9258,7 +9258,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9268,7 +9268,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9295,7 +9295,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128416919</v>
+        <v>128406731</v>
       </c>
       <c r="B82" t="n">
         <v>8450</v>
@@ -9335,10 +9335,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>426842</v>
+        <v>427073</v>
       </c>
       <c r="R82" t="n">
-        <v>6784214</v>
+        <v>6784548</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9370,7 +9370,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9380,7 +9380,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9407,10 +9407,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128404878</v>
+        <v>128409945</v>
       </c>
       <c r="B83" t="n">
-        <v>57682</v>
+        <v>78841</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9418,39 +9418,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>426879</v>
+        <v>427084</v>
       </c>
       <c r="R83" t="n">
-        <v>6784490</v>
+        <v>6784718</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9482,7 +9477,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9492,7 +9487,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9519,10 +9514,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128409945</v>
+        <v>128404878</v>
       </c>
       <c r="B84" t="n">
-        <v>78841</v>
+        <v>57682</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9530,34 +9525,39 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>427084</v>
+        <v>426879</v>
       </c>
       <c r="R84" t="n">
-        <v>6784718</v>
+        <v>6784490</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9589,7 +9589,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9599,7 +9599,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10268,10 +10268,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128417068</v>
+        <v>128423249</v>
       </c>
       <c r="B91" t="n">
-        <v>79083</v>
+        <v>57682</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10279,37 +10279,42 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+          <t>Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>426830</v>
+        <v>427097</v>
       </c>
       <c r="R91" t="n">
-        <v>6784251</v>
+        <v>6784657</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10338,7 +10343,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10348,7 +10353,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10375,10 +10380,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128423249</v>
+        <v>128417068</v>
       </c>
       <c r="B92" t="n">
-        <v>57682</v>
+        <v>79083</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10386,42 +10391,37 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Fisklöstjärnen, Dlr</t>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>427097</v>
+        <v>426830</v>
       </c>
       <c r="R92" t="n">
-        <v>6784657</v>
+        <v>6784251</v>
       </c>
       <c r="S92" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10460,7 +10460,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10487,10 +10487,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128410027</v>
+        <v>128406985</v>
       </c>
       <c r="B93" t="n">
-        <v>91472</v>
+        <v>78840</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10498,41 +10498,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>5442</v>
+        <v>6446</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>427093</v>
+        <v>427087</v>
       </c>
       <c r="R93" t="n">
-        <v>6784727</v>
+        <v>6784548</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10564,7 +10557,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10574,7 +10567,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10583,7 +10576,6 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -10602,50 +10594,45 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128404859</v>
+        <v>128410456</v>
       </c>
       <c r="B94" t="n">
-        <v>8450</v>
+        <v>79083</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>426869</v>
+        <v>426882</v>
       </c>
       <c r="R94" t="n">
-        <v>6784461</v>
+        <v>6784648</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10677,7 +10664,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10687,7 +10674,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10714,50 +10701,52 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128410598</v>
+        <v>128410027</v>
       </c>
       <c r="B95" t="n">
-        <v>8450</v>
+        <v>91472</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>426922</v>
+        <v>427093</v>
       </c>
       <c r="R95" t="n">
-        <v>6784576</v>
+        <v>6784727</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10789,7 +10778,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10799,7 +10788,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10808,6 +10797,7 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10826,45 +10816,50 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128406985</v>
+        <v>128404859</v>
       </c>
       <c r="B96" t="n">
-        <v>78840</v>
+        <v>8450</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>427087</v>
+        <v>426869</v>
       </c>
       <c r="R96" t="n">
-        <v>6784548</v>
+        <v>6784461</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10896,7 +10891,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10906,7 +10901,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10933,45 +10928,50 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128410456</v>
+        <v>128410598</v>
       </c>
       <c r="B97" t="n">
-        <v>79083</v>
+        <v>8450</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>426882</v>
+        <v>426922</v>
       </c>
       <c r="R97" t="n">
-        <v>6784648</v>
+        <v>6784576</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11003,7 +11003,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11013,7 +11013,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD97" t="b">

--- a/artfynd/A 36371-2025 artfynd.xlsx
+++ b/artfynd/A 36371-2025 artfynd.xlsx
@@ -2693,10 +2693,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128415595</v>
+        <v>128411184</v>
       </c>
       <c r="B21" t="n">
-        <v>79083</v>
+        <v>78845</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2704,34 +2704,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>426618</v>
+        <v>426819</v>
       </c>
       <c r="R21" t="n">
-        <v>6784050</v>
+        <v>6784515</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2763,7 +2763,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2773,7 +2773,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2800,10 +2800,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128415015</v>
+        <v>128415595</v>
       </c>
       <c r="B22" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2835,10 +2835,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>426548</v>
+        <v>426618</v>
       </c>
       <c r="R22" t="n">
-        <v>6784175</v>
+        <v>6784050</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2870,7 +2870,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2880,7 +2880,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2907,10 +2907,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128414172</v>
+        <v>128415015</v>
       </c>
       <c r="B23" t="n">
-        <v>78840</v>
+        <v>79087</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2918,21 +2918,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2942,10 +2942,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>426541</v>
+        <v>426548</v>
       </c>
       <c r="R23" t="n">
-        <v>6784302</v>
+        <v>6784175</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2977,7 +2977,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2987,7 +2987,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3014,10 +3014,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128418402</v>
+        <v>128414172</v>
       </c>
       <c r="B24" t="n">
-        <v>78840</v>
+        <v>78844</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3049,10 +3049,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>426596</v>
+        <v>426541</v>
       </c>
       <c r="R24" t="n">
-        <v>6784364</v>
+        <v>6784302</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3121,10 +3121,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128414481</v>
+        <v>128418402</v>
       </c>
       <c r="B25" t="n">
-        <v>79702</v>
+        <v>78844</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3132,21 +3132,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3156,10 +3156,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>426524</v>
+        <v>426596</v>
       </c>
       <c r="R25" t="n">
-        <v>6784260</v>
+        <v>6784364</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3191,7 +3191,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3201,7 +3201,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3228,10 +3228,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128411184</v>
+        <v>128414481</v>
       </c>
       <c r="B26" t="n">
-        <v>78841</v>
+        <v>79706</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3239,34 +3239,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>426819</v>
+        <v>426524</v>
       </c>
       <c r="R26" t="n">
-        <v>6784515</v>
+        <v>6784260</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3298,7 +3298,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3308,7 +3308,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3335,10 +3335,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128414801</v>
+        <v>128417228</v>
       </c>
       <c r="B27" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3366,14 +3366,14 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>426524</v>
+        <v>426801</v>
       </c>
       <c r="R27" t="n">
-        <v>6784260</v>
+        <v>6784284</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3405,7 +3405,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3415,7 +3415,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3442,10 +3442,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128416106</v>
+        <v>128414801</v>
       </c>
       <c r="B28" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3473,14 +3473,14 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>426746</v>
+        <v>426524</v>
       </c>
       <c r="R28" t="n">
-        <v>6784096</v>
+        <v>6784260</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3512,7 +3512,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3522,12 +3522,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:35</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50 meter.</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3554,10 +3549,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128417228</v>
+        <v>128416106</v>
       </c>
       <c r="B29" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3589,10 +3584,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>426801</v>
+        <v>426746</v>
       </c>
       <c r="R29" t="n">
-        <v>6784284</v>
+        <v>6784096</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3624,7 +3619,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3634,7 +3629,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50 meter.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3664,7 +3664,7 @@
         <v>128414155</v>
       </c>
       <c r="B30" t="n">
-        <v>78841</v>
+        <v>78845</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3771,7 +3771,7 @@
         <v>128413169</v>
       </c>
       <c r="B31" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3875,38 +3875,38 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128414306</v>
+        <v>128413945</v>
       </c>
       <c r="B32" t="n">
-        <v>57682</v>
+        <v>8450</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -3915,10 +3915,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>426519</v>
+        <v>426498</v>
       </c>
       <c r="R32" t="n">
-        <v>6784286</v>
+        <v>6784322</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3950,7 +3950,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3990,7 +3990,7 @@
         <v>128418215</v>
       </c>
       <c r="B33" t="n">
-        <v>78841</v>
+        <v>78845</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4094,38 +4094,38 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128413945</v>
+        <v>128414306</v>
       </c>
       <c r="B34" t="n">
-        <v>8450</v>
+        <v>57686</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>426498</v>
+        <v>426519</v>
       </c>
       <c r="R34" t="n">
-        <v>6784322</v>
+        <v>6784286</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4209,7 +4209,7 @@
         <v>128416349</v>
       </c>
       <c r="B35" t="n">
-        <v>78840</v>
+        <v>78844</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4316,7 +4316,7 @@
         <v>128404649</v>
       </c>
       <c r="B36" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4420,10 +4420,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128414383</v>
+        <v>128412524</v>
       </c>
       <c r="B37" t="n">
-        <v>78841</v>
+        <v>79087</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4431,21 +4431,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4455,10 +4455,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>426509</v>
+        <v>426466</v>
       </c>
       <c r="R37" t="n">
-        <v>6784270</v>
+        <v>6784510</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4490,7 +4490,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4527,50 +4527,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128404418</v>
+        <v>128414383</v>
       </c>
       <c r="B38" t="n">
-        <v>8450</v>
+        <v>78845</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>426715</v>
+        <v>426509</v>
       </c>
       <c r="R38" t="n">
-        <v>6784397</v>
+        <v>6784270</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4602,7 +4597,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4612,7 +4607,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4639,45 +4634,50 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128412524</v>
+        <v>128404418</v>
       </c>
       <c r="B39" t="n">
-        <v>79083</v>
+        <v>8450</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>426466</v>
+        <v>426715</v>
       </c>
       <c r="R39" t="n">
-        <v>6784510</v>
+        <v>6784397</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4709,7 +4709,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4719,7 +4719,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4746,10 +4746,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128418704</v>
+        <v>128418198</v>
       </c>
       <c r="B40" t="n">
-        <v>78840</v>
+        <v>79087</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4757,21 +4757,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4781,7 +4781,7 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>426573</v>
+        <v>426656</v>
       </c>
       <c r="R40" t="n">
         <v>6784360</v>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4853,10 +4853,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128418719</v>
+        <v>128415503</v>
       </c>
       <c r="B41" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4888,10 +4888,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>426571</v>
+        <v>426605</v>
       </c>
       <c r="R41" t="n">
-        <v>6784357</v>
+        <v>6784090</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4933,7 +4933,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4960,10 +4960,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128418198</v>
+        <v>128413197</v>
       </c>
       <c r="B42" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4995,10 +4995,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>426656</v>
+        <v>426532</v>
       </c>
       <c r="R42" t="n">
-        <v>6784360</v>
+        <v>6784390</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5030,7 +5030,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5040,7 +5040,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5067,10 +5067,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128413197</v>
+        <v>128418704</v>
       </c>
       <c r="B43" t="n">
-        <v>79083</v>
+        <v>78844</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5078,21 +5078,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5102,10 +5102,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>426532</v>
+        <v>426573</v>
       </c>
       <c r="R43" t="n">
-        <v>6784390</v>
+        <v>6784360</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5137,7 +5137,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5147,7 +5147,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5174,10 +5174,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128415503</v>
+        <v>128418719</v>
       </c>
       <c r="B44" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5209,10 +5209,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>426605</v>
+        <v>426571</v>
       </c>
       <c r="R44" t="n">
-        <v>6784090</v>
+        <v>6784357</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5244,7 +5244,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5254,7 +5254,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5284,7 +5284,7 @@
         <v>128417709</v>
       </c>
       <c r="B45" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5391,7 +5391,7 @@
         <v>128413145</v>
       </c>
       <c r="B46" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5498,7 +5498,7 @@
         <v>128416206</v>
       </c>
       <c r="B47" t="n">
-        <v>78840</v>
+        <v>78844</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5605,7 +5605,7 @@
         <v>128412596</v>
       </c>
       <c r="B48" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5712,7 +5712,7 @@
         <v>128416262</v>
       </c>
       <c r="B49" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5819,7 +5819,7 @@
         <v>128417096</v>
       </c>
       <c r="B50" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5926,7 +5926,7 @@
         <v>128415549</v>
       </c>
       <c r="B51" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6030,7 +6030,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128414874</v>
+        <v>128415767</v>
       </c>
       <c r="B52" t="n">
         <v>8450</v>
@@ -6061,7 +6061,7 @@
       <c r="I52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -6070,10 +6070,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>426535</v>
+        <v>426618</v>
       </c>
       <c r="R52" t="n">
-        <v>6784210</v>
+        <v>6784050</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6105,7 +6105,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6115,7 +6115,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6142,7 +6142,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128415767</v>
+        <v>128414874</v>
       </c>
       <c r="B53" t="n">
         <v>8450</v>
@@ -6173,7 +6173,7 @@
       <c r="I53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6182,10 +6182,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>426618</v>
+        <v>426535</v>
       </c>
       <c r="R53" t="n">
-        <v>6784050</v>
+        <v>6784210</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6217,7 +6217,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6227,7 +6227,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6257,7 +6257,7 @@
         <v>128418647</v>
       </c>
       <c r="B54" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6364,7 +6364,7 @@
         <v>128413992</v>
       </c>
       <c r="B55" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6471,7 +6471,7 @@
         <v>128415267</v>
       </c>
       <c r="B56" t="n">
-        <v>78841</v>
+        <v>78845</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6575,10 +6575,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128417675</v>
+        <v>128415393</v>
       </c>
       <c r="B57" t="n">
-        <v>79083</v>
+        <v>79706</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6586,34 +6586,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>426764</v>
+        <v>426601</v>
       </c>
       <c r="R57" t="n">
-        <v>6784308</v>
+        <v>6784100</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6645,7 +6645,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6655,7 +6655,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6682,10 +6682,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128415393</v>
+        <v>128418258</v>
       </c>
       <c r="B58" t="n">
-        <v>79702</v>
+        <v>79087</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6693,21 +6693,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6717,10 +6717,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>426601</v>
+        <v>426632</v>
       </c>
       <c r="R58" t="n">
-        <v>6784100</v>
+        <v>6784364</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6752,7 +6752,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6762,7 +6762,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6789,10 +6789,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128418258</v>
+        <v>128417675</v>
       </c>
       <c r="B59" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6820,14 +6820,14 @@
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>426632</v>
+        <v>426764</v>
       </c>
       <c r="R59" t="n">
-        <v>6784364</v>
+        <v>6784308</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6859,7 +6859,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6869,7 +6869,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6899,7 +6899,7 @@
         <v>128416385</v>
       </c>
       <c r="B60" t="n">
-        <v>79702</v>
+        <v>79706</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7118,7 +7118,7 @@
         <v>128414843</v>
       </c>
       <c r="B62" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7225,7 +7225,7 @@
         <v>128412109</v>
       </c>
       <c r="B63" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7332,7 +7332,7 @@
         <v>128414095</v>
       </c>
       <c r="B64" t="n">
-        <v>78841</v>
+        <v>78845</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7663,7 +7663,7 @@
         <v>128413310</v>
       </c>
       <c r="B67" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7772,50 +7772,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128417436</v>
+        <v>128413333</v>
       </c>
       <c r="B68" t="n">
-        <v>8450</v>
+        <v>78844</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>426801</v>
+        <v>426459</v>
       </c>
       <c r="R68" t="n">
-        <v>6784284</v>
+        <v>6784412</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7847,7 +7842,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7857,7 +7852,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7884,45 +7879,50 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128413333</v>
+        <v>128417436</v>
       </c>
       <c r="B69" t="n">
-        <v>78840</v>
+        <v>8450</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>426459</v>
+        <v>426801</v>
       </c>
       <c r="R69" t="n">
-        <v>6784412</v>
+        <v>6784284</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7954,7 +7954,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7964,7 +7964,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7994,7 +7994,7 @@
         <v>128417205</v>
       </c>
       <c r="B70" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8101,7 +8101,7 @@
         <v>128418292</v>
       </c>
       <c r="B71" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         <v>128415978</v>
       </c>
       <c r="B72" t="n">
-        <v>78840</v>
+        <v>78844</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8432,7 +8432,7 @@
         <v>128413213</v>
       </c>
       <c r="B74" t="n">
-        <v>78841</v>
+        <v>78845</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8633,50 +8633,45 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128409845</v>
+        <v>128410669</v>
       </c>
       <c r="B76" t="n">
-        <v>8450</v>
+        <v>79087</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>427064</v>
+        <v>426922</v>
       </c>
       <c r="R76" t="n">
-        <v>6784664</v>
+        <v>6784529</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8708,7 +8703,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8718,7 +8713,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8745,45 +8740,50 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128410669</v>
+        <v>128409845</v>
       </c>
       <c r="B77" t="n">
-        <v>79083</v>
+        <v>8450</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>426922</v>
+        <v>427064</v>
       </c>
       <c r="R77" t="n">
-        <v>6784529</v>
+        <v>6784664</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8815,7 +8815,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8825,7 +8825,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8855,7 +8855,7 @@
         <v>128408858</v>
       </c>
       <c r="B78" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8959,38 +8959,38 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128410625</v>
+        <v>128406731</v>
       </c>
       <c r="B79" t="n">
-        <v>57682</v>
+        <v>8450</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="M79" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -8999,13 +8999,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>426917</v>
+        <v>427073</v>
       </c>
       <c r="R79" t="n">
-        <v>6784579</v>
+        <v>6784548</v>
       </c>
       <c r="S79" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9034,7 +9034,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9044,7 +9044,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9295,38 +9295,38 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128406731</v>
+        <v>128410625</v>
       </c>
       <c r="B82" t="n">
-        <v>8450</v>
+        <v>57686</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="M82" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -9335,13 +9335,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>427073</v>
+        <v>426917</v>
       </c>
       <c r="R82" t="n">
-        <v>6784548</v>
+        <v>6784579</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9370,7 +9370,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9380,7 +9380,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9410,7 +9410,7 @@
         <v>128409945</v>
       </c>
       <c r="B83" t="n">
-        <v>78841</v>
+        <v>78845</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9517,7 +9517,7 @@
         <v>128404878</v>
       </c>
       <c r="B84" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9629,7 +9629,7 @@
         <v>128407168</v>
       </c>
       <c r="B85" t="n">
-        <v>78841</v>
+        <v>78845</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9736,7 +9736,7 @@
         <v>128416596</v>
       </c>
       <c r="B86" t="n">
-        <v>79702</v>
+        <v>79706</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9843,7 +9843,7 @@
         <v>128406999</v>
       </c>
       <c r="B87" t="n">
-        <v>78841</v>
+        <v>78845</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9950,7 +9950,7 @@
         <v>128416502</v>
       </c>
       <c r="B88" t="n">
-        <v>78841</v>
+        <v>78845</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10057,7 +10057,7 @@
         <v>128416791</v>
       </c>
       <c r="B89" t="n">
-        <v>78841</v>
+        <v>78845</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10164,7 +10164,7 @@
         <v>128417147</v>
       </c>
       <c r="B90" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10268,10 +10268,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128423249</v>
+        <v>128417068</v>
       </c>
       <c r="B91" t="n">
-        <v>57682</v>
+        <v>79087</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10279,42 +10279,37 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Fisklöstjärnen, Dlr</t>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>427097</v>
+        <v>426830</v>
       </c>
       <c r="R91" t="n">
-        <v>6784657</v>
+        <v>6784251</v>
       </c>
       <c r="S91" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10343,7 +10338,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10353,7 +10348,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10380,10 +10375,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128417068</v>
+        <v>128423249</v>
       </c>
       <c r="B92" t="n">
-        <v>79083</v>
+        <v>57686</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10391,37 +10386,42 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+          <t>Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>426830</v>
+        <v>427097</v>
       </c>
       <c r="R92" t="n">
-        <v>6784251</v>
+        <v>6784657</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10460,7 +10460,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10487,10 +10487,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128406985</v>
+        <v>128410027</v>
       </c>
       <c r="B93" t="n">
-        <v>78840</v>
+        <v>91484</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10498,34 +10498,41 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6446</v>
+        <v>5442</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>427087</v>
+        <v>427093</v>
       </c>
       <c r="R93" t="n">
-        <v>6784548</v>
+        <v>6784727</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10557,7 +10564,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10567,7 +10574,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10576,6 +10583,7 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -10597,7 +10605,7 @@
         <v>128410456</v>
       </c>
       <c r="B94" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10701,10 +10709,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128410027</v>
+        <v>128406985</v>
       </c>
       <c r="B95" t="n">
-        <v>91472</v>
+        <v>78844</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10712,41 +10720,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5442</v>
+        <v>6446</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>427093</v>
+        <v>427087</v>
       </c>
       <c r="R95" t="n">
-        <v>6784727</v>
+        <v>6784548</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10778,7 +10779,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10788,7 +10789,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10797,7 +10798,6 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10816,7 +10816,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128404859</v>
+        <v>128410598</v>
       </c>
       <c r="B96" t="n">
         <v>8450</v>
@@ -10856,10 +10856,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>426869</v>
+        <v>426922</v>
       </c>
       <c r="R96" t="n">
-        <v>6784461</v>
+        <v>6784576</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10891,7 +10891,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10901,7 +10901,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10928,7 +10928,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128410598</v>
+        <v>128404859</v>
       </c>
       <c r="B97" t="n">
         <v>8450</v>
@@ -10968,10 +10968,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>426922</v>
+        <v>426869</v>
       </c>
       <c r="R97" t="n">
-        <v>6784576</v>
+        <v>6784461</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11003,7 +11003,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11013,7 +11013,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11040,50 +11040,45 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128405638</v>
+        <v>128410868</v>
       </c>
       <c r="B98" t="n">
-        <v>8450</v>
+        <v>79087</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>427026</v>
+        <v>426916</v>
       </c>
       <c r="R98" t="n">
-        <v>6784560</v>
+        <v>6784534</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11115,7 +11110,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11125,7 +11120,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11152,45 +11147,50 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128410868</v>
+        <v>128405638</v>
       </c>
       <c r="B99" t="n">
-        <v>79083</v>
+        <v>8450</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>426916</v>
+        <v>427026</v>
       </c>
       <c r="R99" t="n">
-        <v>6784534</v>
+        <v>6784560</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11222,7 +11222,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11232,7 +11232,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11259,50 +11259,45 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128410908</v>
+        <v>128411027</v>
       </c>
       <c r="B100" t="n">
-        <v>8450</v>
+        <v>79087</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>426908</v>
+        <v>426858</v>
       </c>
       <c r="R100" t="n">
-        <v>6784511</v>
+        <v>6784514</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11334,7 +11329,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11344,7 +11339,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11371,45 +11366,50 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128411027</v>
+        <v>128410908</v>
       </c>
       <c r="B101" t="n">
-        <v>79083</v>
+        <v>8450</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>426858</v>
+        <v>426908</v>
       </c>
       <c r="R101" t="n">
-        <v>6784514</v>
+        <v>6784511</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11441,7 +11441,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11451,7 +11451,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11478,10 +11478,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128416713</v>
+        <v>128408932</v>
       </c>
       <c r="B102" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11513,10 +11513,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>426849</v>
+        <v>427081</v>
       </c>
       <c r="R102" t="n">
-        <v>6784145</v>
+        <v>6784657</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11548,7 +11548,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11558,7 +11558,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11585,10 +11585,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128408932</v>
+        <v>128416713</v>
       </c>
       <c r="B103" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11620,10 +11620,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>427081</v>
+        <v>426849</v>
       </c>
       <c r="R103" t="n">
-        <v>6784657</v>
+        <v>6784145</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11655,7 +11655,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11665,7 +11665,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11692,10 +11692,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128409925</v>
+        <v>128407898</v>
       </c>
       <c r="B104" t="n">
-        <v>79673</v>
+        <v>78844</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11703,21 +11703,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11727,10 +11727,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>427082</v>
+        <v>427062</v>
       </c>
       <c r="R104" t="n">
-        <v>6784715</v>
+        <v>6784591</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11762,7 +11762,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11772,7 +11772,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11799,10 +11799,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128407898</v>
+        <v>128409925</v>
       </c>
       <c r="B105" t="n">
-        <v>78840</v>
+        <v>79677</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11810,21 +11810,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11834,10 +11834,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>427062</v>
+        <v>427082</v>
       </c>
       <c r="R105" t="n">
-        <v>6784591</v>
+        <v>6784715</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11869,7 +11869,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11879,7 +11879,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11909,7 +11909,7 @@
         <v>128407848</v>
       </c>
       <c r="B106" t="n">
-        <v>78841</v>
+        <v>78845</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12016,7 +12016,7 @@
         <v>128416606</v>
       </c>
       <c r="B107" t="n">
-        <v>78840</v>
+        <v>78844</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>

--- a/artfynd/A 36371-2025 artfynd.xlsx
+++ b/artfynd/A 36371-2025 artfynd.xlsx
@@ -2693,10 +2693,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128411184</v>
+        <v>128415595</v>
       </c>
       <c r="B21" t="n">
-        <v>78845</v>
+        <v>79087</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2704,34 +2704,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>426819</v>
+        <v>426618</v>
       </c>
       <c r="R21" t="n">
-        <v>6784515</v>
+        <v>6784050</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2763,7 +2763,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2773,7 +2773,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2800,7 +2800,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128415595</v>
+        <v>128415015</v>
       </c>
       <c r="B22" t="n">
         <v>79087</v>
@@ -2835,10 +2835,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>426618</v>
+        <v>426548</v>
       </c>
       <c r="R22" t="n">
-        <v>6784050</v>
+        <v>6784175</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2870,7 +2870,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2880,7 +2880,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2907,10 +2907,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128415015</v>
+        <v>128414172</v>
       </c>
       <c r="B23" t="n">
-        <v>79087</v>
+        <v>78844</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2918,21 +2918,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2942,10 +2942,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>426548</v>
+        <v>426541</v>
       </c>
       <c r="R23" t="n">
-        <v>6784175</v>
+        <v>6784302</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2977,7 +2977,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2987,7 +2987,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3014,7 +3014,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128414172</v>
+        <v>128418402</v>
       </c>
       <c r="B24" t="n">
         <v>78844</v>
@@ -3049,10 +3049,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>426541</v>
+        <v>426596</v>
       </c>
       <c r="R24" t="n">
-        <v>6784302</v>
+        <v>6784364</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3121,10 +3121,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128418402</v>
+        <v>128414481</v>
       </c>
       <c r="B25" t="n">
-        <v>78844</v>
+        <v>79706</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3132,21 +3132,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3156,10 +3156,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>426596</v>
+        <v>426524</v>
       </c>
       <c r="R25" t="n">
-        <v>6784364</v>
+        <v>6784260</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3191,7 +3191,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3201,7 +3201,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3228,10 +3228,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128414481</v>
+        <v>128411184</v>
       </c>
       <c r="B26" t="n">
-        <v>79706</v>
+        <v>78845</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3239,34 +3239,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>426524</v>
+        <v>426819</v>
       </c>
       <c r="R26" t="n">
-        <v>6784260</v>
+        <v>6784515</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3298,7 +3298,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3308,7 +3308,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3768,10 +3768,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128413169</v>
+        <v>128418215</v>
       </c>
       <c r="B31" t="n">
-        <v>79087</v>
+        <v>78845</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3779,21 +3779,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3803,10 +3803,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>426555</v>
+        <v>426655</v>
       </c>
       <c r="R31" t="n">
-        <v>6784393</v>
+        <v>6784360</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3875,38 +3875,38 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128413945</v>
+        <v>128414306</v>
       </c>
       <c r="B32" t="n">
-        <v>8450</v>
+        <v>57686</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -3915,10 +3915,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>426498</v>
+        <v>426519</v>
       </c>
       <c r="R32" t="n">
-        <v>6784322</v>
+        <v>6784286</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3950,7 +3950,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3987,10 +3987,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128418215</v>
+        <v>128413169</v>
       </c>
       <c r="B33" t="n">
-        <v>78845</v>
+        <v>79087</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3998,21 +3998,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4022,10 +4022,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>426655</v>
+        <v>426555</v>
       </c>
       <c r="R33" t="n">
-        <v>6784360</v>
+        <v>6784393</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4057,7 +4057,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4094,38 +4094,38 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128414306</v>
+        <v>128413945</v>
       </c>
       <c r="B34" t="n">
-        <v>57686</v>
+        <v>8450</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>426519</v>
+        <v>426498</v>
       </c>
       <c r="R34" t="n">
-        <v>6784286</v>
+        <v>6784322</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4853,7 +4853,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128415503</v>
+        <v>128413197</v>
       </c>
       <c r="B41" t="n">
         <v>79087</v>
@@ -4888,10 +4888,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>426605</v>
+        <v>426532</v>
       </c>
       <c r="R41" t="n">
-        <v>6784090</v>
+        <v>6784390</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4933,7 +4933,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4960,7 +4960,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128413197</v>
+        <v>128415503</v>
       </c>
       <c r="B42" t="n">
         <v>79087</v>
@@ -4995,10 +4995,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>426532</v>
+        <v>426605</v>
       </c>
       <c r="R42" t="n">
-        <v>6784390</v>
+        <v>6784090</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5030,7 +5030,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5040,7 +5040,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -8959,38 +8959,38 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128406731</v>
+        <v>128410625</v>
       </c>
       <c r="B79" t="n">
-        <v>8450</v>
+        <v>57686</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="M79" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -8999,13 +8999,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>427073</v>
+        <v>426917</v>
       </c>
       <c r="R79" t="n">
-        <v>6784548</v>
+        <v>6784579</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9034,7 +9034,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9044,7 +9044,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9071,7 +9071,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128416919</v>
+        <v>128406731</v>
       </c>
       <c r="B80" t="n">
         <v>8450</v>
@@ -9111,10 +9111,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>426842</v>
+        <v>427073</v>
       </c>
       <c r="R80" t="n">
-        <v>6784214</v>
+        <v>6784548</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9146,7 +9146,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9156,7 +9156,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9183,7 +9183,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128408778</v>
+        <v>128416919</v>
       </c>
       <c r="B81" t="n">
         <v>8450</v>
@@ -9214,7 +9214,7 @@
       <c r="I81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -9223,10 +9223,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>427123</v>
+        <v>426842</v>
       </c>
       <c r="R81" t="n">
-        <v>6784697</v>
+        <v>6784214</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9258,7 +9258,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9268,7 +9268,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9295,38 +9295,38 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128410625</v>
+        <v>128408778</v>
       </c>
       <c r="B82" t="n">
-        <v>57686</v>
+        <v>8450</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="M82" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -9335,13 +9335,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>426917</v>
+        <v>427123</v>
       </c>
       <c r="R82" t="n">
-        <v>6784579</v>
+        <v>6784697</v>
       </c>
       <c r="S82" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9370,7 +9370,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9380,7 +9380,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9407,10 +9407,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128409945</v>
+        <v>128404878</v>
       </c>
       <c r="B83" t="n">
-        <v>78845</v>
+        <v>57686</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9418,34 +9418,39 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>427084</v>
+        <v>426879</v>
       </c>
       <c r="R83" t="n">
-        <v>6784718</v>
+        <v>6784490</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9477,7 +9482,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9487,7 +9492,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9514,10 +9519,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128404878</v>
+        <v>128409945</v>
       </c>
       <c r="B84" t="n">
-        <v>57686</v>
+        <v>78845</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9525,39 +9530,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>426879</v>
+        <v>427084</v>
       </c>
       <c r="R84" t="n">
-        <v>6784490</v>
+        <v>6784718</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9589,7 +9589,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9599,7 +9599,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11906,10 +11906,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128407848</v>
+        <v>128416606</v>
       </c>
       <c r="B106" t="n">
-        <v>78845</v>
+        <v>78844</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11917,21 +11917,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11941,10 +11941,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>427064</v>
+        <v>426859</v>
       </c>
       <c r="R106" t="n">
-        <v>6784585</v>
+        <v>6784153</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11976,7 +11976,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11986,7 +11986,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12013,10 +12013,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128416606</v>
+        <v>128407848</v>
       </c>
       <c r="B107" t="n">
-        <v>78844</v>
+        <v>78845</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12024,21 +12024,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12048,10 +12048,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>426859</v>
+        <v>427064</v>
       </c>
       <c r="R107" t="n">
-        <v>6784153</v>
+        <v>6784585</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12083,7 +12083,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12093,7 +12093,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD107" t="b">

--- a/artfynd/A 36371-2025 artfynd.xlsx
+++ b/artfynd/A 36371-2025 artfynd.xlsx
@@ -2696,7 +2696,7 @@
         <v>128415595</v>
       </c>
       <c r="B21" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         <v>128415015</v>
       </c>
       <c r="B22" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2910,7 +2910,7 @@
         <v>128414172</v>
       </c>
       <c r="B23" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         <v>128418402</v>
       </c>
       <c r="B24" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         <v>128414481</v>
       </c>
       <c r="B25" t="n">
-        <v>79706</v>
+        <v>79708</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3231,7 +3231,7 @@
         <v>128411184</v>
       </c>
       <c r="B26" t="n">
-        <v>78845</v>
+        <v>78847</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3338,7 +3338,7 @@
         <v>128417228</v>
       </c>
       <c r="B27" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
         <v>128414801</v>
       </c>
       <c r="B28" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3552,7 +3552,7 @@
         <v>128416106</v>
       </c>
       <c r="B29" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3664,7 +3664,7 @@
         <v>128414155</v>
       </c>
       <c r="B30" t="n">
-        <v>78845</v>
+        <v>78847</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3768,10 +3768,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128418215</v>
+        <v>128414306</v>
       </c>
       <c r="B31" t="n">
-        <v>78845</v>
+        <v>57686</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3779,34 +3779,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>426655</v>
+        <v>426519</v>
       </c>
       <c r="R31" t="n">
-        <v>6784360</v>
+        <v>6784286</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3838,7 +3843,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3848,7 +3853,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3875,10 +3880,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128414306</v>
+        <v>128413169</v>
       </c>
       <c r="B32" t="n">
-        <v>57686</v>
+        <v>79089</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3886,39 +3891,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>426519</v>
+        <v>426555</v>
       </c>
       <c r="R32" t="n">
-        <v>6784286</v>
+        <v>6784393</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3950,7 +3950,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3987,45 +3987,50 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128413169</v>
+        <v>128413945</v>
       </c>
       <c r="B33" t="n">
-        <v>79087</v>
+        <v>8450</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>426555</v>
+        <v>426498</v>
       </c>
       <c r="R33" t="n">
-        <v>6784393</v>
+        <v>6784322</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4057,7 +4062,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4067,7 +4072,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4094,50 +4099,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128413945</v>
+        <v>128418215</v>
       </c>
       <c r="B34" t="n">
-        <v>8450</v>
+        <v>78847</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>426498</v>
+        <v>426655</v>
       </c>
       <c r="R34" t="n">
-        <v>6784322</v>
+        <v>6784360</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4206,10 +4206,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128416349</v>
+        <v>128404649</v>
       </c>
       <c r="B35" t="n">
-        <v>78844</v>
+        <v>79089</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4217,21 +4217,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4244,7 +4244,7 @@
         <v>426792</v>
       </c>
       <c r="R35" t="n">
-        <v>6784152</v>
+        <v>6784434</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4286,7 +4286,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4313,10 +4313,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128404649</v>
+        <v>128416349</v>
       </c>
       <c r="B36" t="n">
-        <v>79087</v>
+        <v>78846</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4324,21 +4324,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4351,7 +4351,7 @@
         <v>426792</v>
       </c>
       <c r="R36" t="n">
-        <v>6784434</v>
+        <v>6784152</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4383,7 +4383,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4393,7 +4393,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4420,45 +4420,50 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128412524</v>
+        <v>128404418</v>
       </c>
       <c r="B37" t="n">
-        <v>79087</v>
+        <v>8450</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>426466</v>
+        <v>426715</v>
       </c>
       <c r="R37" t="n">
-        <v>6784510</v>
+        <v>6784397</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4490,7 +4495,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4500,7 +4505,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4527,10 +4532,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128414383</v>
+        <v>128412524</v>
       </c>
       <c r="B38" t="n">
-        <v>78845</v>
+        <v>79089</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4538,21 +4543,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4562,10 +4567,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>426509</v>
+        <v>426466</v>
       </c>
       <c r="R38" t="n">
-        <v>6784270</v>
+        <v>6784510</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4597,7 +4602,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4607,7 +4612,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4634,50 +4639,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128404418</v>
+        <v>128414383</v>
       </c>
       <c r="B39" t="n">
-        <v>8450</v>
+        <v>78847</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>426715</v>
+        <v>426509</v>
       </c>
       <c r="R39" t="n">
-        <v>6784397</v>
+        <v>6784270</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4709,7 +4709,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4719,7 +4719,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4746,10 +4746,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128418198</v>
+        <v>128418719</v>
       </c>
       <c r="B40" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4781,10 +4781,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>426656</v>
+        <v>426571</v>
       </c>
       <c r="R40" t="n">
-        <v>6784360</v>
+        <v>6784357</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4856,7 +4856,7 @@
         <v>128413197</v>
       </c>
       <c r="B41" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4963,7 +4963,7 @@
         <v>128415503</v>
       </c>
       <c r="B42" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5067,10 +5067,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128418704</v>
+        <v>128417709</v>
       </c>
       <c r="B43" t="n">
-        <v>78844</v>
+        <v>79089</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5078,34 +5078,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>426573</v>
+        <v>426717</v>
       </c>
       <c r="R43" t="n">
-        <v>6784360</v>
+        <v>6784350</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5137,7 +5137,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5147,7 +5147,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5174,10 +5174,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128418719</v>
+        <v>128418704</v>
       </c>
       <c r="B44" t="n">
-        <v>79087</v>
+        <v>78846</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5185,21 +5185,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5209,10 +5209,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>426571</v>
+        <v>426573</v>
       </c>
       <c r="R44" t="n">
-        <v>6784357</v>
+        <v>6784360</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5244,7 +5244,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5254,7 +5254,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5281,10 +5281,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128417709</v>
+        <v>128418198</v>
       </c>
       <c r="B45" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5312,14 +5312,14 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>426717</v>
+        <v>426656</v>
       </c>
       <c r="R45" t="n">
-        <v>6784350</v>
+        <v>6784360</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5351,7 +5351,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5391,7 +5391,7 @@
         <v>128413145</v>
       </c>
       <c r="B46" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5498,7 +5498,7 @@
         <v>128416206</v>
       </c>
       <c r="B47" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5605,7 +5605,7 @@
         <v>128412596</v>
       </c>
       <c r="B48" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5712,7 +5712,7 @@
         <v>128416262</v>
       </c>
       <c r="B49" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5819,7 +5819,7 @@
         <v>128417096</v>
       </c>
       <c r="B50" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5926,7 +5926,7 @@
         <v>128415549</v>
       </c>
       <c r="B51" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6254,10 +6254,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128418647</v>
+        <v>128415267</v>
       </c>
       <c r="B54" t="n">
-        <v>79087</v>
+        <v>78847</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6265,21 +6265,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6289,10 +6289,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>426573</v>
+        <v>426604</v>
       </c>
       <c r="R54" t="n">
-        <v>6784376</v>
+        <v>6784093</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6324,7 +6324,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>18:59</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>18:59</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6361,10 +6361,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128413992</v>
+        <v>128418647</v>
       </c>
       <c r="B55" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6396,10 +6396,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>426519</v>
+        <v>426573</v>
       </c>
       <c r="R55" t="n">
-        <v>6784308</v>
+        <v>6784376</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>18:59</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6441,7 +6441,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>18:59</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6468,10 +6468,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128415267</v>
+        <v>128413992</v>
       </c>
       <c r="B56" t="n">
-        <v>78845</v>
+        <v>79089</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6479,21 +6479,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6503,10 +6503,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>426604</v>
+        <v>426519</v>
       </c>
       <c r="R56" t="n">
-        <v>6784093</v>
+        <v>6784308</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6538,7 +6538,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6548,7 +6548,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6575,10 +6575,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128415393</v>
+        <v>128417675</v>
       </c>
       <c r="B57" t="n">
-        <v>79706</v>
+        <v>79089</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6586,34 +6586,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>426601</v>
+        <v>426764</v>
       </c>
       <c r="R57" t="n">
-        <v>6784100</v>
+        <v>6784308</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6645,7 +6645,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6655,7 +6655,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6685,7 +6685,7 @@
         <v>128418258</v>
       </c>
       <c r="B58" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6789,10 +6789,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128417675</v>
+        <v>128415393</v>
       </c>
       <c r="B59" t="n">
-        <v>79087</v>
+        <v>79708</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6800,34 +6800,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>426764</v>
+        <v>426601</v>
       </c>
       <c r="R59" t="n">
-        <v>6784308</v>
+        <v>6784100</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6859,7 +6859,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6869,7 +6869,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6896,45 +6896,50 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128416385</v>
+        <v>128404480</v>
       </c>
       <c r="B60" t="n">
-        <v>79706</v>
+        <v>8450</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>426796</v>
+        <v>426773</v>
       </c>
       <c r="R60" t="n">
-        <v>6784156</v>
+        <v>6784434</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6966,7 +6971,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6976,7 +6981,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7003,50 +7008,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128404480</v>
+        <v>128416385</v>
       </c>
       <c r="B61" t="n">
-        <v>8450</v>
+        <v>79708</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>426773</v>
+        <v>426796</v>
       </c>
       <c r="R61" t="n">
-        <v>6784434</v>
+        <v>6784156</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7078,7 +7078,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7088,7 +7088,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7118,7 +7118,7 @@
         <v>128414843</v>
       </c>
       <c r="B62" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7225,7 +7225,7 @@
         <v>128412109</v>
       </c>
       <c r="B63" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7332,7 +7332,7 @@
         <v>128414095</v>
       </c>
       <c r="B64" t="n">
-        <v>78845</v>
+        <v>78847</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7660,10 +7660,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128413310</v>
+        <v>128413333</v>
       </c>
       <c r="B67" t="n">
-        <v>57686</v>
+        <v>78846</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7671,39 +7671,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>426477</v>
+        <v>426459</v>
       </c>
       <c r="R67" t="n">
-        <v>6784397</v>
+        <v>6784412</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7735,7 +7730,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7745,7 +7740,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7772,10 +7767,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128413333</v>
+        <v>128413310</v>
       </c>
       <c r="B68" t="n">
-        <v>78844</v>
+        <v>57686</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7783,34 +7778,39 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>426459</v>
+        <v>426477</v>
       </c>
       <c r="R68" t="n">
-        <v>6784412</v>
+        <v>6784397</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7842,7 +7842,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7852,7 +7852,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7991,10 +7991,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128417205</v>
+        <v>128418292</v>
       </c>
       <c r="B70" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8022,14 +8022,14 @@
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>426813</v>
+        <v>426624</v>
       </c>
       <c r="R70" t="n">
-        <v>6784276</v>
+        <v>6784361</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8061,7 +8061,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8071,7 +8071,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav på tallarna på en radie av 50 meter.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8098,10 +8103,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128418292</v>
+        <v>128417205</v>
       </c>
       <c r="B71" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8129,14 +8134,14 @@
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>426624</v>
+        <v>426813</v>
       </c>
       <c r="R71" t="n">
-        <v>6784361</v>
+        <v>6784276</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8168,7 +8173,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8178,12 +8183,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>18:45</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav på tallarna på en radie av 50 meter.</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8213,7 +8213,7 @@
         <v>128415978</v>
       </c>
       <c r="B72" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8432,7 +8432,7 @@
         <v>128413213</v>
       </c>
       <c r="B74" t="n">
-        <v>78845</v>
+        <v>78847</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8636,7 +8636,7 @@
         <v>128410669</v>
       </c>
       <c r="B76" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8852,10 +8852,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128408858</v>
+        <v>128410625</v>
       </c>
       <c r="B78" t="n">
-        <v>79087</v>
+        <v>57686</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8863,37 +8863,42 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>427123</v>
+        <v>426917</v>
       </c>
       <c r="R78" t="n">
-        <v>6784697</v>
+        <v>6784579</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8922,7 +8927,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8932,7 +8937,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8959,10 +8964,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128410625</v>
+        <v>128408858</v>
       </c>
       <c r="B79" t="n">
-        <v>57686</v>
+        <v>79089</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8970,42 +8975,37 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>426917</v>
+        <v>427123</v>
       </c>
       <c r="R79" t="n">
-        <v>6784579</v>
+        <v>6784697</v>
       </c>
       <c r="S79" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9034,7 +9034,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9044,7 +9044,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9522,7 +9522,7 @@
         <v>128409945</v>
       </c>
       <c r="B84" t="n">
-        <v>78845</v>
+        <v>78847</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9629,7 +9629,7 @@
         <v>128407168</v>
       </c>
       <c r="B85" t="n">
-        <v>78845</v>
+        <v>78847</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9736,7 +9736,7 @@
         <v>128416596</v>
       </c>
       <c r="B86" t="n">
-        <v>79706</v>
+        <v>79708</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9840,10 +9840,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128406999</v>
+        <v>128416502</v>
       </c>
       <c r="B87" t="n">
-        <v>78845</v>
+        <v>78847</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9875,10 +9875,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>427083</v>
+        <v>426841</v>
       </c>
       <c r="R87" t="n">
-        <v>6784551</v>
+        <v>6784169</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9910,7 +9910,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9920,7 +9920,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9947,10 +9947,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128416502</v>
+        <v>128406999</v>
       </c>
       <c r="B88" t="n">
-        <v>78845</v>
+        <v>78847</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9982,10 +9982,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>426841</v>
+        <v>427083</v>
       </c>
       <c r="R88" t="n">
-        <v>6784169</v>
+        <v>6784551</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10017,7 +10017,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10027,7 +10027,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10057,7 +10057,7 @@
         <v>128416791</v>
       </c>
       <c r="B89" t="n">
-        <v>78845</v>
+        <v>78847</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10164,7 +10164,7 @@
         <v>128417147</v>
       </c>
       <c r="B90" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10268,10 +10268,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128417068</v>
+        <v>128423249</v>
       </c>
       <c r="B91" t="n">
-        <v>79087</v>
+        <v>57686</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10279,37 +10279,42 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+          <t>Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>426830</v>
+        <v>427097</v>
       </c>
       <c r="R91" t="n">
-        <v>6784251</v>
+        <v>6784657</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10338,7 +10343,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10348,7 +10353,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10375,10 +10380,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128423249</v>
+        <v>128417068</v>
       </c>
       <c r="B92" t="n">
-        <v>57686</v>
+        <v>79089</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10386,42 +10391,37 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Fisklöstjärnen, Dlr</t>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>427097</v>
+        <v>426830</v>
       </c>
       <c r="R92" t="n">
-        <v>6784657</v>
+        <v>6784251</v>
       </c>
       <c r="S92" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10460,7 +10460,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10487,52 +10487,50 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128410027</v>
+        <v>128404859</v>
       </c>
       <c r="B93" t="n">
-        <v>91484</v>
+        <v>8450</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>427093</v>
+        <v>426869</v>
       </c>
       <c r="R93" t="n">
-        <v>6784727</v>
+        <v>6784461</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10564,7 +10562,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10574,7 +10572,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10583,7 +10581,6 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -10602,10 +10599,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128410456</v>
+        <v>128410027</v>
       </c>
       <c r="B94" t="n">
-        <v>79087</v>
+        <v>91486</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10613,34 +10610,41 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>426882</v>
+        <v>427093</v>
       </c>
       <c r="R94" t="n">
-        <v>6784648</v>
+        <v>6784727</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10672,7 +10676,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10682,7 +10686,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10691,6 +10695,7 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -10709,10 +10714,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128406985</v>
+        <v>128410456</v>
       </c>
       <c r="B95" t="n">
-        <v>78844</v>
+        <v>79089</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10720,21 +10725,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10744,10 +10749,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>427087</v>
+        <v>426882</v>
       </c>
       <c r="R95" t="n">
-        <v>6784548</v>
+        <v>6784648</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10779,7 +10784,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10789,7 +10794,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10816,50 +10821,45 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128410598</v>
+        <v>128406985</v>
       </c>
       <c r="B96" t="n">
-        <v>8450</v>
+        <v>78846</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>426922</v>
+        <v>427087</v>
       </c>
       <c r="R96" t="n">
-        <v>6784576</v>
+        <v>6784548</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10891,7 +10891,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10901,7 +10901,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10928,7 +10928,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128404859</v>
+        <v>128410598</v>
       </c>
       <c r="B97" t="n">
         <v>8450</v>
@@ -10968,10 +10968,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>426869</v>
+        <v>426922</v>
       </c>
       <c r="R97" t="n">
-        <v>6784461</v>
+        <v>6784576</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11003,7 +11003,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11013,7 +11013,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11043,7 +11043,7 @@
         <v>128410868</v>
       </c>
       <c r="B98" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11262,7 +11262,7 @@
         <v>128411027</v>
       </c>
       <c r="B100" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11478,10 +11478,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128408932</v>
+        <v>128416713</v>
       </c>
       <c r="B102" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11513,10 +11513,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>427081</v>
+        <v>426849</v>
       </c>
       <c r="R102" t="n">
-        <v>6784657</v>
+        <v>6784145</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11548,7 +11548,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11558,7 +11558,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11585,10 +11585,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128416713</v>
+        <v>128408932</v>
       </c>
       <c r="B103" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11620,10 +11620,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>426849</v>
+        <v>427081</v>
       </c>
       <c r="R103" t="n">
-        <v>6784145</v>
+        <v>6784657</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11655,7 +11655,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11665,7 +11665,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11692,10 +11692,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128407898</v>
+        <v>128409925</v>
       </c>
       <c r="B104" t="n">
-        <v>78844</v>
+        <v>79679</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11703,21 +11703,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11727,10 +11727,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>427062</v>
+        <v>427082</v>
       </c>
       <c r="R104" t="n">
-        <v>6784591</v>
+        <v>6784715</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11762,7 +11762,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11772,7 +11772,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11799,10 +11799,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128409925</v>
+        <v>128407898</v>
       </c>
       <c r="B105" t="n">
-        <v>79677</v>
+        <v>78846</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11810,21 +11810,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11834,10 +11834,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>427082</v>
+        <v>427062</v>
       </c>
       <c r="R105" t="n">
-        <v>6784715</v>
+        <v>6784591</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11869,7 +11869,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11879,7 +11879,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11909,7 +11909,7 @@
         <v>128416606</v>
       </c>
       <c r="B106" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12016,7 +12016,7 @@
         <v>128407848</v>
       </c>
       <c r="B107" t="n">
-        <v>78845</v>
+        <v>78847</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>

--- a/artfynd/A 36371-2025 artfynd.xlsx
+++ b/artfynd/A 36371-2025 artfynd.xlsx
@@ -2693,7 +2693,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128415595</v>
+        <v>128415015</v>
       </c>
       <c r="B21" t="n">
         <v>79089</v>
@@ -2728,10 +2728,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>426618</v>
+        <v>426548</v>
       </c>
       <c r="R21" t="n">
-        <v>6784050</v>
+        <v>6784175</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2763,7 +2763,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2773,7 +2773,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2800,10 +2800,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128415015</v>
+        <v>128414172</v>
       </c>
       <c r="B22" t="n">
-        <v>79089</v>
+        <v>78846</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2811,21 +2811,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2835,10 +2835,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>426548</v>
+        <v>426541</v>
       </c>
       <c r="R22" t="n">
-        <v>6784175</v>
+        <v>6784302</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2870,7 +2870,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2880,7 +2880,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2907,7 +2907,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128414172</v>
+        <v>128418402</v>
       </c>
       <c r="B23" t="n">
         <v>78846</v>
@@ -2942,10 +2942,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>426541</v>
+        <v>426596</v>
       </c>
       <c r="R23" t="n">
-        <v>6784302</v>
+        <v>6784364</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2977,7 +2977,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2987,7 +2987,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3014,10 +3014,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128418402</v>
+        <v>128414481</v>
       </c>
       <c r="B24" t="n">
-        <v>78846</v>
+        <v>79708</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3025,21 +3025,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3049,10 +3049,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>426596</v>
+        <v>426524</v>
       </c>
       <c r="R24" t="n">
-        <v>6784364</v>
+        <v>6784260</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3121,10 +3121,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128414481</v>
+        <v>128411184</v>
       </c>
       <c r="B25" t="n">
-        <v>79708</v>
+        <v>78847</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3132,34 +3132,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>426524</v>
+        <v>426819</v>
       </c>
       <c r="R25" t="n">
-        <v>6784260</v>
+        <v>6784515</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3191,7 +3191,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3201,7 +3201,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3228,10 +3228,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128411184</v>
+        <v>128415595</v>
       </c>
       <c r="B26" t="n">
-        <v>78847</v>
+        <v>79089</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3239,34 +3239,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>426819</v>
+        <v>426618</v>
       </c>
       <c r="R26" t="n">
-        <v>6784515</v>
+        <v>6784050</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3298,7 +3298,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3308,7 +3308,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3335,10 +3335,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128417228</v>
+        <v>128414155</v>
       </c>
       <c r="B27" t="n">
-        <v>79089</v>
+        <v>78847</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3346,34 +3346,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>426801</v>
+        <v>426540</v>
       </c>
       <c r="R27" t="n">
-        <v>6784284</v>
+        <v>6784305</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3405,7 +3405,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3415,7 +3415,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3442,7 +3442,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128414801</v>
+        <v>128416106</v>
       </c>
       <c r="B28" t="n">
         <v>79089</v>
@@ -3473,14 +3473,14 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>426524</v>
+        <v>426746</v>
       </c>
       <c r="R28" t="n">
-        <v>6784260</v>
+        <v>6784096</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3512,7 +3512,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3522,7 +3522,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50 meter.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3549,7 +3554,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128416106</v>
+        <v>128414801</v>
       </c>
       <c r="B29" t="n">
         <v>79089</v>
@@ -3580,14 +3585,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>426746</v>
+        <v>426524</v>
       </c>
       <c r="R29" t="n">
-        <v>6784096</v>
+        <v>6784260</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3619,7 +3624,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3629,12 +3634,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:35</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50 meter.</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3661,10 +3661,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128414155</v>
+        <v>128417228</v>
       </c>
       <c r="B30" t="n">
-        <v>78847</v>
+        <v>79089</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3672,34 +3672,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>426540</v>
+        <v>426801</v>
       </c>
       <c r="R30" t="n">
-        <v>6784305</v>
+        <v>6784284</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3731,7 +3731,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3768,10 +3768,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128414306</v>
+        <v>128413169</v>
       </c>
       <c r="B31" t="n">
-        <v>57686</v>
+        <v>79089</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3779,39 +3779,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>426519</v>
+        <v>426555</v>
       </c>
       <c r="R31" t="n">
-        <v>6784286</v>
+        <v>6784393</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3843,7 +3838,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3853,7 +3848,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3880,10 +3875,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128413169</v>
+        <v>128414306</v>
       </c>
       <c r="B32" t="n">
-        <v>79089</v>
+        <v>57686</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3891,34 +3886,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>426555</v>
+        <v>426519</v>
       </c>
       <c r="R32" t="n">
-        <v>6784393</v>
+        <v>6784286</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3950,7 +3950,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4420,50 +4420,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128404418</v>
+        <v>128412524</v>
       </c>
       <c r="B37" t="n">
-        <v>8450</v>
+        <v>79089</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>426715</v>
+        <v>426466</v>
       </c>
       <c r="R37" t="n">
-        <v>6784397</v>
+        <v>6784510</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4495,7 +4490,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4505,7 +4500,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4532,45 +4527,50 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128412524</v>
+        <v>128404418</v>
       </c>
       <c r="B38" t="n">
-        <v>79089</v>
+        <v>8450</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>426466</v>
+        <v>426715</v>
       </c>
       <c r="R38" t="n">
-        <v>6784510</v>
+        <v>6784397</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4602,7 +4602,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4612,7 +4612,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4746,7 +4746,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128418719</v>
+        <v>128413197</v>
       </c>
       <c r="B40" t="n">
         <v>79089</v>
@@ -4781,10 +4781,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>426571</v>
+        <v>426532</v>
       </c>
       <c r="R40" t="n">
-        <v>6784357</v>
+        <v>6784390</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4853,7 +4853,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128413197</v>
+        <v>128415503</v>
       </c>
       <c r="B41" t="n">
         <v>79089</v>
@@ -4888,10 +4888,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>426532</v>
+        <v>426605</v>
       </c>
       <c r="R41" t="n">
-        <v>6784390</v>
+        <v>6784090</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4933,7 +4933,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4960,7 +4960,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128415503</v>
+        <v>128417709</v>
       </c>
       <c r="B42" t="n">
         <v>79089</v>
@@ -4991,14 +4991,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>426605</v>
+        <v>426717</v>
       </c>
       <c r="R42" t="n">
-        <v>6784090</v>
+        <v>6784350</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5030,7 +5030,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5040,7 +5040,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5067,7 +5067,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128417709</v>
+        <v>128418719</v>
       </c>
       <c r="B43" t="n">
         <v>79089</v>
@@ -5098,14 +5098,14 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>426717</v>
+        <v>426571</v>
       </c>
       <c r="R43" t="n">
-        <v>6784350</v>
+        <v>6784357</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5137,7 +5137,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5147,7 +5147,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5709,45 +5709,50 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128416262</v>
+        <v>128415767</v>
       </c>
       <c r="B49" t="n">
-        <v>79089</v>
+        <v>8450</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>426784</v>
+        <v>426618</v>
       </c>
       <c r="R49" t="n">
-        <v>6784159</v>
+        <v>6784050</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5779,7 +5784,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5789,7 +5794,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5816,45 +5821,50 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128417096</v>
+        <v>128414874</v>
       </c>
       <c r="B50" t="n">
-        <v>79089</v>
+        <v>8450</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>426812</v>
+        <v>426535</v>
       </c>
       <c r="R50" t="n">
-        <v>6784257</v>
+        <v>6784210</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5886,7 +5896,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5896,7 +5906,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5923,7 +5933,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128415549</v>
+        <v>128416262</v>
       </c>
       <c r="B51" t="n">
         <v>79089</v>
@@ -5954,14 +5964,14 @@
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>426615</v>
+        <v>426784</v>
       </c>
       <c r="R51" t="n">
-        <v>6784068</v>
+        <v>6784159</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5993,7 +6003,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6003,7 +6013,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6030,50 +6040,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128415767</v>
+        <v>128417096</v>
       </c>
       <c r="B52" t="n">
-        <v>8450</v>
+        <v>79089</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>426618</v>
+        <v>426812</v>
       </c>
       <c r="R52" t="n">
-        <v>6784050</v>
+        <v>6784257</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6105,7 +6110,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6115,7 +6120,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6142,50 +6147,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128414874</v>
+        <v>128415549</v>
       </c>
       <c r="B53" t="n">
-        <v>8450</v>
+        <v>79089</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>426535</v>
+        <v>426615</v>
       </c>
       <c r="R53" t="n">
-        <v>6784210</v>
+        <v>6784068</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6217,7 +6217,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6227,7 +6227,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6254,10 +6254,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128415267</v>
+        <v>128418647</v>
       </c>
       <c r="B54" t="n">
-        <v>78847</v>
+        <v>79089</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6265,21 +6265,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6289,10 +6289,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>426604</v>
+        <v>426573</v>
       </c>
       <c r="R54" t="n">
-        <v>6784093</v>
+        <v>6784376</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6324,7 +6324,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>18:59</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>18:59</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6361,7 +6361,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128418647</v>
+        <v>128413992</v>
       </c>
       <c r="B55" t="n">
         <v>79089</v>
@@ -6396,10 +6396,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>426573</v>
+        <v>426519</v>
       </c>
       <c r="R55" t="n">
-        <v>6784376</v>
+        <v>6784308</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>18:59</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6441,7 +6441,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>18:59</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6468,10 +6468,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128413992</v>
+        <v>128415267</v>
       </c>
       <c r="B56" t="n">
-        <v>79089</v>
+        <v>78847</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6479,21 +6479,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6503,10 +6503,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>426519</v>
+        <v>426604</v>
       </c>
       <c r="R56" t="n">
-        <v>6784308</v>
+        <v>6784093</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6538,7 +6538,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6548,7 +6548,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6682,10 +6682,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128418258</v>
+        <v>128415393</v>
       </c>
       <c r="B58" t="n">
-        <v>79089</v>
+        <v>79708</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6693,21 +6693,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6717,10 +6717,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>426632</v>
+        <v>426601</v>
       </c>
       <c r="R58" t="n">
-        <v>6784364</v>
+        <v>6784100</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6752,7 +6752,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6762,7 +6762,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6789,10 +6789,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128415393</v>
+        <v>128418258</v>
       </c>
       <c r="B59" t="n">
-        <v>79708</v>
+        <v>79089</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6800,21 +6800,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6824,10 +6824,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>426601</v>
+        <v>426632</v>
       </c>
       <c r="R59" t="n">
-        <v>6784100</v>
+        <v>6784364</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6859,7 +6859,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6869,7 +6869,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7222,10 +7222,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128412109</v>
+        <v>128414095</v>
       </c>
       <c r="B63" t="n">
-        <v>79089</v>
+        <v>78847</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7233,21 +7233,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7257,10 +7257,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>426646</v>
+        <v>426556</v>
       </c>
       <c r="R63" t="n">
-        <v>6784678</v>
+        <v>6784312</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7292,7 +7292,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7302,7 +7302,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7329,10 +7329,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128414095</v>
+        <v>128412109</v>
       </c>
       <c r="B64" t="n">
-        <v>78847</v>
+        <v>79089</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7340,21 +7340,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7364,10 +7364,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>426556</v>
+        <v>426646</v>
       </c>
       <c r="R64" t="n">
-        <v>6784312</v>
+        <v>6784678</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7399,7 +7399,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7409,7 +7409,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8633,45 +8633,50 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128410669</v>
+        <v>128409845</v>
       </c>
       <c r="B76" t="n">
-        <v>79089</v>
+        <v>8450</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>426922</v>
+        <v>427064</v>
       </c>
       <c r="R76" t="n">
-        <v>6784529</v>
+        <v>6784664</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8703,7 +8708,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8713,7 +8718,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8740,50 +8745,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128409845</v>
+        <v>128410669</v>
       </c>
       <c r="B77" t="n">
-        <v>8450</v>
+        <v>79089</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>427064</v>
+        <v>426922</v>
       </c>
       <c r="R77" t="n">
-        <v>6784664</v>
+        <v>6784529</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8815,7 +8815,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8825,7 +8825,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8852,10 +8852,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128410625</v>
+        <v>128408858</v>
       </c>
       <c r="B78" t="n">
-        <v>57686</v>
+        <v>79089</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8863,42 +8863,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>426917</v>
+        <v>427123</v>
       </c>
       <c r="R78" t="n">
-        <v>6784579</v>
+        <v>6784697</v>
       </c>
       <c r="S78" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8927,7 +8922,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8937,7 +8932,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8964,10 +8959,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128408858</v>
+        <v>128410625</v>
       </c>
       <c r="B79" t="n">
-        <v>79089</v>
+        <v>57686</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8975,37 +8970,42 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>427123</v>
+        <v>426917</v>
       </c>
       <c r="R79" t="n">
-        <v>6784697</v>
+        <v>6784579</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9034,7 +9034,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9044,7 +9044,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9840,7 +9840,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128416502</v>
+        <v>128406999</v>
       </c>
       <c r="B87" t="n">
         <v>78847</v>
@@ -9875,10 +9875,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>426841</v>
+        <v>427083</v>
       </c>
       <c r="R87" t="n">
-        <v>6784169</v>
+        <v>6784551</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9910,7 +9910,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9920,7 +9920,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9947,7 +9947,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128406999</v>
+        <v>128416502</v>
       </c>
       <c r="B88" t="n">
         <v>78847</v>
@@ -9982,10 +9982,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>427083</v>
+        <v>426841</v>
       </c>
       <c r="R88" t="n">
-        <v>6784551</v>
+        <v>6784169</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10017,7 +10017,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10027,7 +10027,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10487,7 +10487,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128404859</v>
+        <v>128410598</v>
       </c>
       <c r="B93" t="n">
         <v>8450</v>
@@ -10527,10 +10527,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>426869</v>
+        <v>426922</v>
       </c>
       <c r="R93" t="n">
-        <v>6784461</v>
+        <v>6784576</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10562,7 +10562,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10572,7 +10572,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10599,52 +10599,50 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128410027</v>
+        <v>128404859</v>
       </c>
       <c r="B94" t="n">
-        <v>91486</v>
+        <v>8450</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>427093</v>
+        <v>426869</v>
       </c>
       <c r="R94" t="n">
-        <v>6784727</v>
+        <v>6784461</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10676,7 +10674,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10686,7 +10684,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10695,7 +10693,6 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -10714,10 +10711,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128410456</v>
+        <v>128410027</v>
       </c>
       <c r="B95" t="n">
-        <v>79089</v>
+        <v>91486</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10725,34 +10722,41 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>426882</v>
+        <v>427093</v>
       </c>
       <c r="R95" t="n">
-        <v>6784648</v>
+        <v>6784727</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10784,7 +10788,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10794,7 +10798,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10803,6 +10807,7 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10821,10 +10826,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128406985</v>
+        <v>128410456</v>
       </c>
       <c r="B96" t="n">
-        <v>78846</v>
+        <v>79089</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10832,21 +10837,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10856,10 +10861,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>427087</v>
+        <v>426882</v>
       </c>
       <c r="R96" t="n">
-        <v>6784548</v>
+        <v>6784648</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10891,7 +10896,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10901,7 +10906,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10928,50 +10933,45 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128410598</v>
+        <v>128406985</v>
       </c>
       <c r="B97" t="n">
-        <v>8450</v>
+        <v>78846</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>426922</v>
+        <v>427087</v>
       </c>
       <c r="R97" t="n">
-        <v>6784576</v>
+        <v>6784548</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11003,7 +11003,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11013,7 +11013,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11040,45 +11040,50 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128410868</v>
+        <v>128405638</v>
       </c>
       <c r="B98" t="n">
-        <v>79089</v>
+        <v>8450</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>426916</v>
+        <v>427026</v>
       </c>
       <c r="R98" t="n">
-        <v>6784534</v>
+        <v>6784560</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11110,7 +11115,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11120,7 +11125,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11147,50 +11152,45 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128405638</v>
+        <v>128410868</v>
       </c>
       <c r="B99" t="n">
-        <v>8450</v>
+        <v>79089</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>427026</v>
+        <v>426916</v>
       </c>
       <c r="R99" t="n">
-        <v>6784560</v>
+        <v>6784534</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11222,7 +11222,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11232,7 +11232,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11478,7 +11478,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128416713</v>
+        <v>128408932</v>
       </c>
       <c r="B102" t="n">
         <v>79089</v>
@@ -11513,10 +11513,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>426849</v>
+        <v>427081</v>
       </c>
       <c r="R102" t="n">
-        <v>6784145</v>
+        <v>6784657</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11548,7 +11548,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11558,7 +11558,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11585,7 +11585,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128408932</v>
+        <v>128416713</v>
       </c>
       <c r="B103" t="n">
         <v>79089</v>
@@ -11620,10 +11620,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>427081</v>
+        <v>426849</v>
       </c>
       <c r="R103" t="n">
-        <v>6784657</v>
+        <v>6784145</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11655,7 +11655,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11665,7 +11665,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11692,10 +11692,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128409925</v>
+        <v>128407898</v>
       </c>
       <c r="B104" t="n">
-        <v>79679</v>
+        <v>78846</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11703,21 +11703,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11727,10 +11727,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>427082</v>
+        <v>427062</v>
       </c>
       <c r="R104" t="n">
-        <v>6784715</v>
+        <v>6784591</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11762,7 +11762,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11772,7 +11772,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11799,10 +11799,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128407898</v>
+        <v>128409925</v>
       </c>
       <c r="B105" t="n">
-        <v>78846</v>
+        <v>79679</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11810,21 +11810,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11834,10 +11834,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>427062</v>
+        <v>427082</v>
       </c>
       <c r="R105" t="n">
-        <v>6784591</v>
+        <v>6784715</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11869,7 +11869,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11879,7 +11879,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11906,10 +11906,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128416606</v>
+        <v>128407848</v>
       </c>
       <c r="B106" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11917,21 +11917,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11941,10 +11941,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>426859</v>
+        <v>427064</v>
       </c>
       <c r="R106" t="n">
-        <v>6784153</v>
+        <v>6784585</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11976,7 +11976,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11986,7 +11986,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12013,10 +12013,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128407848</v>
+        <v>128416606</v>
       </c>
       <c r="B107" t="n">
-        <v>78847</v>
+        <v>78846</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12024,21 +12024,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12048,10 +12048,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>427064</v>
+        <v>426859</v>
       </c>
       <c r="R107" t="n">
-        <v>6784585</v>
+        <v>6784153</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12083,7 +12083,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12093,7 +12093,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD107" t="b">

--- a/artfynd/A 36371-2025 artfynd.xlsx
+++ b/artfynd/A 36371-2025 artfynd.xlsx
@@ -10268,10 +10268,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128423249</v>
+        <v>128417068</v>
       </c>
       <c r="B91" t="n">
-        <v>57686</v>
+        <v>79089</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10279,42 +10279,37 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Fisklöstjärnen, Dlr</t>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>427097</v>
+        <v>426830</v>
       </c>
       <c r="R91" t="n">
-        <v>6784657</v>
+        <v>6784251</v>
       </c>
       <c r="S91" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10343,7 +10338,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10353,7 +10348,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10380,10 +10375,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128417068</v>
+        <v>128423249</v>
       </c>
       <c r="B92" t="n">
-        <v>79089</v>
+        <v>57686</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10391,37 +10386,42 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+          <t>Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>426830</v>
+        <v>427097</v>
       </c>
       <c r="R92" t="n">
-        <v>6784251</v>
+        <v>6784657</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10460,7 +10460,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11692,10 +11692,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128407898</v>
+        <v>128409925</v>
       </c>
       <c r="B104" t="n">
-        <v>78846</v>
+        <v>79679</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11703,21 +11703,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11727,10 +11727,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>427062</v>
+        <v>427082</v>
       </c>
       <c r="R104" t="n">
-        <v>6784591</v>
+        <v>6784715</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11762,7 +11762,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11772,7 +11772,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11799,10 +11799,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128409925</v>
+        <v>128407898</v>
       </c>
       <c r="B105" t="n">
-        <v>79679</v>
+        <v>78846</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11810,21 +11810,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11834,10 +11834,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>427082</v>
+        <v>427062</v>
       </c>
       <c r="R105" t="n">
-        <v>6784715</v>
+        <v>6784591</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11869,7 +11869,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11879,7 +11879,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD105" t="b">

--- a/artfynd/A 36371-2025 artfynd.xlsx
+++ b/artfynd/A 36371-2025 artfynd.xlsx
@@ -2800,10 +2800,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128414172</v>
+        <v>128414481</v>
       </c>
       <c r="B22" t="n">
-        <v>78846</v>
+        <v>79708</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2811,21 +2811,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2835,10 +2835,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>426541</v>
+        <v>426524</v>
       </c>
       <c r="R22" t="n">
-        <v>6784302</v>
+        <v>6784260</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2870,7 +2870,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2880,7 +2880,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2907,7 +2907,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128418402</v>
+        <v>128414172</v>
       </c>
       <c r="B23" t="n">
         <v>78846</v>
@@ -2942,10 +2942,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>426596</v>
+        <v>426541</v>
       </c>
       <c r="R23" t="n">
-        <v>6784364</v>
+        <v>6784302</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2977,7 +2977,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2987,7 +2987,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3014,10 +3014,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128414481</v>
+        <v>128418402</v>
       </c>
       <c r="B24" t="n">
-        <v>79708</v>
+        <v>78846</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3025,21 +3025,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3049,10 +3049,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>426524</v>
+        <v>426596</v>
       </c>
       <c r="R24" t="n">
-        <v>6784260</v>
+        <v>6784364</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3121,10 +3121,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128411184</v>
+        <v>128415595</v>
       </c>
       <c r="B25" t="n">
-        <v>78847</v>
+        <v>79089</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3132,34 +3132,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>426819</v>
+        <v>426618</v>
       </c>
       <c r="R25" t="n">
-        <v>6784515</v>
+        <v>6784050</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3191,7 +3191,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3201,7 +3201,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3228,10 +3228,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128415595</v>
+        <v>128411184</v>
       </c>
       <c r="B26" t="n">
-        <v>79089</v>
+        <v>78847</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3239,34 +3239,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>426618</v>
+        <v>426819</v>
       </c>
       <c r="R26" t="n">
-        <v>6784050</v>
+        <v>6784515</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3298,7 +3298,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3308,7 +3308,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3554,7 +3554,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128414801</v>
+        <v>128417228</v>
       </c>
       <c r="B29" t="n">
         <v>79089</v>
@@ -3585,14 +3585,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>426524</v>
+        <v>426801</v>
       </c>
       <c r="R29" t="n">
-        <v>6784260</v>
+        <v>6784284</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3624,7 +3624,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3634,7 +3634,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3661,7 +3661,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128417228</v>
+        <v>128414801</v>
       </c>
       <c r="B30" t="n">
         <v>79089</v>
@@ -3692,14 +3692,14 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>426801</v>
+        <v>426524</v>
       </c>
       <c r="R30" t="n">
-        <v>6784284</v>
+        <v>6784260</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3731,7 +3731,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3987,50 +3987,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128413945</v>
+        <v>128418215</v>
       </c>
       <c r="B33" t="n">
-        <v>8450</v>
+        <v>78847</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>426498</v>
+        <v>426655</v>
       </c>
       <c r="R33" t="n">
-        <v>6784322</v>
+        <v>6784360</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4062,7 +4057,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4072,7 +4067,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4099,45 +4094,50 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128418215</v>
+        <v>128413945</v>
       </c>
       <c r="B34" t="n">
-        <v>78847</v>
+        <v>8450</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>426655</v>
+        <v>426498</v>
       </c>
       <c r="R34" t="n">
-        <v>6784360</v>
+        <v>6784322</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4206,10 +4206,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128404649</v>
+        <v>128416349</v>
       </c>
       <c r="B35" t="n">
-        <v>79089</v>
+        <v>78846</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4217,21 +4217,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4244,7 +4244,7 @@
         <v>426792</v>
       </c>
       <c r="R35" t="n">
-        <v>6784434</v>
+        <v>6784152</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4286,7 +4286,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4313,10 +4313,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128416349</v>
+        <v>128404649</v>
       </c>
       <c r="B36" t="n">
-        <v>78846</v>
+        <v>79089</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4324,21 +4324,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4351,7 +4351,7 @@
         <v>426792</v>
       </c>
       <c r="R36" t="n">
-        <v>6784152</v>
+        <v>6784434</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4383,7 +4383,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4393,7 +4393,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4527,50 +4527,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128404418</v>
+        <v>128414383</v>
       </c>
       <c r="B38" t="n">
-        <v>8450</v>
+        <v>78847</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>426715</v>
+        <v>426509</v>
       </c>
       <c r="R38" t="n">
-        <v>6784397</v>
+        <v>6784270</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4602,7 +4597,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4612,7 +4607,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4639,45 +4634,50 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128414383</v>
+        <v>128404418</v>
       </c>
       <c r="B39" t="n">
-        <v>78847</v>
+        <v>8450</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>426509</v>
+        <v>426715</v>
       </c>
       <c r="R39" t="n">
-        <v>6784270</v>
+        <v>6784397</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4709,7 +4709,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4719,7 +4719,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4746,7 +4746,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128413197</v>
+        <v>128418198</v>
       </c>
       <c r="B40" t="n">
         <v>79089</v>
@@ -4781,10 +4781,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>426532</v>
+        <v>426656</v>
       </c>
       <c r="R40" t="n">
-        <v>6784390</v>
+        <v>6784360</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4853,10 +4853,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128415503</v>
+        <v>128418704</v>
       </c>
       <c r="B41" t="n">
-        <v>79089</v>
+        <v>78846</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4864,21 +4864,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4888,10 +4888,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>426605</v>
+        <v>426573</v>
       </c>
       <c r="R41" t="n">
-        <v>6784090</v>
+        <v>6784360</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4933,7 +4933,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4960,7 +4960,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128417709</v>
+        <v>128413197</v>
       </c>
       <c r="B42" t="n">
         <v>79089</v>
@@ -4991,14 +4991,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>426717</v>
+        <v>426532</v>
       </c>
       <c r="R42" t="n">
-        <v>6784350</v>
+        <v>6784390</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5030,7 +5030,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5040,7 +5040,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5067,7 +5067,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128418719</v>
+        <v>128415503</v>
       </c>
       <c r="B43" t="n">
         <v>79089</v>
@@ -5102,10 +5102,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>426571</v>
+        <v>426605</v>
       </c>
       <c r="R43" t="n">
-        <v>6784357</v>
+        <v>6784090</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5137,7 +5137,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5147,7 +5147,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5174,10 +5174,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128418704</v>
+        <v>128417709</v>
       </c>
       <c r="B44" t="n">
-        <v>78846</v>
+        <v>79089</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5185,34 +5185,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>426573</v>
+        <v>426717</v>
       </c>
       <c r="R44" t="n">
-        <v>6784360</v>
+        <v>6784350</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5244,7 +5244,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5254,7 +5254,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5281,7 +5281,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128418198</v>
+        <v>128418719</v>
       </c>
       <c r="B45" t="n">
         <v>79089</v>
@@ -5316,10 +5316,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>426656</v>
+        <v>426571</v>
       </c>
       <c r="R45" t="n">
-        <v>6784360</v>
+        <v>6784357</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5351,7 +5351,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5388,10 +5388,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128413145</v>
+        <v>128416206</v>
       </c>
       <c r="B46" t="n">
-        <v>79089</v>
+        <v>78846</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5399,34 +5399,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>426534</v>
+        <v>426760</v>
       </c>
       <c r="R46" t="n">
-        <v>6784406</v>
+        <v>6784153</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5458,7 +5458,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5468,7 +5468,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5495,10 +5495,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128416206</v>
+        <v>128413145</v>
       </c>
       <c r="B47" t="n">
-        <v>78846</v>
+        <v>79089</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5506,34 +5506,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>426760</v>
+        <v>426534</v>
       </c>
       <c r="R47" t="n">
-        <v>6784153</v>
+        <v>6784406</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5565,7 +5565,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5575,7 +5575,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5709,50 +5709,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128415767</v>
+        <v>128416262</v>
       </c>
       <c r="B49" t="n">
-        <v>8450</v>
+        <v>79089</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>426618</v>
+        <v>426784</v>
       </c>
       <c r="R49" t="n">
-        <v>6784050</v>
+        <v>6784159</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5784,7 +5779,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5794,7 +5789,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5821,50 +5816,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128414874</v>
+        <v>128417096</v>
       </c>
       <c r="B50" t="n">
-        <v>8450</v>
+        <v>79089</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>426535</v>
+        <v>426812</v>
       </c>
       <c r="R50" t="n">
-        <v>6784210</v>
+        <v>6784257</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5896,7 +5886,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5906,7 +5896,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5933,7 +5923,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128416262</v>
+        <v>128415549</v>
       </c>
       <c r="B51" t="n">
         <v>79089</v>
@@ -5964,14 +5954,14 @@
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>426784</v>
+        <v>426615</v>
       </c>
       <c r="R51" t="n">
-        <v>6784159</v>
+        <v>6784068</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6003,7 +5993,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6013,7 +6003,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6040,45 +6030,50 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128417096</v>
+        <v>128415767</v>
       </c>
       <c r="B52" t="n">
-        <v>79089</v>
+        <v>8450</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>426812</v>
+        <v>426618</v>
       </c>
       <c r="R52" t="n">
-        <v>6784257</v>
+        <v>6784050</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6110,7 +6105,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6120,7 +6115,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6147,45 +6142,50 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128415549</v>
+        <v>128414874</v>
       </c>
       <c r="B53" t="n">
-        <v>79089</v>
+        <v>8450</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>426615</v>
+        <v>426535</v>
       </c>
       <c r="R53" t="n">
-        <v>6784068</v>
+        <v>6784210</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6217,7 +6217,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6227,7 +6227,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6896,50 +6896,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128404480</v>
+        <v>128416385</v>
       </c>
       <c r="B60" t="n">
-        <v>8450</v>
+        <v>79708</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>426773</v>
+        <v>426796</v>
       </c>
       <c r="R60" t="n">
-        <v>6784434</v>
+        <v>6784156</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6971,7 +6966,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6981,7 +6976,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7008,45 +7003,50 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128416385</v>
+        <v>128404480</v>
       </c>
       <c r="B61" t="n">
-        <v>79708</v>
+        <v>8450</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>426796</v>
+        <v>426773</v>
       </c>
       <c r="R61" t="n">
-        <v>6784156</v>
+        <v>6784434</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7078,7 +7078,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7088,7 +7088,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7222,10 +7222,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128414095</v>
+        <v>128412109</v>
       </c>
       <c r="B63" t="n">
-        <v>78847</v>
+        <v>79089</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7233,21 +7233,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7257,10 +7257,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>426556</v>
+        <v>426646</v>
       </c>
       <c r="R63" t="n">
-        <v>6784312</v>
+        <v>6784678</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7292,7 +7292,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7302,7 +7302,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7329,10 +7329,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128412109</v>
+        <v>128414095</v>
       </c>
       <c r="B64" t="n">
-        <v>79089</v>
+        <v>78847</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7340,21 +7340,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7364,10 +7364,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>426646</v>
+        <v>426556</v>
       </c>
       <c r="R64" t="n">
-        <v>6784678</v>
+        <v>6784312</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7399,7 +7399,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7409,7 +7409,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7660,10 +7660,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128413333</v>
+        <v>128413310</v>
       </c>
       <c r="B67" t="n">
-        <v>78846</v>
+        <v>57686</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7671,34 +7671,39 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>426459</v>
+        <v>426477</v>
       </c>
       <c r="R67" t="n">
-        <v>6784412</v>
+        <v>6784397</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7730,7 +7735,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7740,7 +7745,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7767,10 +7772,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128413310</v>
+        <v>128413333</v>
       </c>
       <c r="B68" t="n">
-        <v>57686</v>
+        <v>78846</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7778,39 +7783,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>426477</v>
+        <v>426459</v>
       </c>
       <c r="R68" t="n">
-        <v>6784397</v>
+        <v>6784412</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7842,7 +7842,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7852,7 +7852,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8633,50 +8633,45 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128409845</v>
+        <v>128410669</v>
       </c>
       <c r="B76" t="n">
-        <v>8450</v>
+        <v>79089</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>427064</v>
+        <v>426922</v>
       </c>
       <c r="R76" t="n">
-        <v>6784664</v>
+        <v>6784529</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8708,7 +8703,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8718,7 +8713,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8745,45 +8740,50 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128410669</v>
+        <v>128409845</v>
       </c>
       <c r="B77" t="n">
-        <v>79089</v>
+        <v>8450</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>426922</v>
+        <v>427064</v>
       </c>
       <c r="R77" t="n">
-        <v>6784529</v>
+        <v>6784664</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8815,7 +8815,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8825,7 +8825,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9840,7 +9840,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128406999</v>
+        <v>128416791</v>
       </c>
       <c r="B87" t="n">
         <v>78847</v>
@@ -9875,10 +9875,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>427083</v>
+        <v>426835</v>
       </c>
       <c r="R87" t="n">
-        <v>6784551</v>
+        <v>6784196</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9910,7 +9910,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9920,7 +9920,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9947,7 +9947,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128416502</v>
+        <v>128406999</v>
       </c>
       <c r="B88" t="n">
         <v>78847</v>
@@ -9982,10 +9982,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>426841</v>
+        <v>427083</v>
       </c>
       <c r="R88" t="n">
-        <v>6784169</v>
+        <v>6784551</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10017,7 +10017,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10027,7 +10027,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10054,7 +10054,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128416791</v>
+        <v>128416502</v>
       </c>
       <c r="B89" t="n">
         <v>78847</v>
@@ -10089,10 +10089,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>426835</v>
+        <v>426841</v>
       </c>
       <c r="R89" t="n">
-        <v>6784196</v>
+        <v>6784169</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10124,7 +10124,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10134,7 +10134,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10487,50 +10487,45 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128410598</v>
+        <v>128406985</v>
       </c>
       <c r="B93" t="n">
-        <v>8450</v>
+        <v>78846</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>426922</v>
+        <v>427087</v>
       </c>
       <c r="R93" t="n">
-        <v>6784576</v>
+        <v>6784548</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10562,7 +10557,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10572,7 +10567,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10599,50 +10594,45 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128404859</v>
+        <v>128410456</v>
       </c>
       <c r="B94" t="n">
-        <v>8450</v>
+        <v>79089</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>426869</v>
+        <v>426882</v>
       </c>
       <c r="R94" t="n">
-        <v>6784461</v>
+        <v>6784648</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10674,7 +10664,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10684,7 +10674,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10714,7 +10704,7 @@
         <v>128410027</v>
       </c>
       <c r="B95" t="n">
-        <v>91486</v>
+        <v>91487</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10826,45 +10816,50 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128410456</v>
+        <v>128410598</v>
       </c>
       <c r="B96" t="n">
-        <v>79089</v>
+        <v>8450</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>426882</v>
+        <v>426922</v>
       </c>
       <c r="R96" t="n">
-        <v>6784648</v>
+        <v>6784576</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10896,7 +10891,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10906,7 +10901,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10933,45 +10928,50 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128406985</v>
+        <v>128404859</v>
       </c>
       <c r="B97" t="n">
-        <v>78846</v>
+        <v>8450</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>427087</v>
+        <v>426869</v>
       </c>
       <c r="R97" t="n">
-        <v>6784548</v>
+        <v>6784461</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11003,7 +11003,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11013,7 +11013,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11040,50 +11040,45 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128405638</v>
+        <v>128410868</v>
       </c>
       <c r="B98" t="n">
-        <v>8450</v>
+        <v>79089</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>427026</v>
+        <v>426916</v>
       </c>
       <c r="R98" t="n">
-        <v>6784560</v>
+        <v>6784534</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11115,7 +11110,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11125,7 +11120,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11152,45 +11147,50 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128410868</v>
+        <v>128405638</v>
       </c>
       <c r="B99" t="n">
-        <v>79089</v>
+        <v>8450</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>426916</v>
+        <v>427026</v>
       </c>
       <c r="R99" t="n">
-        <v>6784534</v>
+        <v>6784560</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11222,7 +11222,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11232,7 +11232,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11478,7 +11478,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128408932</v>
+        <v>128416713</v>
       </c>
       <c r="B102" t="n">
         <v>79089</v>
@@ -11513,10 +11513,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>427081</v>
+        <v>426849</v>
       </c>
       <c r="R102" t="n">
-        <v>6784657</v>
+        <v>6784145</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11548,7 +11548,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11558,7 +11558,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11585,7 +11585,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128416713</v>
+        <v>128408932</v>
       </c>
       <c r="B103" t="n">
         <v>79089</v>
@@ -11620,10 +11620,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>426849</v>
+        <v>427081</v>
       </c>
       <c r="R103" t="n">
-        <v>6784145</v>
+        <v>6784657</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11655,7 +11655,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11665,7 +11665,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11692,10 +11692,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128409925</v>
+        <v>128407898</v>
       </c>
       <c r="B104" t="n">
-        <v>79679</v>
+        <v>78846</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11703,21 +11703,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11727,10 +11727,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>427082</v>
+        <v>427062</v>
       </c>
       <c r="R104" t="n">
-        <v>6784715</v>
+        <v>6784591</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11762,7 +11762,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11772,7 +11772,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11799,10 +11799,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128407898</v>
+        <v>128409925</v>
       </c>
       <c r="B105" t="n">
-        <v>78846</v>
+        <v>79679</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11810,21 +11810,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11834,10 +11834,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>427062</v>
+        <v>427082</v>
       </c>
       <c r="R105" t="n">
-        <v>6784591</v>
+        <v>6784715</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11869,7 +11869,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11879,7 +11879,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11906,10 +11906,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128407848</v>
+        <v>128416606</v>
       </c>
       <c r="B106" t="n">
-        <v>78847</v>
+        <v>78846</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11917,21 +11917,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11941,10 +11941,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>427064</v>
+        <v>426859</v>
       </c>
       <c r="R106" t="n">
-        <v>6784585</v>
+        <v>6784153</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11976,7 +11976,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11986,7 +11986,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12013,10 +12013,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128416606</v>
+        <v>128407848</v>
       </c>
       <c r="B107" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12024,21 +12024,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12048,10 +12048,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>426859</v>
+        <v>427064</v>
       </c>
       <c r="R107" t="n">
-        <v>6784153</v>
+        <v>6784585</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12083,7 +12083,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12093,7 +12093,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD107" t="b">

--- a/artfynd/A 36371-2025 artfynd.xlsx
+++ b/artfynd/A 36371-2025 artfynd.xlsx
@@ -2693,10 +2693,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128415015</v>
+        <v>128411184</v>
       </c>
       <c r="B21" t="n">
-        <v>79089</v>
+        <v>78847</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2704,34 +2704,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>426548</v>
+        <v>426819</v>
       </c>
       <c r="R21" t="n">
-        <v>6784175</v>
+        <v>6784515</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2763,7 +2763,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2773,7 +2773,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2800,10 +2800,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128414481</v>
+        <v>128415015</v>
       </c>
       <c r="B22" t="n">
-        <v>79708</v>
+        <v>79089</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2811,21 +2811,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2835,10 +2835,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>426524</v>
+        <v>426548</v>
       </c>
       <c r="R22" t="n">
-        <v>6784260</v>
+        <v>6784175</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2870,7 +2870,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2880,7 +2880,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2907,10 +2907,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128414172</v>
+        <v>128414481</v>
       </c>
       <c r="B23" t="n">
-        <v>78846</v>
+        <v>79708</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2918,21 +2918,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2942,10 +2942,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>426541</v>
+        <v>426524</v>
       </c>
       <c r="R23" t="n">
-        <v>6784302</v>
+        <v>6784260</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2977,7 +2977,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2987,7 +2987,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3014,7 +3014,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128418402</v>
+        <v>128414172</v>
       </c>
       <c r="B24" t="n">
         <v>78846</v>
@@ -3049,10 +3049,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>426596</v>
+        <v>426541</v>
       </c>
       <c r="R24" t="n">
-        <v>6784364</v>
+        <v>6784302</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3121,10 +3121,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128415595</v>
+        <v>128418402</v>
       </c>
       <c r="B25" t="n">
-        <v>79089</v>
+        <v>78846</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3132,21 +3132,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3156,10 +3156,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>426618</v>
+        <v>426596</v>
       </c>
       <c r="R25" t="n">
-        <v>6784050</v>
+        <v>6784364</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3191,7 +3191,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3201,7 +3201,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3228,10 +3228,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128411184</v>
+        <v>128415595</v>
       </c>
       <c r="B26" t="n">
-        <v>78847</v>
+        <v>79089</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3239,34 +3239,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>426819</v>
+        <v>426618</v>
       </c>
       <c r="R26" t="n">
-        <v>6784515</v>
+        <v>6784050</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3298,7 +3298,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3308,7 +3308,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4420,45 +4420,50 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128412524</v>
+        <v>128404418</v>
       </c>
       <c r="B37" t="n">
-        <v>79089</v>
+        <v>8450</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>426466</v>
+        <v>426715</v>
       </c>
       <c r="R37" t="n">
-        <v>6784510</v>
+        <v>6784397</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4490,7 +4495,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4500,7 +4505,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4634,50 +4639,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128404418</v>
+        <v>128412524</v>
       </c>
       <c r="B39" t="n">
-        <v>8450</v>
+        <v>79089</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>426715</v>
+        <v>426466</v>
       </c>
       <c r="R39" t="n">
-        <v>6784397</v>
+        <v>6784510</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4709,7 +4709,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4719,7 +4719,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5709,45 +5709,50 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128416262</v>
+        <v>128415767</v>
       </c>
       <c r="B49" t="n">
-        <v>79089</v>
+        <v>8450</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>426784</v>
+        <v>426618</v>
       </c>
       <c r="R49" t="n">
-        <v>6784159</v>
+        <v>6784050</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5779,7 +5784,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5789,7 +5794,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5816,45 +5821,50 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128417096</v>
+        <v>128414874</v>
       </c>
       <c r="B50" t="n">
-        <v>79089</v>
+        <v>8450</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>426812</v>
+        <v>426535</v>
       </c>
       <c r="R50" t="n">
-        <v>6784257</v>
+        <v>6784210</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5886,7 +5896,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5896,7 +5906,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5923,7 +5933,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128415549</v>
+        <v>128416262</v>
       </c>
       <c r="B51" t="n">
         <v>79089</v>
@@ -5954,14 +5964,14 @@
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>426615</v>
+        <v>426784</v>
       </c>
       <c r="R51" t="n">
-        <v>6784068</v>
+        <v>6784159</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5993,7 +6003,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6003,7 +6013,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6030,50 +6040,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128415767</v>
+        <v>128417096</v>
       </c>
       <c r="B52" t="n">
-        <v>8450</v>
+        <v>79089</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>426618</v>
+        <v>426812</v>
       </c>
       <c r="R52" t="n">
-        <v>6784050</v>
+        <v>6784257</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6105,7 +6110,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6115,7 +6120,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6142,50 +6147,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128414874</v>
+        <v>128415549</v>
       </c>
       <c r="B53" t="n">
-        <v>8450</v>
+        <v>79089</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>426535</v>
+        <v>426615</v>
       </c>
       <c r="R53" t="n">
-        <v>6784210</v>
+        <v>6784068</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6217,7 +6217,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6227,7 +6227,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -8633,45 +8633,50 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128410669</v>
+        <v>128409845</v>
       </c>
       <c r="B76" t="n">
-        <v>79089</v>
+        <v>8450</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>426922</v>
+        <v>427064</v>
       </c>
       <c r="R76" t="n">
-        <v>6784529</v>
+        <v>6784664</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8703,7 +8708,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8713,7 +8718,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8740,50 +8745,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128409845</v>
+        <v>128410669</v>
       </c>
       <c r="B77" t="n">
-        <v>8450</v>
+        <v>79089</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>427064</v>
+        <v>426922</v>
       </c>
       <c r="R77" t="n">
-        <v>6784664</v>
+        <v>6784529</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8815,7 +8815,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8825,7 +8825,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -11478,7 +11478,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128416713</v>
+        <v>128408932</v>
       </c>
       <c r="B102" t="n">
         <v>79089</v>
@@ -11513,10 +11513,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>426849</v>
+        <v>427081</v>
       </c>
       <c r="R102" t="n">
-        <v>6784145</v>
+        <v>6784657</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11548,7 +11548,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11558,7 +11558,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11585,7 +11585,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128408932</v>
+        <v>128416713</v>
       </c>
       <c r="B103" t="n">
         <v>79089</v>
@@ -11620,10 +11620,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>427081</v>
+        <v>426849</v>
       </c>
       <c r="R103" t="n">
-        <v>6784657</v>
+        <v>6784145</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11655,7 +11655,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11665,7 +11665,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11692,10 +11692,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128407898</v>
+        <v>128409925</v>
       </c>
       <c r="B104" t="n">
-        <v>78846</v>
+        <v>79679</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11703,21 +11703,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11727,10 +11727,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>427062</v>
+        <v>427082</v>
       </c>
       <c r="R104" t="n">
-        <v>6784591</v>
+        <v>6784715</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11762,7 +11762,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11772,7 +11772,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11799,10 +11799,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128409925</v>
+        <v>128407898</v>
       </c>
       <c r="B105" t="n">
-        <v>79679</v>
+        <v>78846</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11810,21 +11810,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11834,10 +11834,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>427082</v>
+        <v>427062</v>
       </c>
       <c r="R105" t="n">
-        <v>6784715</v>
+        <v>6784591</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11869,7 +11869,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11879,7 +11879,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD105" t="b">

--- a/artfynd/A 36371-2025 artfynd.xlsx
+++ b/artfynd/A 36371-2025 artfynd.xlsx
@@ -2693,10 +2693,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128411184</v>
+        <v>128415595</v>
       </c>
       <c r="B21" t="n">
-        <v>78847</v>
+        <v>79116</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2704,34 +2704,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>426819</v>
+        <v>426618</v>
       </c>
       <c r="R21" t="n">
-        <v>6784515</v>
+        <v>6784050</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2763,7 +2763,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2773,7 +2773,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2803,7 +2803,7 @@
         <v>128415015</v>
       </c>
       <c r="B22" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2907,10 +2907,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128414481</v>
+        <v>128414172</v>
       </c>
       <c r="B23" t="n">
-        <v>79708</v>
+        <v>78873</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2918,21 +2918,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2942,10 +2942,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>426524</v>
+        <v>426541</v>
       </c>
       <c r="R23" t="n">
-        <v>6784260</v>
+        <v>6784302</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2977,7 +2977,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2987,7 +2987,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3014,10 +3014,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128414172</v>
+        <v>128418402</v>
       </c>
       <c r="B24" t="n">
-        <v>78846</v>
+        <v>78873</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3049,10 +3049,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>426541</v>
+        <v>426596</v>
       </c>
       <c r="R24" t="n">
-        <v>6784302</v>
+        <v>6784364</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3121,10 +3121,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128418402</v>
+        <v>128414481</v>
       </c>
       <c r="B25" t="n">
-        <v>78846</v>
+        <v>79735</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3132,21 +3132,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3156,10 +3156,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>426596</v>
+        <v>426524</v>
       </c>
       <c r="R25" t="n">
-        <v>6784364</v>
+        <v>6784260</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3191,7 +3191,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3201,7 +3201,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3228,10 +3228,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128415595</v>
+        <v>128411184</v>
       </c>
       <c r="B26" t="n">
-        <v>79089</v>
+        <v>78874</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3239,34 +3239,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>426618</v>
+        <v>426819</v>
       </c>
       <c r="R26" t="n">
-        <v>6784050</v>
+        <v>6784515</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3298,7 +3298,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3308,7 +3308,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3335,10 +3335,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128414155</v>
+        <v>128414801</v>
       </c>
       <c r="B27" t="n">
-        <v>78847</v>
+        <v>79116</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3346,21 +3346,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3370,10 +3370,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>426540</v>
+        <v>426524</v>
       </c>
       <c r="R27" t="n">
-        <v>6784305</v>
+        <v>6784260</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3405,7 +3405,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3415,7 +3415,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3445,7 +3445,7 @@
         <v>128416106</v>
       </c>
       <c r="B28" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3557,7 +3557,7 @@
         <v>128417228</v>
       </c>
       <c r="B29" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3661,10 +3661,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128414801</v>
+        <v>128414155</v>
       </c>
       <c r="B30" t="n">
-        <v>79089</v>
+        <v>78874</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3672,21 +3672,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3696,10 +3696,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>426524</v>
+        <v>426540</v>
       </c>
       <c r="R30" t="n">
-        <v>6784260</v>
+        <v>6784305</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3731,7 +3731,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3768,10 +3768,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128413169</v>
+        <v>128418215</v>
       </c>
       <c r="B31" t="n">
-        <v>79089</v>
+        <v>78874</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3779,21 +3779,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3803,10 +3803,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>426555</v>
+        <v>426655</v>
       </c>
       <c r="R31" t="n">
-        <v>6784393</v>
+        <v>6784360</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3875,10 +3875,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128414306</v>
+        <v>128413169</v>
       </c>
       <c r="B32" t="n">
-        <v>57686</v>
+        <v>79116</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3886,39 +3886,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>426519</v>
+        <v>426555</v>
       </c>
       <c r="R32" t="n">
-        <v>6784286</v>
+        <v>6784393</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3950,7 +3945,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3960,7 +3955,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3987,10 +3982,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128418215</v>
+        <v>128414306</v>
       </c>
       <c r="B33" t="n">
-        <v>78847</v>
+        <v>57713</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3998,34 +3993,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>426655</v>
+        <v>426519</v>
       </c>
       <c r="R33" t="n">
-        <v>6784360</v>
+        <v>6784286</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4057,7 +4057,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4209,7 +4209,7 @@
         <v>128416349</v>
       </c>
       <c r="B35" t="n">
-        <v>78846</v>
+        <v>78873</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4316,7 +4316,7 @@
         <v>128404649</v>
       </c>
       <c r="B36" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4420,50 +4420,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128404418</v>
+        <v>128412524</v>
       </c>
       <c r="B37" t="n">
-        <v>8450</v>
+        <v>79116</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>426715</v>
+        <v>426466</v>
       </c>
       <c r="R37" t="n">
-        <v>6784397</v>
+        <v>6784510</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4495,7 +4490,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4505,7 +4500,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4532,45 +4527,50 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128414383</v>
+        <v>128404418</v>
       </c>
       <c r="B38" t="n">
-        <v>78847</v>
+        <v>8450</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>426509</v>
+        <v>426715</v>
       </c>
       <c r="R38" t="n">
-        <v>6784270</v>
+        <v>6784397</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4602,7 +4602,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4612,7 +4612,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4639,10 +4639,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128412524</v>
+        <v>128414383</v>
       </c>
       <c r="B39" t="n">
-        <v>79089</v>
+        <v>78874</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4650,21 +4650,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4674,10 +4674,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>426466</v>
+        <v>426509</v>
       </c>
       <c r="R39" t="n">
-        <v>6784510</v>
+        <v>6784270</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4709,7 +4709,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4719,7 +4719,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4746,10 +4746,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128418198</v>
+        <v>128418704</v>
       </c>
       <c r="B40" t="n">
-        <v>79089</v>
+        <v>78873</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4757,21 +4757,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4781,7 +4781,7 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>426656</v>
+        <v>426573</v>
       </c>
       <c r="R40" t="n">
         <v>6784360</v>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4853,10 +4853,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128418704</v>
+        <v>128418719</v>
       </c>
       <c r="B41" t="n">
-        <v>78846</v>
+        <v>79116</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4864,21 +4864,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4888,10 +4888,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>426573</v>
+        <v>426571</v>
       </c>
       <c r="R41" t="n">
-        <v>6784360</v>
+        <v>6784357</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4933,7 +4933,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4960,10 +4960,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128413197</v>
+        <v>128418198</v>
       </c>
       <c r="B42" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4995,10 +4995,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>426532</v>
+        <v>426656</v>
       </c>
       <c r="R42" t="n">
-        <v>6784390</v>
+        <v>6784360</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5030,7 +5030,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5040,7 +5040,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5067,10 +5067,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128415503</v>
+        <v>128413197</v>
       </c>
       <c r="B43" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5102,10 +5102,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>426605</v>
+        <v>426532</v>
       </c>
       <c r="R43" t="n">
-        <v>6784090</v>
+        <v>6784390</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5137,7 +5137,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5147,7 +5147,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5174,10 +5174,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128417709</v>
+        <v>128415503</v>
       </c>
       <c r="B44" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5205,14 +5205,14 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>426717</v>
+        <v>426605</v>
       </c>
       <c r="R44" t="n">
-        <v>6784350</v>
+        <v>6784090</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5244,7 +5244,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5254,7 +5254,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5281,10 +5281,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128418719</v>
+        <v>128417709</v>
       </c>
       <c r="B45" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5312,14 +5312,14 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>426571</v>
+        <v>426717</v>
       </c>
       <c r="R45" t="n">
-        <v>6784357</v>
+        <v>6784350</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5351,7 +5351,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5388,10 +5388,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128416206</v>
+        <v>128413145</v>
       </c>
       <c r="B46" t="n">
-        <v>78846</v>
+        <v>79116</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5399,34 +5399,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>426760</v>
+        <v>426534</v>
       </c>
       <c r="R46" t="n">
-        <v>6784153</v>
+        <v>6784406</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5458,7 +5458,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5468,7 +5468,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5495,10 +5495,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128413145</v>
+        <v>128416206</v>
       </c>
       <c r="B47" t="n">
-        <v>79089</v>
+        <v>78873</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5506,34 +5506,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>426534</v>
+        <v>426760</v>
       </c>
       <c r="R47" t="n">
-        <v>6784406</v>
+        <v>6784153</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5565,7 +5565,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5575,7 +5575,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5605,7 +5605,7 @@
         <v>128412596</v>
       </c>
       <c r="B48" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5709,50 +5709,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128415767</v>
+        <v>128416262</v>
       </c>
       <c r="B49" t="n">
-        <v>8450</v>
+        <v>79116</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>426618</v>
+        <v>426784</v>
       </c>
       <c r="R49" t="n">
-        <v>6784050</v>
+        <v>6784159</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5784,7 +5779,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5794,7 +5789,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5821,50 +5816,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128414874</v>
+        <v>128417096</v>
       </c>
       <c r="B50" t="n">
-        <v>8450</v>
+        <v>79116</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>426535</v>
+        <v>426812</v>
       </c>
       <c r="R50" t="n">
-        <v>6784210</v>
+        <v>6784257</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5896,7 +5886,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5906,7 +5896,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5933,10 +5923,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128416262</v>
+        <v>128415549</v>
       </c>
       <c r="B51" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5964,14 +5954,14 @@
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>426784</v>
+        <v>426615</v>
       </c>
       <c r="R51" t="n">
-        <v>6784159</v>
+        <v>6784068</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6003,7 +5993,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6013,7 +6003,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6040,45 +6030,50 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128417096</v>
+        <v>128415767</v>
       </c>
       <c r="B52" t="n">
-        <v>79089</v>
+        <v>8450</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>426812</v>
+        <v>426618</v>
       </c>
       <c r="R52" t="n">
-        <v>6784257</v>
+        <v>6784050</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6110,7 +6105,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6120,7 +6115,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6147,45 +6142,50 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128415549</v>
+        <v>128414874</v>
       </c>
       <c r="B53" t="n">
-        <v>79089</v>
+        <v>8450</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>426615</v>
+        <v>426535</v>
       </c>
       <c r="R53" t="n">
-        <v>6784068</v>
+        <v>6784210</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6217,7 +6217,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6227,7 +6227,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6254,10 +6254,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128418647</v>
+        <v>128415267</v>
       </c>
       <c r="B54" t="n">
-        <v>79089</v>
+        <v>78874</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6265,21 +6265,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6289,10 +6289,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>426573</v>
+        <v>426604</v>
       </c>
       <c r="R54" t="n">
-        <v>6784376</v>
+        <v>6784093</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6324,7 +6324,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>18:59</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>18:59</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6361,10 +6361,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128413992</v>
+        <v>128418647</v>
       </c>
       <c r="B55" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6396,10 +6396,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>426519</v>
+        <v>426573</v>
       </c>
       <c r="R55" t="n">
-        <v>6784308</v>
+        <v>6784376</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>18:59</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6441,7 +6441,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>18:59</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6468,10 +6468,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128415267</v>
+        <v>128413992</v>
       </c>
       <c r="B56" t="n">
-        <v>78847</v>
+        <v>79116</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6479,21 +6479,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6503,10 +6503,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>426604</v>
+        <v>426519</v>
       </c>
       <c r="R56" t="n">
-        <v>6784093</v>
+        <v>6784308</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6538,7 +6538,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6548,7 +6548,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6578,7 +6578,7 @@
         <v>128417675</v>
       </c>
       <c r="B57" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6685,7 +6685,7 @@
         <v>128415393</v>
       </c>
       <c r="B58" t="n">
-        <v>79708</v>
+        <v>79735</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6792,7 +6792,7 @@
         <v>128418258</v>
       </c>
       <c r="B59" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6899,7 +6899,7 @@
         <v>128416385</v>
       </c>
       <c r="B60" t="n">
-        <v>79708</v>
+        <v>79735</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7118,7 +7118,7 @@
         <v>128414843</v>
       </c>
       <c r="B62" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7222,10 +7222,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128412109</v>
+        <v>128414095</v>
       </c>
       <c r="B63" t="n">
-        <v>79089</v>
+        <v>78874</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7233,21 +7233,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7257,10 +7257,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>426646</v>
+        <v>426556</v>
       </c>
       <c r="R63" t="n">
-        <v>6784678</v>
+        <v>6784312</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7292,7 +7292,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7302,7 +7302,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7329,10 +7329,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128414095</v>
+        <v>128412109</v>
       </c>
       <c r="B64" t="n">
-        <v>78847</v>
+        <v>79116</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7340,21 +7340,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7364,10 +7364,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>426556</v>
+        <v>426646</v>
       </c>
       <c r="R64" t="n">
-        <v>6784312</v>
+        <v>6784678</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7399,7 +7399,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7409,7 +7409,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7660,50 +7660,50 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128413310</v>
+        <v>128417436</v>
       </c>
       <c r="B67" t="n">
-        <v>57686</v>
+        <v>8450</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>426477</v>
+        <v>426801</v>
       </c>
       <c r="R67" t="n">
-        <v>6784397</v>
+        <v>6784284</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7735,7 +7735,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7745,7 +7745,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7775,7 +7775,7 @@
         <v>128413333</v>
       </c>
       <c r="B68" t="n">
-        <v>78846</v>
+        <v>78873</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7879,50 +7879,50 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128417436</v>
+        <v>128413310</v>
       </c>
       <c r="B69" t="n">
-        <v>8450</v>
+        <v>57713</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>426801</v>
+        <v>426477</v>
       </c>
       <c r="R69" t="n">
-        <v>6784284</v>
+        <v>6784397</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7954,7 +7954,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7964,7 +7964,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7991,10 +7991,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128418292</v>
+        <v>128417205</v>
       </c>
       <c r="B70" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8022,14 +8022,14 @@
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>426624</v>
+        <v>426813</v>
       </c>
       <c r="R70" t="n">
-        <v>6784361</v>
+        <v>6784276</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8061,7 +8061,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8071,12 +8071,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>18:45</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav på tallarna på en radie av 50 meter.</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8103,10 +8098,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128417205</v>
+        <v>128418292</v>
       </c>
       <c r="B71" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8134,14 +8129,14 @@
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>426813</v>
+        <v>426624</v>
       </c>
       <c r="R71" t="n">
-        <v>6784276</v>
+        <v>6784361</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8173,7 +8168,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8183,7 +8178,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav på tallarna på en radie av 50 meter.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8213,7 +8213,7 @@
         <v>128415978</v>
       </c>
       <c r="B72" t="n">
-        <v>78846</v>
+        <v>78873</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8317,50 +8317,45 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128414247</v>
+        <v>128413213</v>
       </c>
       <c r="B73" t="n">
-        <v>8450</v>
+        <v>78874</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>426535</v>
+        <v>426524</v>
       </c>
       <c r="R73" t="n">
-        <v>6784292</v>
+        <v>6784388</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8392,7 +8387,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8402,7 +8397,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8429,45 +8424,50 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128413213</v>
+        <v>128414247</v>
       </c>
       <c r="B74" t="n">
-        <v>78847</v>
+        <v>8450</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>426524</v>
+        <v>426535</v>
       </c>
       <c r="R74" t="n">
-        <v>6784388</v>
+        <v>6784292</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8499,7 +8499,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8509,7 +8509,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8633,50 +8633,45 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128409845</v>
+        <v>128410669</v>
       </c>
       <c r="B76" t="n">
-        <v>8450</v>
+        <v>79116</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>427064</v>
+        <v>426922</v>
       </c>
       <c r="R76" t="n">
-        <v>6784664</v>
+        <v>6784529</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8708,7 +8703,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8718,7 +8713,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8745,45 +8740,50 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128410669</v>
+        <v>128409845</v>
       </c>
       <c r="B77" t="n">
-        <v>79089</v>
+        <v>8450</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>426922</v>
+        <v>427064</v>
       </c>
       <c r="R77" t="n">
-        <v>6784529</v>
+        <v>6784664</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8815,7 +8815,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8825,7 +8825,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8855,7 +8855,7 @@
         <v>128408858</v>
       </c>
       <c r="B78" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8962,7 +8962,7 @@
         <v>128410625</v>
       </c>
       <c r="B79" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9410,7 +9410,7 @@
         <v>128404878</v>
       </c>
       <c r="B83" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9522,7 +9522,7 @@
         <v>128409945</v>
       </c>
       <c r="B84" t="n">
-        <v>78847</v>
+        <v>78874</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9629,7 +9629,7 @@
         <v>128407168</v>
       </c>
       <c r="B85" t="n">
-        <v>78847</v>
+        <v>78874</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9736,7 +9736,7 @@
         <v>128416596</v>
       </c>
       <c r="B86" t="n">
-        <v>79708</v>
+        <v>79735</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9840,10 +9840,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128416791</v>
+        <v>128416502</v>
       </c>
       <c r="B87" t="n">
-        <v>78847</v>
+        <v>78874</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9875,10 +9875,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>426835</v>
+        <v>426841</v>
       </c>
       <c r="R87" t="n">
-        <v>6784196</v>
+        <v>6784169</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9910,7 +9910,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9920,7 +9920,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9950,7 +9950,7 @@
         <v>128406999</v>
       </c>
       <c r="B88" t="n">
-        <v>78847</v>
+        <v>78874</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10054,10 +10054,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128416502</v>
+        <v>128416791</v>
       </c>
       <c r="B89" t="n">
-        <v>78847</v>
+        <v>78874</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10089,10 +10089,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>426841</v>
+        <v>426835</v>
       </c>
       <c r="R89" t="n">
-        <v>6784169</v>
+        <v>6784196</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10124,7 +10124,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10134,7 +10134,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10164,7 +10164,7 @@
         <v>128417147</v>
       </c>
       <c r="B90" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10271,7 +10271,7 @@
         <v>128417068</v>
       </c>
       <c r="B91" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10378,7 +10378,7 @@
         <v>128423249</v>
       </c>
       <c r="B92" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10490,7 +10490,7 @@
         <v>128406985</v>
       </c>
       <c r="B93" t="n">
-        <v>78846</v>
+        <v>78873</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10597,7 +10597,7 @@
         <v>128410456</v>
       </c>
       <c r="B94" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10704,7 +10704,7 @@
         <v>128410027</v>
       </c>
       <c r="B95" t="n">
-        <v>91487</v>
+        <v>91514</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11043,7 +11043,7 @@
         <v>128410868</v>
       </c>
       <c r="B98" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11259,45 +11259,50 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128411027</v>
+        <v>128410908</v>
       </c>
       <c r="B100" t="n">
-        <v>79089</v>
+        <v>8450</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>426858</v>
+        <v>426908</v>
       </c>
       <c r="R100" t="n">
-        <v>6784514</v>
+        <v>6784511</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11329,7 +11334,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11339,7 +11344,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11366,50 +11371,45 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128410908</v>
+        <v>128411027</v>
       </c>
       <c r="B101" t="n">
-        <v>8450</v>
+        <v>79116</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>426908</v>
+        <v>426858</v>
       </c>
       <c r="R101" t="n">
-        <v>6784511</v>
+        <v>6784514</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11441,7 +11441,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11451,7 +11451,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11478,10 +11478,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128408932</v>
+        <v>128416713</v>
       </c>
       <c r="B102" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11513,10 +11513,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>427081</v>
+        <v>426849</v>
       </c>
       <c r="R102" t="n">
-        <v>6784657</v>
+        <v>6784145</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11548,7 +11548,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11558,7 +11558,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11585,10 +11585,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128416713</v>
+        <v>128408932</v>
       </c>
       <c r="B103" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11620,10 +11620,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>426849</v>
+        <v>427081</v>
       </c>
       <c r="R103" t="n">
-        <v>6784145</v>
+        <v>6784657</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11655,7 +11655,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11665,7 +11665,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11695,7 +11695,7 @@
         <v>128409925</v>
       </c>
       <c r="B104" t="n">
-        <v>79679</v>
+        <v>79706</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11802,7 +11802,7 @@
         <v>128407898</v>
       </c>
       <c r="B105" t="n">
-        <v>78846</v>
+        <v>78873</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11909,7 +11909,7 @@
         <v>128416606</v>
       </c>
       <c r="B106" t="n">
-        <v>78846</v>
+        <v>78873</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12016,7 +12016,7 @@
         <v>128407848</v>
       </c>
       <c r="B107" t="n">
-        <v>78847</v>
+        <v>78874</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>

--- a/artfynd/A 36371-2025 artfynd.xlsx
+++ b/artfynd/A 36371-2025 artfynd.xlsx
@@ -2693,10 +2693,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128415595</v>
+        <v>128411184</v>
       </c>
       <c r="B21" t="n">
-        <v>79116</v>
+        <v>78874</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2704,34 +2704,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>426618</v>
+        <v>426819</v>
       </c>
       <c r="R21" t="n">
-        <v>6784050</v>
+        <v>6784515</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2763,7 +2763,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2773,7 +2773,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2800,7 +2800,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128415015</v>
+        <v>128415595</v>
       </c>
       <c r="B22" t="n">
         <v>79116</v>
@@ -2835,10 +2835,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>426548</v>
+        <v>426618</v>
       </c>
       <c r="R22" t="n">
-        <v>6784175</v>
+        <v>6784050</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2870,7 +2870,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2880,7 +2880,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2907,10 +2907,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128414172</v>
+        <v>128415015</v>
       </c>
       <c r="B23" t="n">
-        <v>78873</v>
+        <v>79116</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2918,21 +2918,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2942,10 +2942,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>426541</v>
+        <v>426548</v>
       </c>
       <c r="R23" t="n">
-        <v>6784302</v>
+        <v>6784175</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2977,7 +2977,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2987,7 +2987,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3014,7 +3014,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128418402</v>
+        <v>128414172</v>
       </c>
       <c r="B24" t="n">
         <v>78873</v>
@@ -3049,10 +3049,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>426596</v>
+        <v>426541</v>
       </c>
       <c r="R24" t="n">
-        <v>6784364</v>
+        <v>6784302</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3121,10 +3121,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128414481</v>
+        <v>128418402</v>
       </c>
       <c r="B25" t="n">
-        <v>79735</v>
+        <v>78873</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3132,21 +3132,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3156,10 +3156,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>426524</v>
+        <v>426596</v>
       </c>
       <c r="R25" t="n">
-        <v>6784260</v>
+        <v>6784364</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3191,7 +3191,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3201,7 +3201,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3228,10 +3228,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128411184</v>
+        <v>128414481</v>
       </c>
       <c r="B26" t="n">
-        <v>78874</v>
+        <v>79735</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3239,34 +3239,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>426819</v>
+        <v>426524</v>
       </c>
       <c r="R26" t="n">
-        <v>6784515</v>
+        <v>6784260</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3298,7 +3298,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3308,7 +3308,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -6896,45 +6896,50 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128416385</v>
+        <v>128404480</v>
       </c>
       <c r="B60" t="n">
-        <v>79735</v>
+        <v>8450</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>426796</v>
+        <v>426773</v>
       </c>
       <c r="R60" t="n">
-        <v>6784156</v>
+        <v>6784434</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6966,7 +6971,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6976,7 +6981,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7003,50 +7008,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128404480</v>
+        <v>128416385</v>
       </c>
       <c r="B61" t="n">
-        <v>8450</v>
+        <v>79735</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>426773</v>
+        <v>426796</v>
       </c>
       <c r="R61" t="n">
-        <v>6784434</v>
+        <v>6784156</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7078,7 +7078,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7088,7 +7088,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7222,10 +7222,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128414095</v>
+        <v>128412109</v>
       </c>
       <c r="B63" t="n">
-        <v>78874</v>
+        <v>79116</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7233,21 +7233,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7257,10 +7257,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>426556</v>
+        <v>426646</v>
       </c>
       <c r="R63" t="n">
-        <v>6784312</v>
+        <v>6784678</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7292,7 +7292,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7302,7 +7302,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7329,10 +7329,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128412109</v>
+        <v>128414095</v>
       </c>
       <c r="B64" t="n">
-        <v>79116</v>
+        <v>78874</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7340,21 +7340,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7364,10 +7364,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>426646</v>
+        <v>426556</v>
       </c>
       <c r="R64" t="n">
-        <v>6784678</v>
+        <v>6784312</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7399,7 +7399,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7409,7 +7409,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8317,45 +8317,50 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128413213</v>
+        <v>128414247</v>
       </c>
       <c r="B73" t="n">
-        <v>78874</v>
+        <v>8450</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>426524</v>
+        <v>426535</v>
       </c>
       <c r="R73" t="n">
-        <v>6784388</v>
+        <v>6784292</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8387,7 +8392,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8397,7 +8402,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8424,50 +8429,45 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128414247</v>
+        <v>128413213</v>
       </c>
       <c r="B74" t="n">
-        <v>8450</v>
+        <v>78874</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>426535</v>
+        <v>426524</v>
       </c>
       <c r="R74" t="n">
-        <v>6784292</v>
+        <v>6784388</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8499,7 +8499,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8509,7 +8509,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9407,10 +9407,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128404878</v>
+        <v>128409945</v>
       </c>
       <c r="B83" t="n">
-        <v>57713</v>
+        <v>78874</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9418,39 +9418,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>426879</v>
+        <v>427084</v>
       </c>
       <c r="R83" t="n">
-        <v>6784490</v>
+        <v>6784718</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9482,7 +9477,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9492,7 +9487,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9519,10 +9514,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128409945</v>
+        <v>128404878</v>
       </c>
       <c r="B84" t="n">
-        <v>78874</v>
+        <v>57713</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9530,34 +9525,39 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>427084</v>
+        <v>426879</v>
       </c>
       <c r="R84" t="n">
-        <v>6784718</v>
+        <v>6784490</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9589,7 +9589,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9599,7 +9599,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9840,7 +9840,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128416502</v>
+        <v>128406999</v>
       </c>
       <c r="B87" t="n">
         <v>78874</v>
@@ -9875,10 +9875,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>426841</v>
+        <v>427083</v>
       </c>
       <c r="R87" t="n">
-        <v>6784169</v>
+        <v>6784551</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9910,7 +9910,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9920,7 +9920,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9947,7 +9947,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128406999</v>
+        <v>128416502</v>
       </c>
       <c r="B88" t="n">
         <v>78874</v>
@@ -9982,10 +9982,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>427083</v>
+        <v>426841</v>
       </c>
       <c r="R88" t="n">
-        <v>6784551</v>
+        <v>6784169</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10017,7 +10017,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10027,7 +10027,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10487,10 +10487,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128406985</v>
+        <v>128410027</v>
       </c>
       <c r="B93" t="n">
-        <v>78873</v>
+        <v>91514</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10498,34 +10498,41 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6446</v>
+        <v>5442</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>427087</v>
+        <v>427093</v>
       </c>
       <c r="R93" t="n">
-        <v>6784548</v>
+        <v>6784727</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10557,7 +10564,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10567,7 +10574,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10576,6 +10583,7 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -10594,45 +10602,50 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128410456</v>
+        <v>128410598</v>
       </c>
       <c r="B94" t="n">
-        <v>79116</v>
+        <v>8450</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>426882</v>
+        <v>426922</v>
       </c>
       <c r="R94" t="n">
-        <v>6784648</v>
+        <v>6784576</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10664,7 +10677,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10674,7 +10687,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10701,52 +10714,50 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128410027</v>
+        <v>128404859</v>
       </c>
       <c r="B95" t="n">
-        <v>91514</v>
+        <v>8450</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>427093</v>
+        <v>426869</v>
       </c>
       <c r="R95" t="n">
-        <v>6784727</v>
+        <v>6784461</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10778,7 +10789,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10788,7 +10799,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10797,7 +10808,6 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10816,50 +10826,45 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128410598</v>
+        <v>128406985</v>
       </c>
       <c r="B96" t="n">
-        <v>8450</v>
+        <v>78873</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>426922</v>
+        <v>427087</v>
       </c>
       <c r="R96" t="n">
-        <v>6784576</v>
+        <v>6784548</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10891,7 +10896,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10901,7 +10906,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10928,50 +10933,45 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128404859</v>
+        <v>128410456</v>
       </c>
       <c r="B97" t="n">
-        <v>8450</v>
+        <v>79116</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>426869</v>
+        <v>426882</v>
       </c>
       <c r="R97" t="n">
-        <v>6784461</v>
+        <v>6784648</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11003,7 +11003,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11013,7 +11013,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11692,10 +11692,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128409925</v>
+        <v>128407898</v>
       </c>
       <c r="B104" t="n">
-        <v>79706</v>
+        <v>78873</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11703,21 +11703,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11727,10 +11727,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>427082</v>
+        <v>427062</v>
       </c>
       <c r="R104" t="n">
-        <v>6784715</v>
+        <v>6784591</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11762,7 +11762,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11772,7 +11772,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11799,10 +11799,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128407898</v>
+        <v>128409925</v>
       </c>
       <c r="B105" t="n">
-        <v>78873</v>
+        <v>79706</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11810,21 +11810,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11834,10 +11834,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>427062</v>
+        <v>427082</v>
       </c>
       <c r="R105" t="n">
-        <v>6784591</v>
+        <v>6784715</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11869,7 +11869,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11879,7 +11879,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD105" t="b">

--- a/artfynd/A 36371-2025 artfynd.xlsx
+++ b/artfynd/A 36371-2025 artfynd.xlsx
@@ -2693,10 +2693,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128411184</v>
+        <v>128414481</v>
       </c>
       <c r="B21" t="n">
-        <v>78874</v>
+        <v>79739</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2704,34 +2704,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>426819</v>
+        <v>426524</v>
       </c>
       <c r="R21" t="n">
-        <v>6784515</v>
+        <v>6784260</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2763,7 +2763,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2773,7 +2773,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2803,7 +2803,7 @@
         <v>128415595</v>
       </c>
       <c r="B22" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2910,7 +2910,7 @@
         <v>128415015</v>
       </c>
       <c r="B23" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         <v>128414172</v>
       </c>
       <c r="B24" t="n">
-        <v>78873</v>
+        <v>78877</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         <v>128418402</v>
       </c>
       <c r="B25" t="n">
-        <v>78873</v>
+        <v>78877</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3228,10 +3228,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128414481</v>
+        <v>128411184</v>
       </c>
       <c r="B26" t="n">
-        <v>79735</v>
+        <v>78878</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3239,34 +3239,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>426524</v>
+        <v>426819</v>
       </c>
       <c r="R26" t="n">
-        <v>6784260</v>
+        <v>6784515</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3298,7 +3298,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3308,7 +3308,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3338,7 +3338,7 @@
         <v>128414801</v>
       </c>
       <c r="B27" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
         <v>128416106</v>
       </c>
       <c r="B28" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3557,7 +3557,7 @@
         <v>128417228</v>
       </c>
       <c r="B29" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3664,7 +3664,7 @@
         <v>128414155</v>
       </c>
       <c r="B30" t="n">
-        <v>78874</v>
+        <v>78878</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3768,10 +3768,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128418215</v>
+        <v>128413169</v>
       </c>
       <c r="B31" t="n">
-        <v>78874</v>
+        <v>79120</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3779,21 +3779,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3803,10 +3803,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>426655</v>
+        <v>426555</v>
       </c>
       <c r="R31" t="n">
-        <v>6784360</v>
+        <v>6784393</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3875,10 +3875,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128413169</v>
+        <v>128414306</v>
       </c>
       <c r="B32" t="n">
-        <v>79116</v>
+        <v>57713</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3886,34 +3886,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>426555</v>
+        <v>426519</v>
       </c>
       <c r="R32" t="n">
-        <v>6784393</v>
+        <v>6784286</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3945,7 +3950,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3955,7 +3960,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3982,38 +3987,38 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128414306</v>
+        <v>128413945</v>
       </c>
       <c r="B33" t="n">
-        <v>57713</v>
+        <v>8450</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4022,10 +4027,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>426519</v>
+        <v>426498</v>
       </c>
       <c r="R33" t="n">
-        <v>6784286</v>
+        <v>6784322</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4057,7 +4062,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4067,7 +4072,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4094,50 +4099,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128413945</v>
+        <v>128418215</v>
       </c>
       <c r="B34" t="n">
-        <v>8450</v>
+        <v>78878</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>426498</v>
+        <v>426655</v>
       </c>
       <c r="R34" t="n">
-        <v>6784322</v>
+        <v>6784360</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4209,7 +4209,7 @@
         <v>128416349</v>
       </c>
       <c r="B35" t="n">
-        <v>78873</v>
+        <v>78877</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4316,7 +4316,7 @@
         <v>128404649</v>
       </c>
       <c r="B36" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4423,7 +4423,7 @@
         <v>128412524</v>
       </c>
       <c r="B37" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4527,50 +4527,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128404418</v>
+        <v>128414383</v>
       </c>
       <c r="B38" t="n">
-        <v>8450</v>
+        <v>78878</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>426715</v>
+        <v>426509</v>
       </c>
       <c r="R38" t="n">
-        <v>6784397</v>
+        <v>6784270</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4602,7 +4597,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4612,7 +4607,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4639,45 +4634,50 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128414383</v>
+        <v>128404418</v>
       </c>
       <c r="B39" t="n">
-        <v>78874</v>
+        <v>8450</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>426509</v>
+        <v>426715</v>
       </c>
       <c r="R39" t="n">
-        <v>6784270</v>
+        <v>6784397</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4709,7 +4709,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4719,7 +4719,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4749,7 +4749,7 @@
         <v>128418704</v>
       </c>
       <c r="B40" t="n">
-        <v>78873</v>
+        <v>78877</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4856,7 +4856,7 @@
         <v>128418719</v>
       </c>
       <c r="B41" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4963,7 +4963,7 @@
         <v>128418198</v>
       </c>
       <c r="B42" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
         <v>128413197</v>
       </c>
       <c r="B43" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5177,7 +5177,7 @@
         <v>128415503</v>
       </c>
       <c r="B44" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5284,7 +5284,7 @@
         <v>128417709</v>
       </c>
       <c r="B45" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5391,7 +5391,7 @@
         <v>128413145</v>
       </c>
       <c r="B46" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5498,7 +5498,7 @@
         <v>128416206</v>
       </c>
       <c r="B47" t="n">
-        <v>78873</v>
+        <v>78877</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5605,7 +5605,7 @@
         <v>128412596</v>
       </c>
       <c r="B48" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5712,7 +5712,7 @@
         <v>128416262</v>
       </c>
       <c r="B49" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5819,7 +5819,7 @@
         <v>128417096</v>
       </c>
       <c r="B50" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5926,7 +5926,7 @@
         <v>128415549</v>
       </c>
       <c r="B51" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6030,7 +6030,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128415767</v>
+        <v>128414874</v>
       </c>
       <c r="B52" t="n">
         <v>8450</v>
@@ -6061,7 +6061,7 @@
       <c r="I52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -6070,10 +6070,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>426618</v>
+        <v>426535</v>
       </c>
       <c r="R52" t="n">
-        <v>6784050</v>
+        <v>6784210</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6105,7 +6105,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6115,7 +6115,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6142,7 +6142,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128414874</v>
+        <v>128415767</v>
       </c>
       <c r="B53" t="n">
         <v>8450</v>
@@ -6173,7 +6173,7 @@
       <c r="I53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6182,10 +6182,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>426535</v>
+        <v>426618</v>
       </c>
       <c r="R53" t="n">
-        <v>6784210</v>
+        <v>6784050</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6217,7 +6217,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6227,7 +6227,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6257,7 +6257,7 @@
         <v>128415267</v>
       </c>
       <c r="B54" t="n">
-        <v>78874</v>
+        <v>78878</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6364,7 +6364,7 @@
         <v>128418647</v>
       </c>
       <c r="B55" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6471,7 +6471,7 @@
         <v>128413992</v>
       </c>
       <c r="B56" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6578,7 +6578,7 @@
         <v>128417675</v>
       </c>
       <c r="B57" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6682,10 +6682,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128415393</v>
+        <v>128418258</v>
       </c>
       <c r="B58" t="n">
-        <v>79735</v>
+        <v>79120</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6693,21 +6693,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6717,10 +6717,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>426601</v>
+        <v>426632</v>
       </c>
       <c r="R58" t="n">
-        <v>6784100</v>
+        <v>6784364</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6752,7 +6752,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6762,7 +6762,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6789,10 +6789,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128418258</v>
+        <v>128415393</v>
       </c>
       <c r="B59" t="n">
-        <v>79116</v>
+        <v>79739</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6800,21 +6800,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6824,10 +6824,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>426632</v>
+        <v>426601</v>
       </c>
       <c r="R59" t="n">
-        <v>6784364</v>
+        <v>6784100</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6859,7 +6859,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6869,7 +6869,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6896,50 +6896,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128404480</v>
+        <v>128416385</v>
       </c>
       <c r="B60" t="n">
-        <v>8450</v>
+        <v>79739</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>426773</v>
+        <v>426796</v>
       </c>
       <c r="R60" t="n">
-        <v>6784434</v>
+        <v>6784156</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6971,7 +6966,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6981,7 +6976,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7008,45 +7003,50 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128416385</v>
+        <v>128404480</v>
       </c>
       <c r="B61" t="n">
-        <v>79735</v>
+        <v>8450</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>426796</v>
+        <v>426773</v>
       </c>
       <c r="R61" t="n">
-        <v>6784156</v>
+        <v>6784434</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7078,7 +7078,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7088,7 +7088,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7118,7 +7118,7 @@
         <v>128414843</v>
       </c>
       <c r="B62" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7225,7 +7225,7 @@
         <v>128412109</v>
       </c>
       <c r="B63" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7332,7 +7332,7 @@
         <v>128414095</v>
       </c>
       <c r="B64" t="n">
-        <v>78874</v>
+        <v>78878</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7660,50 +7660,50 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128417436</v>
+        <v>128413310</v>
       </c>
       <c r="B67" t="n">
-        <v>8450</v>
+        <v>57713</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>426801</v>
+        <v>426477</v>
       </c>
       <c r="R67" t="n">
-        <v>6784284</v>
+        <v>6784397</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7735,7 +7735,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7745,7 +7745,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7775,7 +7775,7 @@
         <v>128413333</v>
       </c>
       <c r="B68" t="n">
-        <v>78873</v>
+        <v>78877</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7879,50 +7879,50 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128413310</v>
+        <v>128417436</v>
       </c>
       <c r="B69" t="n">
-        <v>57713</v>
+        <v>8450</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>426477</v>
+        <v>426801</v>
       </c>
       <c r="R69" t="n">
-        <v>6784397</v>
+        <v>6784284</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7954,7 +7954,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7964,7 +7964,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7994,7 +7994,7 @@
         <v>128417205</v>
       </c>
       <c r="B70" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8101,7 +8101,7 @@
         <v>128418292</v>
       </c>
       <c r="B71" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         <v>128415978</v>
       </c>
       <c r="B72" t="n">
-        <v>78873</v>
+        <v>78877</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8432,7 +8432,7 @@
         <v>128413213</v>
       </c>
       <c r="B74" t="n">
-        <v>78874</v>
+        <v>78878</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8636,7 +8636,7 @@
         <v>128410669</v>
       </c>
       <c r="B76" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8855,7 +8855,7 @@
         <v>128408858</v>
       </c>
       <c r="B78" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9071,7 +9071,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128406731</v>
+        <v>128416919</v>
       </c>
       <c r="B80" t="n">
         <v>8450</v>
@@ -9111,10 +9111,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>427073</v>
+        <v>426842</v>
       </c>
       <c r="R80" t="n">
-        <v>6784548</v>
+        <v>6784214</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9146,7 +9146,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9156,7 +9156,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9183,7 +9183,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128416919</v>
+        <v>128408778</v>
       </c>
       <c r="B81" t="n">
         <v>8450</v>
@@ -9214,7 +9214,7 @@
       <c r="I81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -9223,10 +9223,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>426842</v>
+        <v>427123</v>
       </c>
       <c r="R81" t="n">
-        <v>6784214</v>
+        <v>6784697</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9258,7 +9258,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9268,7 +9268,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9295,7 +9295,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128408778</v>
+        <v>128406731</v>
       </c>
       <c r="B82" t="n">
         <v>8450</v>
@@ -9326,7 +9326,7 @@
       <c r="I82" t="inlineStr"/>
       <c r="M82" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -9335,10 +9335,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>427123</v>
+        <v>427073</v>
       </c>
       <c r="R82" t="n">
-        <v>6784697</v>
+        <v>6784548</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9370,7 +9370,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9380,7 +9380,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9407,10 +9407,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128409945</v>
+        <v>128404878</v>
       </c>
       <c r="B83" t="n">
-        <v>78874</v>
+        <v>57713</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9418,34 +9418,39 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>427084</v>
+        <v>426879</v>
       </c>
       <c r="R83" t="n">
-        <v>6784718</v>
+        <v>6784490</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9477,7 +9482,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9487,7 +9492,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9514,10 +9519,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128404878</v>
+        <v>128409945</v>
       </c>
       <c r="B84" t="n">
-        <v>57713</v>
+        <v>78878</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9525,39 +9530,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>426879</v>
+        <v>427084</v>
       </c>
       <c r="R84" t="n">
-        <v>6784490</v>
+        <v>6784718</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9589,7 +9589,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9599,7 +9599,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9629,7 +9629,7 @@
         <v>128407168</v>
       </c>
       <c r="B85" t="n">
-        <v>78874</v>
+        <v>78878</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9736,7 +9736,7 @@
         <v>128416596</v>
       </c>
       <c r="B86" t="n">
-        <v>79735</v>
+        <v>79739</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9840,10 +9840,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128406999</v>
+        <v>128416502</v>
       </c>
       <c r="B87" t="n">
-        <v>78874</v>
+        <v>78878</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9875,10 +9875,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>427083</v>
+        <v>426841</v>
       </c>
       <c r="R87" t="n">
-        <v>6784551</v>
+        <v>6784169</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9910,7 +9910,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9920,7 +9920,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9947,10 +9947,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128416502</v>
+        <v>128406999</v>
       </c>
       <c r="B88" t="n">
-        <v>78874</v>
+        <v>78878</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9982,10 +9982,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>426841</v>
+        <v>427083</v>
       </c>
       <c r="R88" t="n">
-        <v>6784169</v>
+        <v>6784551</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10017,7 +10017,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10027,7 +10027,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10057,7 +10057,7 @@
         <v>128416791</v>
       </c>
       <c r="B89" t="n">
-        <v>78874</v>
+        <v>78878</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10164,7 +10164,7 @@
         <v>128417147</v>
       </c>
       <c r="B90" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10271,7 +10271,7 @@
         <v>128417068</v>
       </c>
       <c r="B91" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10487,10 +10487,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128410027</v>
+        <v>128406985</v>
       </c>
       <c r="B93" t="n">
-        <v>91514</v>
+        <v>78877</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10498,41 +10498,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>5442</v>
+        <v>6446</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>427093</v>
+        <v>427087</v>
       </c>
       <c r="R93" t="n">
-        <v>6784727</v>
+        <v>6784548</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10564,7 +10557,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10574,7 +10567,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10583,7 +10576,6 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -10602,50 +10594,45 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128410598</v>
+        <v>128410456</v>
       </c>
       <c r="B94" t="n">
-        <v>8450</v>
+        <v>79120</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>426922</v>
+        <v>426882</v>
       </c>
       <c r="R94" t="n">
-        <v>6784576</v>
+        <v>6784648</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10677,7 +10664,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10687,7 +10674,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10714,50 +10701,52 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128404859</v>
+        <v>128410027</v>
       </c>
       <c r="B95" t="n">
-        <v>8450</v>
+        <v>91524</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>426869</v>
+        <v>427093</v>
       </c>
       <c r="R95" t="n">
-        <v>6784461</v>
+        <v>6784727</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10789,7 +10778,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10799,7 +10788,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10808,6 +10797,7 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10826,45 +10816,50 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128406985</v>
+        <v>128404859</v>
       </c>
       <c r="B96" t="n">
-        <v>78873</v>
+        <v>8450</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>427087</v>
+        <v>426869</v>
       </c>
       <c r="R96" t="n">
-        <v>6784548</v>
+        <v>6784461</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10896,7 +10891,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10906,7 +10901,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10933,45 +10928,50 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128410456</v>
+        <v>128410598</v>
       </c>
       <c r="B97" t="n">
-        <v>79116</v>
+        <v>8450</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>426882</v>
+        <v>426922</v>
       </c>
       <c r="R97" t="n">
-        <v>6784648</v>
+        <v>6784576</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11003,7 +11003,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11013,7 +11013,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11043,7 +11043,7 @@
         <v>128410868</v>
       </c>
       <c r="B98" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11259,50 +11259,45 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128410908</v>
+        <v>128411027</v>
       </c>
       <c r="B100" t="n">
-        <v>8450</v>
+        <v>79120</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>426908</v>
+        <v>426858</v>
       </c>
       <c r="R100" t="n">
-        <v>6784511</v>
+        <v>6784514</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11334,7 +11329,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11344,7 +11339,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11371,45 +11366,50 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128411027</v>
+        <v>128410908</v>
       </c>
       <c r="B101" t="n">
-        <v>79116</v>
+        <v>8450</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>426858</v>
+        <v>426908</v>
       </c>
       <c r="R101" t="n">
-        <v>6784514</v>
+        <v>6784511</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11441,7 +11441,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11451,7 +11451,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11481,7 +11481,7 @@
         <v>128416713</v>
       </c>
       <c r="B102" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11588,7 +11588,7 @@
         <v>128408932</v>
       </c>
       <c r="B103" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11695,7 +11695,7 @@
         <v>128407898</v>
       </c>
       <c r="B104" t="n">
-        <v>78873</v>
+        <v>78877</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11802,7 +11802,7 @@
         <v>128409925</v>
       </c>
       <c r="B105" t="n">
-        <v>79706</v>
+        <v>79710</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11909,7 +11909,7 @@
         <v>128416606</v>
       </c>
       <c r="B106" t="n">
-        <v>78873</v>
+        <v>78877</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12016,7 +12016,7 @@
         <v>128407848</v>
       </c>
       <c r="B107" t="n">
-        <v>78874</v>
+        <v>78878</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>

--- a/artfynd/A 36371-2025 artfynd.xlsx
+++ b/artfynd/A 36371-2025 artfynd.xlsx
@@ -2693,10 +2693,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128414481</v>
+        <v>128411184</v>
       </c>
       <c r="B21" t="n">
-        <v>79739</v>
+        <v>78878</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2704,34 +2704,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>426524</v>
+        <v>426819</v>
       </c>
       <c r="R21" t="n">
-        <v>6784260</v>
+        <v>6784515</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2763,7 +2763,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2773,7 +2773,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2800,7 +2800,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128415595</v>
+        <v>128415015</v>
       </c>
       <c r="B22" t="n">
         <v>79120</v>
@@ -2835,10 +2835,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>426618</v>
+        <v>426548</v>
       </c>
       <c r="R22" t="n">
-        <v>6784050</v>
+        <v>6784175</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2870,7 +2870,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2880,7 +2880,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2907,10 +2907,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128415015</v>
+        <v>128414172</v>
       </c>
       <c r="B23" t="n">
-        <v>79120</v>
+        <v>78877</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2918,21 +2918,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2942,10 +2942,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>426548</v>
+        <v>426541</v>
       </c>
       <c r="R23" t="n">
-        <v>6784175</v>
+        <v>6784302</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2977,7 +2977,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2987,7 +2987,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3014,7 +3014,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128414172</v>
+        <v>128418402</v>
       </c>
       <c r="B24" t="n">
         <v>78877</v>
@@ -3049,10 +3049,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>426541</v>
+        <v>426596</v>
       </c>
       <c r="R24" t="n">
-        <v>6784302</v>
+        <v>6784364</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3121,10 +3121,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128418402</v>
+        <v>128414481</v>
       </c>
       <c r="B25" t="n">
-        <v>78877</v>
+        <v>79739</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3132,21 +3132,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3156,10 +3156,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>426596</v>
+        <v>426524</v>
       </c>
       <c r="R25" t="n">
-        <v>6784364</v>
+        <v>6784260</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3191,7 +3191,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3201,7 +3201,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3228,10 +3228,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128411184</v>
+        <v>128415595</v>
       </c>
       <c r="B26" t="n">
-        <v>78878</v>
+        <v>79120</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3239,34 +3239,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>426819</v>
+        <v>426618</v>
       </c>
       <c r="R26" t="n">
-        <v>6784515</v>
+        <v>6784050</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3298,7 +3298,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3308,7 +3308,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4420,45 +4420,50 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128412524</v>
+        <v>128404418</v>
       </c>
       <c r="B37" t="n">
-        <v>79120</v>
+        <v>8450</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>426466</v>
+        <v>426715</v>
       </c>
       <c r="R37" t="n">
-        <v>6784510</v>
+        <v>6784397</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4490,7 +4495,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4500,7 +4505,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4634,50 +4639,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128404418</v>
+        <v>128412524</v>
       </c>
       <c r="B39" t="n">
-        <v>8450</v>
+        <v>79120</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>426715</v>
+        <v>426466</v>
       </c>
       <c r="R39" t="n">
-        <v>6784397</v>
+        <v>6784510</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4709,7 +4709,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4719,7 +4719,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -6030,7 +6030,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128414874</v>
+        <v>128415767</v>
       </c>
       <c r="B52" t="n">
         <v>8450</v>
@@ -6061,7 +6061,7 @@
       <c r="I52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -6070,10 +6070,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>426535</v>
+        <v>426618</v>
       </c>
       <c r="R52" t="n">
-        <v>6784210</v>
+        <v>6784050</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6105,7 +6105,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6115,7 +6115,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6142,7 +6142,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128415767</v>
+        <v>128414874</v>
       </c>
       <c r="B53" t="n">
         <v>8450</v>
@@ -6173,7 +6173,7 @@
       <c r="I53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6182,10 +6182,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>426618</v>
+        <v>426535</v>
       </c>
       <c r="R53" t="n">
-        <v>6784050</v>
+        <v>6784210</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6217,7 +6217,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6227,7 +6227,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6254,10 +6254,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128415267</v>
+        <v>128413992</v>
       </c>
       <c r="B54" t="n">
-        <v>78878</v>
+        <v>79120</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6265,21 +6265,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6289,10 +6289,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>426604</v>
+        <v>426519</v>
       </c>
       <c r="R54" t="n">
-        <v>6784093</v>
+        <v>6784308</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6324,7 +6324,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6468,10 +6468,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128413992</v>
+        <v>128415267</v>
       </c>
       <c r="B56" t="n">
-        <v>79120</v>
+        <v>78878</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6479,21 +6479,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6503,10 +6503,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>426519</v>
+        <v>426604</v>
       </c>
       <c r="R56" t="n">
-        <v>6784308</v>
+        <v>6784093</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6538,7 +6538,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6548,7 +6548,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6682,10 +6682,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128418258</v>
+        <v>128415393</v>
       </c>
       <c r="B58" t="n">
-        <v>79120</v>
+        <v>79739</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6693,21 +6693,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6717,10 +6717,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>426632</v>
+        <v>426601</v>
       </c>
       <c r="R58" t="n">
-        <v>6784364</v>
+        <v>6784100</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6752,7 +6752,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6762,7 +6762,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6789,10 +6789,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128415393</v>
+        <v>128418258</v>
       </c>
       <c r="B59" t="n">
-        <v>79739</v>
+        <v>79120</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6800,21 +6800,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6824,10 +6824,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>426601</v>
+        <v>426632</v>
       </c>
       <c r="R59" t="n">
-        <v>6784100</v>
+        <v>6784364</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6859,7 +6859,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6869,7 +6869,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6896,45 +6896,50 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128416385</v>
+        <v>128404480</v>
       </c>
       <c r="B60" t="n">
-        <v>79739</v>
+        <v>8450</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>426796</v>
+        <v>426773</v>
       </c>
       <c r="R60" t="n">
-        <v>6784156</v>
+        <v>6784434</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6966,7 +6971,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6976,7 +6981,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7003,50 +7008,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128404480</v>
+        <v>128416385</v>
       </c>
       <c r="B61" t="n">
-        <v>8450</v>
+        <v>79739</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>426773</v>
+        <v>426796</v>
       </c>
       <c r="R61" t="n">
-        <v>6784434</v>
+        <v>6784156</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7078,7 +7078,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7088,7 +7088,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7660,10 +7660,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128413310</v>
+        <v>128413333</v>
       </c>
       <c r="B67" t="n">
-        <v>57713</v>
+        <v>78877</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7671,39 +7671,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>426477</v>
+        <v>426459</v>
       </c>
       <c r="R67" t="n">
-        <v>6784397</v>
+        <v>6784412</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7735,7 +7730,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7745,7 +7740,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7772,10 +7767,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128413333</v>
+        <v>128413310</v>
       </c>
       <c r="B68" t="n">
-        <v>78877</v>
+        <v>57713</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7783,34 +7778,39 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>426459</v>
+        <v>426477</v>
       </c>
       <c r="R68" t="n">
-        <v>6784412</v>
+        <v>6784397</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7842,7 +7842,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7852,7 +7852,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7991,7 +7991,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128417205</v>
+        <v>128418292</v>
       </c>
       <c r="B70" t="n">
         <v>79120</v>
@@ -8022,14 +8022,14 @@
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>426813</v>
+        <v>426624</v>
       </c>
       <c r="R70" t="n">
-        <v>6784276</v>
+        <v>6784361</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8061,7 +8061,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8071,7 +8071,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav på tallarna på en radie av 50 meter.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8098,7 +8103,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128418292</v>
+        <v>128417205</v>
       </c>
       <c r="B71" t="n">
         <v>79120</v>
@@ -8129,14 +8134,14 @@
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>426624</v>
+        <v>426813</v>
       </c>
       <c r="R71" t="n">
-        <v>6784361</v>
+        <v>6784276</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8168,7 +8173,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8178,12 +8183,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>18:45</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav på tallarna på en radie av 50 meter.</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8633,45 +8633,50 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128410669</v>
+        <v>128409845</v>
       </c>
       <c r="B76" t="n">
-        <v>79120</v>
+        <v>8450</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>426922</v>
+        <v>427064</v>
       </c>
       <c r="R76" t="n">
-        <v>6784529</v>
+        <v>6784664</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8703,7 +8708,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8713,7 +8718,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8740,50 +8745,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128409845</v>
+        <v>128410669</v>
       </c>
       <c r="B77" t="n">
-        <v>8450</v>
+        <v>79120</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>427064</v>
+        <v>426922</v>
       </c>
       <c r="R77" t="n">
-        <v>6784664</v>
+        <v>6784529</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8815,7 +8815,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8825,7 +8825,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9407,10 +9407,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128404878</v>
+        <v>128409945</v>
       </c>
       <c r="B83" t="n">
-        <v>57713</v>
+        <v>78878</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9418,39 +9418,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>426879</v>
+        <v>427084</v>
       </c>
       <c r="R83" t="n">
-        <v>6784490</v>
+        <v>6784718</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9482,7 +9477,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9492,7 +9487,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9519,10 +9514,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128409945</v>
+        <v>128404878</v>
       </c>
       <c r="B84" t="n">
-        <v>78878</v>
+        <v>57713</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9530,34 +9525,39 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>427084</v>
+        <v>426879</v>
       </c>
       <c r="R84" t="n">
-        <v>6784718</v>
+        <v>6784490</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9589,7 +9589,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9599,7 +9599,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9840,7 +9840,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128416502</v>
+        <v>128406999</v>
       </c>
       <c r="B87" t="n">
         <v>78878</v>
@@ -9875,10 +9875,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>426841</v>
+        <v>427083</v>
       </c>
       <c r="R87" t="n">
-        <v>6784169</v>
+        <v>6784551</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9910,7 +9910,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9920,7 +9920,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9947,7 +9947,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128406999</v>
+        <v>128416502</v>
       </c>
       <c r="B88" t="n">
         <v>78878</v>
@@ -9982,10 +9982,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>427083</v>
+        <v>426841</v>
       </c>
       <c r="R88" t="n">
-        <v>6784551</v>
+        <v>6784169</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10017,7 +10017,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10027,7 +10027,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10487,10 +10487,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128406985</v>
+        <v>128410027</v>
       </c>
       <c r="B93" t="n">
-        <v>78877</v>
+        <v>91524</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10498,34 +10498,41 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6446</v>
+        <v>5442</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>427087</v>
+        <v>427093</v>
       </c>
       <c r="R93" t="n">
-        <v>6784548</v>
+        <v>6784727</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10557,7 +10564,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10567,7 +10574,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10576,6 +10583,7 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -10594,45 +10602,50 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128410456</v>
+        <v>128410598</v>
       </c>
       <c r="B94" t="n">
-        <v>79120</v>
+        <v>8450</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>426882</v>
+        <v>426922</v>
       </c>
       <c r="R94" t="n">
-        <v>6784648</v>
+        <v>6784576</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10664,7 +10677,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10674,7 +10687,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10701,52 +10714,50 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128410027</v>
+        <v>128404859</v>
       </c>
       <c r="B95" t="n">
-        <v>91524</v>
+        <v>8450</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>427093</v>
+        <v>426869</v>
       </c>
       <c r="R95" t="n">
-        <v>6784727</v>
+        <v>6784461</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10778,7 +10789,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10788,7 +10799,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10797,7 +10808,6 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10816,50 +10826,45 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128404859</v>
+        <v>128406985</v>
       </c>
       <c r="B96" t="n">
-        <v>8450</v>
+        <v>78877</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>426869</v>
+        <v>427087</v>
       </c>
       <c r="R96" t="n">
-        <v>6784461</v>
+        <v>6784548</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10891,7 +10896,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10901,7 +10906,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10928,50 +10933,45 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128410598</v>
+        <v>128410456</v>
       </c>
       <c r="B97" t="n">
-        <v>8450</v>
+        <v>79120</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>426922</v>
+        <v>426882</v>
       </c>
       <c r="R97" t="n">
-        <v>6784576</v>
+        <v>6784648</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11003,7 +11003,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11013,7 +11013,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD97" t="b">

--- a/artfynd/A 36371-2025 artfynd.xlsx
+++ b/artfynd/A 36371-2025 artfynd.xlsx
@@ -4420,50 +4420,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128404418</v>
+        <v>128412524</v>
       </c>
       <c r="B37" t="n">
-        <v>8450</v>
+        <v>79120</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>426715</v>
+        <v>426466</v>
       </c>
       <c r="R37" t="n">
-        <v>6784397</v>
+        <v>6784510</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4495,7 +4490,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4505,7 +4500,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4532,45 +4527,50 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128414383</v>
+        <v>128404418</v>
       </c>
       <c r="B38" t="n">
-        <v>78878</v>
+        <v>8450</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>426509</v>
+        <v>426715</v>
       </c>
       <c r="R38" t="n">
-        <v>6784270</v>
+        <v>6784397</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4602,7 +4602,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4612,7 +4612,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4639,10 +4639,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128412524</v>
+        <v>128414383</v>
       </c>
       <c r="B39" t="n">
-        <v>79120</v>
+        <v>78878</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4650,21 +4650,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4674,10 +4674,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>426466</v>
+        <v>426509</v>
       </c>
       <c r="R39" t="n">
-        <v>6784510</v>
+        <v>6784270</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4709,7 +4709,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4719,7 +4719,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -6254,10 +6254,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128413992</v>
+        <v>128415267</v>
       </c>
       <c r="B54" t="n">
-        <v>79120</v>
+        <v>78878</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6265,21 +6265,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6289,10 +6289,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>426519</v>
+        <v>426604</v>
       </c>
       <c r="R54" t="n">
-        <v>6784308</v>
+        <v>6784093</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6324,7 +6324,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6361,7 +6361,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128418647</v>
+        <v>128413992</v>
       </c>
       <c r="B55" t="n">
         <v>79120</v>
@@ -6396,10 +6396,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>426573</v>
+        <v>426519</v>
       </c>
       <c r="R55" t="n">
-        <v>6784376</v>
+        <v>6784308</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>18:59</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6441,7 +6441,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>18:59</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6468,10 +6468,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128415267</v>
+        <v>128418647</v>
       </c>
       <c r="B56" t="n">
-        <v>78878</v>
+        <v>79120</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6479,21 +6479,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6503,10 +6503,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>426604</v>
+        <v>426573</v>
       </c>
       <c r="R56" t="n">
-        <v>6784093</v>
+        <v>6784376</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6538,7 +6538,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>18:59</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6548,7 +6548,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>18:59</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7660,45 +7660,50 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128413333</v>
+        <v>128417436</v>
       </c>
       <c r="B67" t="n">
-        <v>78877</v>
+        <v>8450</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>426459</v>
+        <v>426801</v>
       </c>
       <c r="R67" t="n">
-        <v>6784412</v>
+        <v>6784284</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7730,7 +7735,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7740,7 +7745,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7767,10 +7772,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128413310</v>
+        <v>128413333</v>
       </c>
       <c r="B68" t="n">
-        <v>57713</v>
+        <v>78877</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7778,39 +7783,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>426477</v>
+        <v>426459</v>
       </c>
       <c r="R68" t="n">
-        <v>6784397</v>
+        <v>6784412</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7842,7 +7842,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7852,7 +7852,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7879,50 +7879,50 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128417436</v>
+        <v>128413310</v>
       </c>
       <c r="B69" t="n">
-        <v>8450</v>
+        <v>57713</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>426801</v>
+        <v>426477</v>
       </c>
       <c r="R69" t="n">
-        <v>6784284</v>
+        <v>6784397</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7954,7 +7954,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7964,7 +7964,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7991,7 +7991,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128418292</v>
+        <v>128417205</v>
       </c>
       <c r="B70" t="n">
         <v>79120</v>
@@ -8022,14 +8022,14 @@
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>426624</v>
+        <v>426813</v>
       </c>
       <c r="R70" t="n">
-        <v>6784361</v>
+        <v>6784276</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8061,7 +8061,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8071,12 +8071,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>18:45</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav på tallarna på en radie av 50 meter.</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8103,7 +8098,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128417205</v>
+        <v>128418292</v>
       </c>
       <c r="B71" t="n">
         <v>79120</v>
@@ -8134,14 +8129,14 @@
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>426813</v>
+        <v>426624</v>
       </c>
       <c r="R71" t="n">
-        <v>6784276</v>
+        <v>6784361</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8173,7 +8168,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8183,7 +8178,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav på tallarna på en radie av 50 meter.</t>
         </is>
       </c>
       <c r="AD71" t="b">

--- a/artfynd/A 36371-2025 artfynd.xlsx
+++ b/artfynd/A 36371-2025 artfynd.xlsx
@@ -2693,10 +2693,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128411184</v>
+        <v>128415595</v>
       </c>
       <c r="B21" t="n">
-        <v>78878</v>
+        <v>79120</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2704,34 +2704,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>426819</v>
+        <v>426618</v>
       </c>
       <c r="R21" t="n">
-        <v>6784515</v>
+        <v>6784050</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2763,7 +2763,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2773,7 +2773,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2800,10 +2800,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128415015</v>
+        <v>128414172</v>
       </c>
       <c r="B22" t="n">
-        <v>79120</v>
+        <v>78877</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2811,21 +2811,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2835,10 +2835,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>426548</v>
+        <v>426541</v>
       </c>
       <c r="R22" t="n">
-        <v>6784175</v>
+        <v>6784302</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2870,7 +2870,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2880,7 +2880,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2907,7 +2907,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128414172</v>
+        <v>128418402</v>
       </c>
       <c r="B23" t="n">
         <v>78877</v>
@@ -2942,10 +2942,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>426541</v>
+        <v>426596</v>
       </c>
       <c r="R23" t="n">
-        <v>6784302</v>
+        <v>6784364</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2977,7 +2977,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2987,7 +2987,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3014,10 +3014,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128418402</v>
+        <v>128414481</v>
       </c>
       <c r="B24" t="n">
-        <v>78877</v>
+        <v>79739</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3025,21 +3025,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3049,10 +3049,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>426596</v>
+        <v>426524</v>
       </c>
       <c r="R24" t="n">
-        <v>6784364</v>
+        <v>6784260</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3121,10 +3121,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128414481</v>
+        <v>128415015</v>
       </c>
       <c r="B25" t="n">
-        <v>79739</v>
+        <v>79120</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3132,21 +3132,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3156,10 +3156,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>426524</v>
+        <v>426548</v>
       </c>
       <c r="R25" t="n">
-        <v>6784260</v>
+        <v>6784175</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3191,7 +3191,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3201,7 +3201,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3228,10 +3228,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128415595</v>
+        <v>128411184</v>
       </c>
       <c r="B26" t="n">
-        <v>79120</v>
+        <v>78878</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3239,34 +3239,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>426618</v>
+        <v>426819</v>
       </c>
       <c r="R26" t="n">
-        <v>6784050</v>
+        <v>6784515</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3298,7 +3298,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3308,7 +3308,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3768,10 +3768,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128413169</v>
+        <v>128418215</v>
       </c>
       <c r="B31" t="n">
-        <v>79120</v>
+        <v>78878</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3779,21 +3779,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3803,10 +3803,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>426555</v>
+        <v>426655</v>
       </c>
       <c r="R31" t="n">
-        <v>6784393</v>
+        <v>6784360</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3875,38 +3875,38 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128414306</v>
+        <v>128413945</v>
       </c>
       <c r="B32" t="n">
-        <v>57713</v>
+        <v>8450</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -3915,10 +3915,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>426519</v>
+        <v>426498</v>
       </c>
       <c r="R32" t="n">
-        <v>6784286</v>
+        <v>6784322</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3950,7 +3950,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3987,38 +3987,38 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128413945</v>
+        <v>128414306</v>
       </c>
       <c r="B33" t="n">
-        <v>8450</v>
+        <v>57713</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4027,10 +4027,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>426498</v>
+        <v>426519</v>
       </c>
       <c r="R33" t="n">
-        <v>6784322</v>
+        <v>6784286</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4099,10 +4099,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128418215</v>
+        <v>128413169</v>
       </c>
       <c r="B34" t="n">
-        <v>78878</v>
+        <v>79120</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4110,21 +4110,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>426655</v>
+        <v>426555</v>
       </c>
       <c r="R34" t="n">
-        <v>6784360</v>
+        <v>6784393</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4420,45 +4420,50 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128412524</v>
+        <v>128404418</v>
       </c>
       <c r="B37" t="n">
-        <v>79120</v>
+        <v>8450</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>426466</v>
+        <v>426715</v>
       </c>
       <c r="R37" t="n">
-        <v>6784510</v>
+        <v>6784397</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4490,7 +4495,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4500,7 +4505,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4527,50 +4532,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128404418</v>
+        <v>128414383</v>
       </c>
       <c r="B38" t="n">
-        <v>8450</v>
+        <v>78878</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>426715</v>
+        <v>426509</v>
       </c>
       <c r="R38" t="n">
-        <v>6784397</v>
+        <v>6784270</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4602,7 +4602,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4612,7 +4612,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4639,10 +4639,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128414383</v>
+        <v>128412524</v>
       </c>
       <c r="B39" t="n">
-        <v>78878</v>
+        <v>79120</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4650,21 +4650,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4674,10 +4674,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>426509</v>
+        <v>426466</v>
       </c>
       <c r="R39" t="n">
-        <v>6784270</v>
+        <v>6784510</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4709,7 +4709,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4719,7 +4719,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4746,10 +4746,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128418704</v>
+        <v>128415503</v>
       </c>
       <c r="B40" t="n">
-        <v>78877</v>
+        <v>79120</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4757,21 +4757,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4781,10 +4781,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>426573</v>
+        <v>426605</v>
       </c>
       <c r="R40" t="n">
-        <v>6784360</v>
+        <v>6784090</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4853,10 +4853,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128418719</v>
+        <v>128418704</v>
       </c>
       <c r="B41" t="n">
-        <v>79120</v>
+        <v>78877</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4864,21 +4864,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4888,10 +4888,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>426571</v>
+        <v>426573</v>
       </c>
       <c r="R41" t="n">
-        <v>6784357</v>
+        <v>6784360</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4933,7 +4933,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4960,7 +4960,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128418198</v>
+        <v>128418719</v>
       </c>
       <c r="B42" t="n">
         <v>79120</v>
@@ -4995,10 +4995,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>426656</v>
+        <v>426571</v>
       </c>
       <c r="R42" t="n">
-        <v>6784360</v>
+        <v>6784357</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5030,7 +5030,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5040,7 +5040,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5067,7 +5067,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128413197</v>
+        <v>128418198</v>
       </c>
       <c r="B43" t="n">
         <v>79120</v>
@@ -5102,10 +5102,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>426532</v>
+        <v>426656</v>
       </c>
       <c r="R43" t="n">
-        <v>6784390</v>
+        <v>6784360</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5137,7 +5137,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5147,7 +5147,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5174,7 +5174,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128415503</v>
+        <v>128413197</v>
       </c>
       <c r="B44" t="n">
         <v>79120</v>
@@ -5209,10 +5209,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>426605</v>
+        <v>426532</v>
       </c>
       <c r="R44" t="n">
-        <v>6784090</v>
+        <v>6784390</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5244,7 +5244,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5254,7 +5254,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5388,10 +5388,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128413145</v>
+        <v>128416206</v>
       </c>
       <c r="B46" t="n">
-        <v>79120</v>
+        <v>78877</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5399,34 +5399,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>426534</v>
+        <v>426760</v>
       </c>
       <c r="R46" t="n">
-        <v>6784406</v>
+        <v>6784153</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5458,7 +5458,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5468,7 +5468,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5495,10 +5495,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128416206</v>
+        <v>128413145</v>
       </c>
       <c r="B47" t="n">
-        <v>78877</v>
+        <v>79120</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5506,34 +5506,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>426760</v>
+        <v>426534</v>
       </c>
       <c r="R47" t="n">
-        <v>6784153</v>
+        <v>6784406</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5565,7 +5565,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5575,7 +5575,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6361,7 +6361,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128413992</v>
+        <v>128418647</v>
       </c>
       <c r="B55" t="n">
         <v>79120</v>
@@ -6396,10 +6396,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>426519</v>
+        <v>426573</v>
       </c>
       <c r="R55" t="n">
-        <v>6784308</v>
+        <v>6784376</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>18:59</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6441,7 +6441,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>18:59</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6468,7 +6468,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128418647</v>
+        <v>128413992</v>
       </c>
       <c r="B56" t="n">
         <v>79120</v>
@@ -6503,10 +6503,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>426573</v>
+        <v>426519</v>
       </c>
       <c r="R56" t="n">
-        <v>6784376</v>
+        <v>6784308</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6538,7 +6538,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>18:59</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6548,7 +6548,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>18:59</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7436,7 +7436,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128415117</v>
+        <v>128416277</v>
       </c>
       <c r="B65" t="n">
         <v>8450</v>
@@ -7472,14 +7472,14 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>426554</v>
+        <v>426797</v>
       </c>
       <c r="R65" t="n">
-        <v>6784161</v>
+        <v>6784155</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7511,7 +7511,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7521,7 +7521,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7548,7 +7548,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128416277</v>
+        <v>128415117</v>
       </c>
       <c r="B66" t="n">
         <v>8450</v>
@@ -7584,14 +7584,14 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>426797</v>
+        <v>426554</v>
       </c>
       <c r="R66" t="n">
-        <v>6784155</v>
+        <v>6784161</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7623,7 +7623,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7633,7 +7633,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8317,50 +8317,45 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128414247</v>
+        <v>128413213</v>
       </c>
       <c r="B73" t="n">
-        <v>8450</v>
+        <v>78878</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>426535</v>
+        <v>426524</v>
       </c>
       <c r="R73" t="n">
-        <v>6784292</v>
+        <v>6784388</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8392,7 +8387,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8402,7 +8397,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8429,45 +8424,50 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128413213</v>
+        <v>128414247</v>
       </c>
       <c r="B74" t="n">
-        <v>78878</v>
+        <v>8450</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>426524</v>
+        <v>426535</v>
       </c>
       <c r="R74" t="n">
-        <v>6784388</v>
+        <v>6784292</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8499,7 +8499,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8509,7 +8509,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8633,50 +8633,45 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128409845</v>
+        <v>128410669</v>
       </c>
       <c r="B76" t="n">
-        <v>8450</v>
+        <v>79120</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>427064</v>
+        <v>426922</v>
       </c>
       <c r="R76" t="n">
-        <v>6784664</v>
+        <v>6784529</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8708,7 +8703,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8718,7 +8713,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8745,45 +8740,50 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128410669</v>
+        <v>128409845</v>
       </c>
       <c r="B77" t="n">
-        <v>79120</v>
+        <v>8450</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>426922</v>
+        <v>427064</v>
       </c>
       <c r="R77" t="n">
-        <v>6784529</v>
+        <v>6784664</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8815,7 +8815,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8825,7 +8825,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8852,45 +8852,50 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128408858</v>
+        <v>128406731</v>
       </c>
       <c r="B78" t="n">
-        <v>79120</v>
+        <v>8450</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>427123</v>
+        <v>427073</v>
       </c>
       <c r="R78" t="n">
-        <v>6784697</v>
+        <v>6784548</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8922,7 +8927,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8932,7 +8937,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8959,38 +8964,38 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128410625</v>
+        <v>128416919</v>
       </c>
       <c r="B79" t="n">
-        <v>57713</v>
+        <v>8450</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="M79" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -8999,13 +9004,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>426917</v>
+        <v>426842</v>
       </c>
       <c r="R79" t="n">
-        <v>6784579</v>
+        <v>6784214</v>
       </c>
       <c r="S79" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9034,7 +9039,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9044,7 +9049,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9071,7 +9076,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128416919</v>
+        <v>128408778</v>
       </c>
       <c r="B80" t="n">
         <v>8450</v>
@@ -9102,7 +9107,7 @@
       <c r="I80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -9111,10 +9116,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>426842</v>
+        <v>427123</v>
       </c>
       <c r="R80" t="n">
-        <v>6784214</v>
+        <v>6784697</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9146,7 +9151,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9156,7 +9161,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9183,40 +9188,35 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128408778</v>
+        <v>128408858</v>
       </c>
       <c r="B81" t="n">
-        <v>8450</v>
+        <v>79120</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
@@ -9258,7 +9258,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9268,7 +9268,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9295,38 +9295,38 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128406731</v>
+        <v>128410625</v>
       </c>
       <c r="B82" t="n">
-        <v>8450</v>
+        <v>57713</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="M82" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -9335,13 +9335,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>427073</v>
+        <v>426917</v>
       </c>
       <c r="R82" t="n">
-        <v>6784548</v>
+        <v>6784579</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9370,7 +9370,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9380,7 +9380,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10487,52 +10487,50 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128410027</v>
+        <v>128410598</v>
       </c>
       <c r="B93" t="n">
-        <v>91524</v>
+        <v>8450</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>427093</v>
+        <v>426922</v>
       </c>
       <c r="R93" t="n">
-        <v>6784727</v>
+        <v>6784576</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10564,7 +10562,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10574,7 +10572,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10583,7 +10581,6 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -10602,7 +10599,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128410598</v>
+        <v>128404859</v>
       </c>
       <c r="B94" t="n">
         <v>8450</v>
@@ -10642,10 +10639,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>426922</v>
+        <v>426869</v>
       </c>
       <c r="R94" t="n">
-        <v>6784576</v>
+        <v>6784461</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10677,7 +10674,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10687,7 +10684,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10714,50 +10711,52 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128404859</v>
+        <v>128410027</v>
       </c>
       <c r="B95" t="n">
-        <v>8450</v>
+        <v>91524</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>426869</v>
+        <v>427093</v>
       </c>
       <c r="R95" t="n">
-        <v>6784461</v>
+        <v>6784727</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10789,7 +10788,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10799,7 +10798,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10808,6 +10807,7 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -11259,45 +11259,50 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128411027</v>
+        <v>128410908</v>
       </c>
       <c r="B100" t="n">
-        <v>79120</v>
+        <v>8450</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>426858</v>
+        <v>426908</v>
       </c>
       <c r="R100" t="n">
-        <v>6784514</v>
+        <v>6784511</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11329,7 +11334,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11339,7 +11344,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11366,50 +11371,45 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128410908</v>
+        <v>128411027</v>
       </c>
       <c r="B101" t="n">
-        <v>8450</v>
+        <v>79120</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>426908</v>
+        <v>426858</v>
       </c>
       <c r="R101" t="n">
-        <v>6784511</v>
+        <v>6784514</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11441,7 +11441,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11451,7 +11451,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11478,7 +11478,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128416713</v>
+        <v>128408932</v>
       </c>
       <c r="B102" t="n">
         <v>79120</v>
@@ -11513,10 +11513,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>426849</v>
+        <v>427081</v>
       </c>
       <c r="R102" t="n">
-        <v>6784145</v>
+        <v>6784657</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11548,7 +11548,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11558,7 +11558,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11585,7 +11585,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128408932</v>
+        <v>128416713</v>
       </c>
       <c r="B103" t="n">
         <v>79120</v>
@@ -11620,10 +11620,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>427081</v>
+        <v>426849</v>
       </c>
       <c r="R103" t="n">
-        <v>6784657</v>
+        <v>6784145</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11655,7 +11655,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11665,7 +11665,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11906,10 +11906,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128416606</v>
+        <v>128407848</v>
       </c>
       <c r="B106" t="n">
-        <v>78877</v>
+        <v>78878</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11917,21 +11917,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11941,10 +11941,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>426859</v>
+        <v>427064</v>
       </c>
       <c r="R106" t="n">
-        <v>6784153</v>
+        <v>6784585</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11976,7 +11976,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11986,7 +11986,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12013,10 +12013,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128407848</v>
+        <v>128416606</v>
       </c>
       <c r="B107" t="n">
-        <v>78878</v>
+        <v>78877</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12024,21 +12024,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12048,10 +12048,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>427064</v>
+        <v>426859</v>
       </c>
       <c r="R107" t="n">
-        <v>6784585</v>
+        <v>6784153</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12083,7 +12083,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12093,7 +12093,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD107" t="b">

--- a/artfynd/A 36371-2025 artfynd.xlsx
+++ b/artfynd/A 36371-2025 artfynd.xlsx
@@ -2696,7 +2696,7 @@
         <v>128415595</v>
       </c>
       <c r="B21" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128414172</v>
+        <v>128415015</v>
       </c>
       <c r="B22" t="n">
-        <v>78877</v>
+        <v>79124</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2811,21 +2811,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2835,10 +2835,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>426541</v>
+        <v>426548</v>
       </c>
       <c r="R22" t="n">
-        <v>6784302</v>
+        <v>6784175</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2870,7 +2870,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2880,7 +2880,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2907,10 +2907,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128418402</v>
+        <v>128414172</v>
       </c>
       <c r="B23" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2942,10 +2942,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>426596</v>
+        <v>426541</v>
       </c>
       <c r="R23" t="n">
-        <v>6784364</v>
+        <v>6784302</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2977,7 +2977,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2987,7 +2987,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3014,10 +3014,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128414481</v>
+        <v>128418402</v>
       </c>
       <c r="B24" t="n">
-        <v>79739</v>
+        <v>78881</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3025,21 +3025,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3049,10 +3049,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>426524</v>
+        <v>426596</v>
       </c>
       <c r="R24" t="n">
-        <v>6784260</v>
+        <v>6784364</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3121,10 +3121,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128415015</v>
+        <v>128414481</v>
       </c>
       <c r="B25" t="n">
-        <v>79120</v>
+        <v>79743</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3132,21 +3132,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3156,10 +3156,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>426548</v>
+        <v>426524</v>
       </c>
       <c r="R25" t="n">
-        <v>6784175</v>
+        <v>6784260</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3191,7 +3191,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3201,7 +3201,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3231,7 +3231,7 @@
         <v>128411184</v>
       </c>
       <c r="B26" t="n">
-        <v>78878</v>
+        <v>78882</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3335,10 +3335,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128414801</v>
+        <v>128414155</v>
       </c>
       <c r="B27" t="n">
-        <v>79120</v>
+        <v>78882</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3346,21 +3346,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3370,10 +3370,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>426524</v>
+        <v>426540</v>
       </c>
       <c r="R27" t="n">
-        <v>6784260</v>
+        <v>6784305</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3405,7 +3405,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3415,7 +3415,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3442,10 +3442,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128416106</v>
+        <v>128414801</v>
       </c>
       <c r="B28" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3473,14 +3473,14 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>426746</v>
+        <v>426524</v>
       </c>
       <c r="R28" t="n">
-        <v>6784096</v>
+        <v>6784260</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3512,7 +3512,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3522,12 +3522,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:35</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50 meter.</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3554,10 +3549,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128417228</v>
+        <v>128416106</v>
       </c>
       <c r="B29" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3589,10 +3584,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>426801</v>
+        <v>426746</v>
       </c>
       <c r="R29" t="n">
-        <v>6784284</v>
+        <v>6784096</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3624,7 +3619,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3634,7 +3629,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50 meter.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3661,10 +3661,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128414155</v>
+        <v>128417228</v>
       </c>
       <c r="B30" t="n">
-        <v>78878</v>
+        <v>79124</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3672,34 +3672,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>426540</v>
+        <v>426801</v>
       </c>
       <c r="R30" t="n">
-        <v>6784305</v>
+        <v>6784284</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3731,7 +3731,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3768,10 +3768,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128418215</v>
+        <v>128414306</v>
       </c>
       <c r="B31" t="n">
-        <v>78878</v>
+        <v>57717</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3779,34 +3779,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>426655</v>
+        <v>426519</v>
       </c>
       <c r="R31" t="n">
-        <v>6784360</v>
+        <v>6784286</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3838,7 +3843,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3848,7 +3853,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3875,50 +3880,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128413945</v>
+        <v>128413169</v>
       </c>
       <c r="B32" t="n">
-        <v>8450</v>
+        <v>79124</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>426498</v>
+        <v>426555</v>
       </c>
       <c r="R32" t="n">
-        <v>6784322</v>
+        <v>6784393</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3950,7 +3950,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3987,38 +3987,38 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128414306</v>
+        <v>128413945</v>
       </c>
       <c r="B33" t="n">
-        <v>57713</v>
+        <v>8450</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4027,10 +4027,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>426519</v>
+        <v>426498</v>
       </c>
       <c r="R33" t="n">
-        <v>6784286</v>
+        <v>6784322</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4099,10 +4099,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128413169</v>
+        <v>128418215</v>
       </c>
       <c r="B34" t="n">
-        <v>79120</v>
+        <v>78882</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4110,21 +4110,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>426555</v>
+        <v>426655</v>
       </c>
       <c r="R34" t="n">
-        <v>6784393</v>
+        <v>6784360</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4209,7 +4209,7 @@
         <v>128416349</v>
       </c>
       <c r="B35" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4316,7 +4316,7 @@
         <v>128404649</v>
       </c>
       <c r="B36" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4532,10 +4532,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128414383</v>
+        <v>128412524</v>
       </c>
       <c r="B38" t="n">
-        <v>78878</v>
+        <v>79124</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4543,21 +4543,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4567,10 +4567,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>426509</v>
+        <v>426466</v>
       </c>
       <c r="R38" t="n">
-        <v>6784270</v>
+        <v>6784510</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4602,7 +4602,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4612,7 +4612,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4639,10 +4639,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128412524</v>
+        <v>128414383</v>
       </c>
       <c r="B39" t="n">
-        <v>79120</v>
+        <v>78882</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4650,21 +4650,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4674,10 +4674,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>426466</v>
+        <v>426509</v>
       </c>
       <c r="R39" t="n">
-        <v>6784510</v>
+        <v>6784270</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4709,7 +4709,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4719,7 +4719,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4746,10 +4746,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128415503</v>
+        <v>128418704</v>
       </c>
       <c r="B40" t="n">
-        <v>79120</v>
+        <v>78881</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4757,21 +4757,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4781,10 +4781,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>426605</v>
+        <v>426573</v>
       </c>
       <c r="R40" t="n">
-        <v>6784090</v>
+        <v>6784360</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4853,10 +4853,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128418704</v>
+        <v>128418719</v>
       </c>
       <c r="B41" t="n">
-        <v>78877</v>
+        <v>79124</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4864,21 +4864,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4888,10 +4888,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>426573</v>
+        <v>426571</v>
       </c>
       <c r="R41" t="n">
-        <v>6784360</v>
+        <v>6784357</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4933,7 +4933,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4960,10 +4960,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128418719</v>
+        <v>128415503</v>
       </c>
       <c r="B42" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4995,10 +4995,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>426571</v>
+        <v>426605</v>
       </c>
       <c r="R42" t="n">
-        <v>6784357</v>
+        <v>6784090</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5030,7 +5030,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5040,7 +5040,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5070,7 +5070,7 @@
         <v>128418198</v>
       </c>
       <c r="B43" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5177,7 +5177,7 @@
         <v>128413197</v>
       </c>
       <c r="B44" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5284,7 +5284,7 @@
         <v>128417709</v>
       </c>
       <c r="B45" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5391,7 +5391,7 @@
         <v>128416206</v>
       </c>
       <c r="B46" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5498,7 +5498,7 @@
         <v>128413145</v>
       </c>
       <c r="B47" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5605,7 +5605,7 @@
         <v>128412596</v>
       </c>
       <c r="B48" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5712,7 +5712,7 @@
         <v>128416262</v>
       </c>
       <c r="B49" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5819,7 +5819,7 @@
         <v>128417096</v>
       </c>
       <c r="B50" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5923,45 +5923,50 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128415549</v>
+        <v>128415767</v>
       </c>
       <c r="B51" t="n">
-        <v>79120</v>
+        <v>8450</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>426615</v>
+        <v>426618</v>
       </c>
       <c r="R51" t="n">
-        <v>6784068</v>
+        <v>6784050</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5993,7 +5998,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6003,7 +6008,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6030,7 +6035,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128415767</v>
+        <v>128414874</v>
       </c>
       <c r="B52" t="n">
         <v>8450</v>
@@ -6061,7 +6066,7 @@
       <c r="I52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -6070,10 +6075,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>426618</v>
+        <v>426535</v>
       </c>
       <c r="R52" t="n">
-        <v>6784050</v>
+        <v>6784210</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6105,7 +6110,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6115,7 +6120,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6142,50 +6147,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128414874</v>
+        <v>128415549</v>
       </c>
       <c r="B53" t="n">
-        <v>8450</v>
+        <v>79124</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>426535</v>
+        <v>426615</v>
       </c>
       <c r="R53" t="n">
-        <v>6784210</v>
+        <v>6784068</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6217,7 +6217,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6227,7 +6227,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6257,7 +6257,7 @@
         <v>128415267</v>
       </c>
       <c r="B54" t="n">
-        <v>78878</v>
+        <v>78882</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6364,7 +6364,7 @@
         <v>128418647</v>
       </c>
       <c r="B55" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6471,7 +6471,7 @@
         <v>128413992</v>
       </c>
       <c r="B56" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6578,7 +6578,7 @@
         <v>128417675</v>
       </c>
       <c r="B57" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6685,7 +6685,7 @@
         <v>128415393</v>
       </c>
       <c r="B58" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6792,7 +6792,7 @@
         <v>128418258</v>
       </c>
       <c r="B59" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6896,50 +6896,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128404480</v>
+        <v>128416385</v>
       </c>
       <c r="B60" t="n">
-        <v>8450</v>
+        <v>79743</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>426773</v>
+        <v>426796</v>
       </c>
       <c r="R60" t="n">
-        <v>6784434</v>
+        <v>6784156</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6971,7 +6966,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6981,7 +6976,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7008,45 +7003,50 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128416385</v>
+        <v>128404480</v>
       </c>
       <c r="B61" t="n">
-        <v>79739</v>
+        <v>8450</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>426796</v>
+        <v>426773</v>
       </c>
       <c r="R61" t="n">
-        <v>6784156</v>
+        <v>6784434</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7078,7 +7078,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7088,7 +7088,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7118,7 +7118,7 @@
         <v>128414843</v>
       </c>
       <c r="B62" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7225,7 +7225,7 @@
         <v>128412109</v>
       </c>
       <c r="B63" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7332,7 +7332,7 @@
         <v>128414095</v>
       </c>
       <c r="B64" t="n">
-        <v>78878</v>
+        <v>78882</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7436,7 +7436,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128416277</v>
+        <v>128415117</v>
       </c>
       <c r="B65" t="n">
         <v>8450</v>
@@ -7472,14 +7472,14 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>426797</v>
+        <v>426554</v>
       </c>
       <c r="R65" t="n">
-        <v>6784155</v>
+        <v>6784161</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7511,7 +7511,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7521,7 +7521,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7548,7 +7548,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128415117</v>
+        <v>128416277</v>
       </c>
       <c r="B66" t="n">
         <v>8450</v>
@@ -7584,14 +7584,14 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>426554</v>
+        <v>426797</v>
       </c>
       <c r="R66" t="n">
-        <v>6784161</v>
+        <v>6784155</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7623,7 +7623,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7633,7 +7633,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7660,50 +7660,50 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128417436</v>
+        <v>128413310</v>
       </c>
       <c r="B67" t="n">
-        <v>8450</v>
+        <v>57717</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>426801</v>
+        <v>426477</v>
       </c>
       <c r="R67" t="n">
-        <v>6784284</v>
+        <v>6784397</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7735,7 +7735,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7745,7 +7745,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7775,7 +7775,7 @@
         <v>128413333</v>
       </c>
       <c r="B68" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7879,50 +7879,50 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128413310</v>
+        <v>128417436</v>
       </c>
       <c r="B69" t="n">
-        <v>57713</v>
+        <v>8450</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>426477</v>
+        <v>426801</v>
       </c>
       <c r="R69" t="n">
-        <v>6784397</v>
+        <v>6784284</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7954,7 +7954,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7964,7 +7964,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7991,10 +7991,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128417205</v>
+        <v>128418292</v>
       </c>
       <c r="B70" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8022,14 +8022,14 @@
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>426813</v>
+        <v>426624</v>
       </c>
       <c r="R70" t="n">
-        <v>6784276</v>
+        <v>6784361</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8061,7 +8061,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8071,7 +8071,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav på tallarna på en radie av 50 meter.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8098,10 +8103,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128418292</v>
+        <v>128417205</v>
       </c>
       <c r="B71" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8129,14 +8134,14 @@
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>426624</v>
+        <v>426813</v>
       </c>
       <c r="R71" t="n">
-        <v>6784361</v>
+        <v>6784276</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8168,7 +8173,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8178,12 +8183,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>18:45</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav på tallarna på en radie av 50 meter.</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8213,7 +8213,7 @@
         <v>128415978</v>
       </c>
       <c r="B72" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8317,45 +8317,50 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128413213</v>
+        <v>128414247</v>
       </c>
       <c r="B73" t="n">
-        <v>78878</v>
+        <v>8450</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>426524</v>
+        <v>426535</v>
       </c>
       <c r="R73" t="n">
-        <v>6784388</v>
+        <v>6784292</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8387,7 +8392,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8397,7 +8402,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8424,50 +8429,45 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128414247</v>
+        <v>128413213</v>
       </c>
       <c r="B74" t="n">
-        <v>8450</v>
+        <v>78882</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>426535</v>
+        <v>426524</v>
       </c>
       <c r="R74" t="n">
-        <v>6784292</v>
+        <v>6784388</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8499,7 +8499,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8509,7 +8509,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8636,7 +8636,7 @@
         <v>128410669</v>
       </c>
       <c r="B76" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8852,38 +8852,38 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128406731</v>
+        <v>128410625</v>
       </c>
       <c r="B78" t="n">
-        <v>8450</v>
+        <v>57717</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="M78" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -8892,13 +8892,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>427073</v>
+        <v>426917</v>
       </c>
       <c r="R78" t="n">
-        <v>6784548</v>
+        <v>6784579</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8927,7 +8927,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8937,7 +8937,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8964,50 +8964,45 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128416919</v>
+        <v>128408858</v>
       </c>
       <c r="B79" t="n">
-        <v>8450</v>
+        <v>79124</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>426842</v>
+        <v>427123</v>
       </c>
       <c r="R79" t="n">
-        <v>6784214</v>
+        <v>6784697</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9039,7 +9034,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9049,7 +9044,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9076,7 +9071,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128408778</v>
+        <v>128406731</v>
       </c>
       <c r="B80" t="n">
         <v>8450</v>
@@ -9107,7 +9102,7 @@
       <c r="I80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -9116,10 +9111,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>427123</v>
+        <v>427073</v>
       </c>
       <c r="R80" t="n">
-        <v>6784697</v>
+        <v>6784548</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9151,7 +9146,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9161,7 +9156,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9188,45 +9183,50 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128408858</v>
+        <v>128416919</v>
       </c>
       <c r="B81" t="n">
-        <v>79120</v>
+        <v>8450</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>427123</v>
+        <v>426842</v>
       </c>
       <c r="R81" t="n">
-        <v>6784697</v>
+        <v>6784214</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9258,7 +9258,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9268,7 +9268,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9295,38 +9295,38 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128410625</v>
+        <v>128408778</v>
       </c>
       <c r="B82" t="n">
-        <v>57713</v>
+        <v>8450</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="M82" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -9335,13 +9335,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>426917</v>
+        <v>427123</v>
       </c>
       <c r="R82" t="n">
-        <v>6784579</v>
+        <v>6784697</v>
       </c>
       <c r="S82" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9370,7 +9370,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9380,7 +9380,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9407,10 +9407,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128409945</v>
+        <v>128404878</v>
       </c>
       <c r="B83" t="n">
-        <v>78878</v>
+        <v>57717</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9418,34 +9418,39 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>427084</v>
+        <v>426879</v>
       </c>
       <c r="R83" t="n">
-        <v>6784718</v>
+        <v>6784490</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9477,7 +9482,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9487,7 +9492,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9514,10 +9519,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128404878</v>
+        <v>128409945</v>
       </c>
       <c r="B84" t="n">
-        <v>57713</v>
+        <v>78882</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9525,39 +9530,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>426879</v>
+        <v>427084</v>
       </c>
       <c r="R84" t="n">
-        <v>6784490</v>
+        <v>6784718</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9589,7 +9589,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9599,7 +9599,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9629,7 +9629,7 @@
         <v>128407168</v>
       </c>
       <c r="B85" t="n">
-        <v>78878</v>
+        <v>78882</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9736,7 +9736,7 @@
         <v>128416596</v>
       </c>
       <c r="B86" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9843,7 +9843,7 @@
         <v>128406999</v>
       </c>
       <c r="B87" t="n">
-        <v>78878</v>
+        <v>78882</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9950,7 +9950,7 @@
         <v>128416502</v>
       </c>
       <c r="B88" t="n">
-        <v>78878</v>
+        <v>78882</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10057,7 +10057,7 @@
         <v>128416791</v>
       </c>
       <c r="B89" t="n">
-        <v>78878</v>
+        <v>78882</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10164,7 +10164,7 @@
         <v>128417147</v>
       </c>
       <c r="B90" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10271,7 +10271,7 @@
         <v>128417068</v>
       </c>
       <c r="B91" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10378,7 +10378,7 @@
         <v>128423249</v>
       </c>
       <c r="B92" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10487,50 +10487,45 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128410598</v>
+        <v>128406985</v>
       </c>
       <c r="B93" t="n">
-        <v>8450</v>
+        <v>78881</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>426922</v>
+        <v>427087</v>
       </c>
       <c r="R93" t="n">
-        <v>6784576</v>
+        <v>6784548</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10562,7 +10557,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10572,7 +10567,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10599,50 +10594,45 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128404859</v>
+        <v>128410456</v>
       </c>
       <c r="B94" t="n">
-        <v>8450</v>
+        <v>79124</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>426869</v>
+        <v>426882</v>
       </c>
       <c r="R94" t="n">
-        <v>6784461</v>
+        <v>6784648</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10674,7 +10664,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10684,7 +10674,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10714,7 +10704,7 @@
         <v>128410027</v>
       </c>
       <c r="B95" t="n">
-        <v>91524</v>
+        <v>91528</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10826,45 +10816,50 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128406985</v>
+        <v>128410598</v>
       </c>
       <c r="B96" t="n">
-        <v>78877</v>
+        <v>8450</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>427087</v>
+        <v>426922</v>
       </c>
       <c r="R96" t="n">
-        <v>6784548</v>
+        <v>6784576</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10896,7 +10891,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10906,7 +10901,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10933,45 +10928,50 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128410456</v>
+        <v>128404859</v>
       </c>
       <c r="B97" t="n">
-        <v>79120</v>
+        <v>8450</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>426882</v>
+        <v>426869</v>
       </c>
       <c r="R97" t="n">
-        <v>6784648</v>
+        <v>6784461</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11003,7 +11003,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11013,7 +11013,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11043,7 +11043,7 @@
         <v>128410868</v>
       </c>
       <c r="B98" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11259,50 +11259,45 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128410908</v>
+        <v>128411027</v>
       </c>
       <c r="B100" t="n">
-        <v>8450</v>
+        <v>79124</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>426908</v>
+        <v>426858</v>
       </c>
       <c r="R100" t="n">
-        <v>6784511</v>
+        <v>6784514</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11334,7 +11329,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11344,7 +11339,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11371,45 +11366,50 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128411027</v>
+        <v>128410908</v>
       </c>
       <c r="B101" t="n">
-        <v>79120</v>
+        <v>8450</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>426858</v>
+        <v>426908</v>
       </c>
       <c r="R101" t="n">
-        <v>6784514</v>
+        <v>6784511</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11441,7 +11441,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11451,7 +11451,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11478,10 +11478,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128408932</v>
+        <v>128416713</v>
       </c>
       <c r="B102" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11513,10 +11513,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>427081</v>
+        <v>426849</v>
       </c>
       <c r="R102" t="n">
-        <v>6784657</v>
+        <v>6784145</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11548,7 +11548,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11558,7 +11558,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11585,10 +11585,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128416713</v>
+        <v>128408932</v>
       </c>
       <c r="B103" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11620,10 +11620,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>426849</v>
+        <v>427081</v>
       </c>
       <c r="R103" t="n">
-        <v>6784145</v>
+        <v>6784657</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11655,7 +11655,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11665,7 +11665,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11695,7 +11695,7 @@
         <v>128407898</v>
       </c>
       <c r="B104" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11802,7 +11802,7 @@
         <v>128409925</v>
       </c>
       <c r="B105" t="n">
-        <v>79710</v>
+        <v>79714</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11909,7 +11909,7 @@
         <v>128407848</v>
       </c>
       <c r="B106" t="n">
-        <v>78878</v>
+        <v>78882</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12016,7 +12016,7 @@
         <v>128416606</v>
       </c>
       <c r="B107" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>

--- a/artfynd/A 36371-2025 artfynd.xlsx
+++ b/artfynd/A 36371-2025 artfynd.xlsx
@@ -4420,50 +4420,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128404418</v>
+        <v>128412524</v>
       </c>
       <c r="B37" t="n">
-        <v>8450</v>
+        <v>79124</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>426715</v>
+        <v>426466</v>
       </c>
       <c r="R37" t="n">
-        <v>6784397</v>
+        <v>6784510</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4495,7 +4490,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4505,7 +4500,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4532,10 +4527,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128412524</v>
+        <v>128414383</v>
       </c>
       <c r="B38" t="n">
-        <v>79124</v>
+        <v>78882</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4543,21 +4538,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4567,10 +4562,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>426466</v>
+        <v>426509</v>
       </c>
       <c r="R38" t="n">
-        <v>6784510</v>
+        <v>6784270</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4602,7 +4597,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4612,7 +4607,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4639,45 +4634,50 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128414383</v>
+        <v>128404418</v>
       </c>
       <c r="B39" t="n">
-        <v>78882</v>
+        <v>8450</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>426509</v>
+        <v>426715</v>
       </c>
       <c r="R39" t="n">
-        <v>6784270</v>
+        <v>6784397</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4709,7 +4709,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4719,7 +4719,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -6254,10 +6254,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128415267</v>
+        <v>128418647</v>
       </c>
       <c r="B54" t="n">
-        <v>78882</v>
+        <v>79124</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6265,21 +6265,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6289,10 +6289,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>426604</v>
+        <v>426573</v>
       </c>
       <c r="R54" t="n">
-        <v>6784093</v>
+        <v>6784376</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6324,7 +6324,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>18:59</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>18:59</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6361,7 +6361,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128418647</v>
+        <v>128413992</v>
       </c>
       <c r="B55" t="n">
         <v>79124</v>
@@ -6396,10 +6396,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>426573</v>
+        <v>426519</v>
       </c>
       <c r="R55" t="n">
-        <v>6784376</v>
+        <v>6784308</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>18:59</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6441,7 +6441,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>18:59</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6468,10 +6468,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128413992</v>
+        <v>128415267</v>
       </c>
       <c r="B56" t="n">
-        <v>79124</v>
+        <v>78882</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6479,21 +6479,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6503,10 +6503,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>426519</v>
+        <v>426604</v>
       </c>
       <c r="R56" t="n">
-        <v>6784308</v>
+        <v>6784093</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6538,7 +6538,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6548,7 +6548,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7222,10 +7222,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128412109</v>
+        <v>128414095</v>
       </c>
       <c r="B63" t="n">
-        <v>79124</v>
+        <v>78882</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7233,21 +7233,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7257,10 +7257,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>426646</v>
+        <v>426556</v>
       </c>
       <c r="R63" t="n">
-        <v>6784678</v>
+        <v>6784312</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7292,7 +7292,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7302,7 +7302,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7329,10 +7329,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128414095</v>
+        <v>128412109</v>
       </c>
       <c r="B64" t="n">
-        <v>78882</v>
+        <v>79124</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7340,21 +7340,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7364,10 +7364,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>426556</v>
+        <v>426646</v>
       </c>
       <c r="R64" t="n">
-        <v>6784312</v>
+        <v>6784678</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7399,7 +7399,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7409,7 +7409,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7991,7 +7991,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128418292</v>
+        <v>128417205</v>
       </c>
       <c r="B70" t="n">
         <v>79124</v>
@@ -8022,14 +8022,14 @@
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>426624</v>
+        <v>426813</v>
       </c>
       <c r="R70" t="n">
-        <v>6784361</v>
+        <v>6784276</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8061,7 +8061,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8071,12 +8071,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>18:45</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav på tallarna på en radie av 50 meter.</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8103,7 +8098,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128417205</v>
+        <v>128418292</v>
       </c>
       <c r="B71" t="n">
         <v>79124</v>
@@ -8134,14 +8129,14 @@
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>426813</v>
+        <v>426624</v>
       </c>
       <c r="R71" t="n">
-        <v>6784276</v>
+        <v>6784361</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8173,7 +8168,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8183,7 +8178,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav på tallarna på en radie av 50 meter.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -11040,45 +11040,50 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128410868</v>
+        <v>128405638</v>
       </c>
       <c r="B98" t="n">
-        <v>79124</v>
+        <v>8450</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>426916</v>
+        <v>427026</v>
       </c>
       <c r="R98" t="n">
-        <v>6784534</v>
+        <v>6784560</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11110,7 +11115,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11120,7 +11125,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11147,50 +11152,45 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128405638</v>
+        <v>128410868</v>
       </c>
       <c r="B99" t="n">
-        <v>8450</v>
+        <v>79124</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>427026</v>
+        <v>426916</v>
       </c>
       <c r="R99" t="n">
-        <v>6784560</v>
+        <v>6784534</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11222,7 +11222,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11232,7 +11232,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11692,10 +11692,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128407898</v>
+        <v>128409925</v>
       </c>
       <c r="B104" t="n">
-        <v>78881</v>
+        <v>79714</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11703,21 +11703,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11727,10 +11727,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>427062</v>
+        <v>427082</v>
       </c>
       <c r="R104" t="n">
-        <v>6784591</v>
+        <v>6784715</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11762,7 +11762,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11772,7 +11772,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11799,10 +11799,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128409925</v>
+        <v>128407898</v>
       </c>
       <c r="B105" t="n">
-        <v>79714</v>
+        <v>78881</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11810,21 +11810,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11834,10 +11834,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>427082</v>
+        <v>427062</v>
       </c>
       <c r="R105" t="n">
-        <v>6784715</v>
+        <v>6784591</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11869,7 +11869,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11879,7 +11879,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD105" t="b">

--- a/artfynd/A 36371-2025 artfynd.xlsx
+++ b/artfynd/A 36371-2025 artfynd.xlsx
@@ -2696,7 +2696,7 @@
         <v>128415595</v>
       </c>
       <c r="B21" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128415015</v>
+        <v>128411184</v>
       </c>
       <c r="B22" t="n">
-        <v>79124</v>
+        <v>78787</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2811,34 +2811,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>426548</v>
+        <v>426819</v>
       </c>
       <c r="R22" t="n">
-        <v>6784175</v>
+        <v>6784515</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2870,7 +2870,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2880,7 +2880,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2907,10 +2907,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128414172</v>
+        <v>128415015</v>
       </c>
       <c r="B23" t="n">
-        <v>78881</v>
+        <v>79029</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2918,21 +2918,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2942,10 +2942,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>426541</v>
+        <v>426548</v>
       </c>
       <c r="R23" t="n">
-        <v>6784302</v>
+        <v>6784175</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2977,7 +2977,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2987,7 +2987,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3014,10 +3014,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128418402</v>
+        <v>128414172</v>
       </c>
       <c r="B24" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3049,10 +3049,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>426596</v>
+        <v>426541</v>
       </c>
       <c r="R24" t="n">
-        <v>6784364</v>
+        <v>6784302</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3121,10 +3121,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128414481</v>
+        <v>128418402</v>
       </c>
       <c r="B25" t="n">
-        <v>79743</v>
+        <v>78786</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3132,21 +3132,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3156,10 +3156,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>426524</v>
+        <v>426596</v>
       </c>
       <c r="R25" t="n">
-        <v>6784260</v>
+        <v>6784364</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3191,7 +3191,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3201,7 +3201,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3228,10 +3228,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128411184</v>
+        <v>128414481</v>
       </c>
       <c r="B26" t="n">
-        <v>78882</v>
+        <v>79648</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3239,34 +3239,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>426819</v>
+        <v>426524</v>
       </c>
       <c r="R26" t="n">
-        <v>6784515</v>
+        <v>6784260</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3298,7 +3298,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3308,7 +3308,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3335,10 +3335,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128414155</v>
+        <v>128414801</v>
       </c>
       <c r="B27" t="n">
-        <v>78882</v>
+        <v>79029</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3346,21 +3346,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3370,10 +3370,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>426540</v>
+        <v>426524</v>
       </c>
       <c r="R27" t="n">
-        <v>6784305</v>
+        <v>6784260</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3405,7 +3405,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3415,7 +3415,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3442,10 +3442,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128414801</v>
+        <v>128416106</v>
       </c>
       <c r="B28" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3473,14 +3473,14 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>426524</v>
+        <v>426746</v>
       </c>
       <c r="R28" t="n">
-        <v>6784260</v>
+        <v>6784096</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3512,7 +3512,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3522,7 +3522,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50 meter.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3549,10 +3554,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128416106</v>
+        <v>128417228</v>
       </c>
       <c r="B29" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3584,10 +3589,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>426746</v>
+        <v>426801</v>
       </c>
       <c r="R29" t="n">
-        <v>6784096</v>
+        <v>6784284</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3619,7 +3624,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3629,12 +3634,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:35</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50 meter.</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3661,10 +3661,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128417228</v>
+        <v>128414155</v>
       </c>
       <c r="B30" t="n">
-        <v>79124</v>
+        <v>78787</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3672,34 +3672,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>426801</v>
+        <v>426540</v>
       </c>
       <c r="R30" t="n">
-        <v>6784284</v>
+        <v>6784305</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3731,7 +3731,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3768,10 +3768,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128414306</v>
+        <v>128413169</v>
       </c>
       <c r="B31" t="n">
-        <v>57717</v>
+        <v>79029</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3779,39 +3779,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>426519</v>
+        <v>426555</v>
       </c>
       <c r="R31" t="n">
-        <v>6784286</v>
+        <v>6784393</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3843,7 +3838,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3853,7 +3848,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3880,10 +3875,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128413169</v>
+        <v>128414306</v>
       </c>
       <c r="B32" t="n">
-        <v>79124</v>
+        <v>57720</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3891,34 +3886,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>426555</v>
+        <v>426519</v>
       </c>
       <c r="R32" t="n">
-        <v>6784393</v>
+        <v>6784286</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3950,7 +3950,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3987,50 +3987,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128413945</v>
+        <v>128418215</v>
       </c>
       <c r="B33" t="n">
-        <v>8450</v>
+        <v>78787</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>426498</v>
+        <v>426655</v>
       </c>
       <c r="R33" t="n">
-        <v>6784322</v>
+        <v>6784360</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4062,7 +4057,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4072,7 +4067,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4099,45 +4094,50 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128418215</v>
+        <v>128413945</v>
       </c>
       <c r="B34" t="n">
-        <v>78882</v>
+        <v>8450</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>426655</v>
+        <v>426498</v>
       </c>
       <c r="R34" t="n">
-        <v>6784360</v>
+        <v>6784322</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4209,7 +4209,7 @@
         <v>128416349</v>
       </c>
       <c r="B35" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4316,7 +4316,7 @@
         <v>128404649</v>
       </c>
       <c r="B36" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4420,10 +4420,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128412524</v>
+        <v>128414383</v>
       </c>
       <c r="B37" t="n">
-        <v>79124</v>
+        <v>78787</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4431,21 +4431,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4455,10 +4455,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>426466</v>
+        <v>426509</v>
       </c>
       <c r="R37" t="n">
-        <v>6784510</v>
+        <v>6784270</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4490,7 +4490,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4527,10 +4527,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128414383</v>
+        <v>128412524</v>
       </c>
       <c r="B38" t="n">
-        <v>78882</v>
+        <v>79029</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4538,21 +4538,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4562,10 +4562,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>426509</v>
+        <v>426466</v>
       </c>
       <c r="R38" t="n">
-        <v>6784270</v>
+        <v>6784510</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4597,7 +4597,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4607,7 +4607,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4746,10 +4746,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128418704</v>
+        <v>128417709</v>
       </c>
       <c r="B40" t="n">
-        <v>78881</v>
+        <v>79029</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4757,34 +4757,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>426573</v>
+        <v>426717</v>
       </c>
       <c r="R40" t="n">
-        <v>6784360</v>
+        <v>6784350</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4853,10 +4853,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128418719</v>
+        <v>128418704</v>
       </c>
       <c r="B41" t="n">
-        <v>79124</v>
+        <v>78786</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4864,21 +4864,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4888,10 +4888,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>426571</v>
+        <v>426573</v>
       </c>
       <c r="R41" t="n">
-        <v>6784357</v>
+        <v>6784360</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4933,7 +4933,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4960,10 +4960,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128415503</v>
+        <v>128418719</v>
       </c>
       <c r="B42" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4995,10 +4995,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>426605</v>
+        <v>426571</v>
       </c>
       <c r="R42" t="n">
-        <v>6784090</v>
+        <v>6784357</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5030,7 +5030,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5040,7 +5040,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5070,7 +5070,7 @@
         <v>128418198</v>
       </c>
       <c r="B43" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5177,7 +5177,7 @@
         <v>128413197</v>
       </c>
       <c r="B44" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5281,10 +5281,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128417709</v>
+        <v>128415503</v>
       </c>
       <c r="B45" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5312,14 +5312,14 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>426717</v>
+        <v>426605</v>
       </c>
       <c r="R45" t="n">
-        <v>6784350</v>
+        <v>6784090</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5351,7 +5351,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5388,10 +5388,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128416206</v>
+        <v>128413145</v>
       </c>
       <c r="B46" t="n">
-        <v>78881</v>
+        <v>79029</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5399,34 +5399,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>426760</v>
+        <v>426534</v>
       </c>
       <c r="R46" t="n">
-        <v>6784153</v>
+        <v>6784406</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5458,7 +5458,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5468,7 +5468,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5495,10 +5495,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128413145</v>
+        <v>128416206</v>
       </c>
       <c r="B47" t="n">
-        <v>79124</v>
+        <v>78786</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5506,34 +5506,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>426534</v>
+        <v>426760</v>
       </c>
       <c r="R47" t="n">
-        <v>6784406</v>
+        <v>6784153</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5565,7 +5565,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5575,7 +5575,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5605,7 +5605,7 @@
         <v>128412596</v>
       </c>
       <c r="B48" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5709,45 +5709,50 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128416262</v>
+        <v>128415767</v>
       </c>
       <c r="B49" t="n">
-        <v>79124</v>
+        <v>8450</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>426784</v>
+        <v>426618</v>
       </c>
       <c r="R49" t="n">
-        <v>6784159</v>
+        <v>6784050</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5779,7 +5784,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5789,7 +5794,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5816,45 +5821,50 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128417096</v>
+        <v>128414874</v>
       </c>
       <c r="B50" t="n">
-        <v>79124</v>
+        <v>8450</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>426812</v>
+        <v>426535</v>
       </c>
       <c r="R50" t="n">
-        <v>6784257</v>
+        <v>6784210</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5886,7 +5896,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5896,7 +5906,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5923,50 +5933,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128415767</v>
+        <v>128416262</v>
       </c>
       <c r="B51" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>426618</v>
+        <v>426784</v>
       </c>
       <c r="R51" t="n">
-        <v>6784050</v>
+        <v>6784159</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5998,7 +6003,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6008,7 +6013,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6035,50 +6040,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128414874</v>
+        <v>128417096</v>
       </c>
       <c r="B52" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>426535</v>
+        <v>426812</v>
       </c>
       <c r="R52" t="n">
-        <v>6784210</v>
+        <v>6784257</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6110,7 +6110,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6120,7 +6120,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6150,7 +6150,7 @@
         <v>128415549</v>
       </c>
       <c r="B53" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6257,7 +6257,7 @@
         <v>128418647</v>
       </c>
       <c r="B54" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6364,7 +6364,7 @@
         <v>128413992</v>
       </c>
       <c r="B55" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6471,7 +6471,7 @@
         <v>128415267</v>
       </c>
       <c r="B56" t="n">
-        <v>78882</v>
+        <v>78787</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6578,7 +6578,7 @@
         <v>128417675</v>
       </c>
       <c r="B57" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6685,7 +6685,7 @@
         <v>128415393</v>
       </c>
       <c r="B58" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6792,7 +6792,7 @@
         <v>128418258</v>
       </c>
       <c r="B59" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6899,7 +6899,7 @@
         <v>128416385</v>
       </c>
       <c r="B60" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7118,7 +7118,7 @@
         <v>128414843</v>
       </c>
       <c r="B62" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7225,7 +7225,7 @@
         <v>128414095</v>
       </c>
       <c r="B63" t="n">
-        <v>78882</v>
+        <v>78787</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7332,7 +7332,7 @@
         <v>128412109</v>
       </c>
       <c r="B64" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7660,50 +7660,50 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128413310</v>
+        <v>128417436</v>
       </c>
       <c r="B67" t="n">
-        <v>57717</v>
+        <v>8450</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
+          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>426477</v>
+        <v>426801</v>
       </c>
       <c r="R67" t="n">
-        <v>6784397</v>
+        <v>6784284</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7735,7 +7735,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7745,7 +7745,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7772,10 +7772,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128413333</v>
+        <v>128413310</v>
       </c>
       <c r="B68" t="n">
-        <v>78881</v>
+        <v>57720</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7783,34 +7783,39 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>426459</v>
+        <v>426477</v>
       </c>
       <c r="R68" t="n">
-        <v>6784412</v>
+        <v>6784397</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7842,7 +7847,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7852,7 +7857,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7879,50 +7884,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128417436</v>
+        <v>128413333</v>
       </c>
       <c r="B69" t="n">
-        <v>8450</v>
+        <v>78786</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
+          <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>426801</v>
+        <v>426459</v>
       </c>
       <c r="R69" t="n">
-        <v>6784284</v>
+        <v>6784412</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7954,7 +7954,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7964,7 +7964,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7994,7 +7994,7 @@
         <v>128417205</v>
       </c>
       <c r="B70" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8101,7 +8101,7 @@
         <v>128418292</v>
       </c>
       <c r="B71" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         <v>128415978</v>
       </c>
       <c r="B72" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8317,50 +8317,45 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128414247</v>
+        <v>128413213</v>
       </c>
       <c r="B73" t="n">
-        <v>8450</v>
+        <v>78787</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>426535</v>
+        <v>426524</v>
       </c>
       <c r="R73" t="n">
-        <v>6784292</v>
+        <v>6784388</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8392,7 +8387,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8402,7 +8397,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8429,45 +8424,50 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128413213</v>
+        <v>128414247</v>
       </c>
       <c r="B74" t="n">
-        <v>78882</v>
+        <v>8450</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Silvertjärnarna, Silvertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>426524</v>
+        <v>426535</v>
       </c>
       <c r="R74" t="n">
-        <v>6784388</v>
+        <v>6784292</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8499,7 +8499,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8509,7 +8509,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8636,7 +8636,7 @@
         <v>128410669</v>
       </c>
       <c r="B76" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8852,10 +8852,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128410625</v>
+        <v>128408858</v>
       </c>
       <c r="B78" t="n">
-        <v>57717</v>
+        <v>79029</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8863,42 +8863,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>426917</v>
+        <v>427123</v>
       </c>
       <c r="R78" t="n">
-        <v>6784579</v>
+        <v>6784697</v>
       </c>
       <c r="S78" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8927,7 +8922,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8937,7 +8932,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8964,10 +8959,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128408858</v>
+        <v>128410625</v>
       </c>
       <c r="B79" t="n">
-        <v>79124</v>
+        <v>57720</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8975,37 +8970,42 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>427123</v>
+        <v>426917</v>
       </c>
       <c r="R79" t="n">
-        <v>6784697</v>
+        <v>6784579</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9034,7 +9034,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9044,7 +9044,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9410,7 +9410,7 @@
         <v>128404878</v>
       </c>
       <c r="B83" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9522,7 +9522,7 @@
         <v>128409945</v>
       </c>
       <c r="B84" t="n">
-        <v>78882</v>
+        <v>78787</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9629,7 +9629,7 @@
         <v>128407168</v>
       </c>
       <c r="B85" t="n">
-        <v>78882</v>
+        <v>78787</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9736,7 +9736,7 @@
         <v>128416596</v>
       </c>
       <c r="B86" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9843,7 +9843,7 @@
         <v>128406999</v>
       </c>
       <c r="B87" t="n">
-        <v>78882</v>
+        <v>78787</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9950,7 +9950,7 @@
         <v>128416502</v>
       </c>
       <c r="B88" t="n">
-        <v>78882</v>
+        <v>78787</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10057,7 +10057,7 @@
         <v>128416791</v>
       </c>
       <c r="B89" t="n">
-        <v>78882</v>
+        <v>78787</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10164,7 +10164,7 @@
         <v>128417147</v>
       </c>
       <c r="B90" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10271,7 +10271,7 @@
         <v>128417068</v>
       </c>
       <c r="B91" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10378,7 +10378,7 @@
         <v>128423249</v>
       </c>
       <c r="B92" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10487,10 +10487,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128406985</v>
+        <v>128410027</v>
       </c>
       <c r="B93" t="n">
-        <v>78881</v>
+        <v>91533</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10498,34 +10498,41 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6446</v>
+        <v>5442</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>427087</v>
+        <v>427093</v>
       </c>
       <c r="R93" t="n">
-        <v>6784548</v>
+        <v>6784727</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10557,7 +10564,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10567,7 +10574,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10576,6 +10583,7 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -10594,10 +10602,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128410456</v>
+        <v>128406985</v>
       </c>
       <c r="B94" t="n">
-        <v>79124</v>
+        <v>78786</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10605,21 +10613,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10629,10 +10637,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>426882</v>
+        <v>427087</v>
       </c>
       <c r="R94" t="n">
-        <v>6784648</v>
+        <v>6784548</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10664,7 +10672,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10674,7 +10682,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10701,10 +10709,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128410027</v>
+        <v>128410456</v>
       </c>
       <c r="B95" t="n">
-        <v>91528</v>
+        <v>79029</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10712,41 +10720,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>427093</v>
+        <v>426882</v>
       </c>
       <c r="R95" t="n">
-        <v>6784727</v>
+        <v>6784648</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10778,7 +10779,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10788,7 +10789,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10797,7 +10798,6 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -11155,7 +11155,7 @@
         <v>128410868</v>
       </c>
       <c r="B99" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11259,45 +11259,50 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128411027</v>
+        <v>128410908</v>
       </c>
       <c r="B100" t="n">
-        <v>79124</v>
+        <v>8450</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>426858</v>
+        <v>426908</v>
       </c>
       <c r="R100" t="n">
-        <v>6784514</v>
+        <v>6784511</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11329,7 +11334,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11339,7 +11344,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11366,50 +11371,45 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128410908</v>
+        <v>128411027</v>
       </c>
       <c r="B101" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Fisklöstjärnen, Fisklöstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>426908</v>
+        <v>426858</v>
       </c>
       <c r="R101" t="n">
-        <v>6784511</v>
+        <v>6784514</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11441,7 +11441,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11451,7 +11451,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11481,7 +11481,7 @@
         <v>128416713</v>
       </c>
       <c r="B102" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11588,7 +11588,7 @@
         <v>128408932</v>
       </c>
       <c r="B103" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11692,10 +11692,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128409925</v>
+        <v>128407898</v>
       </c>
       <c r="B104" t="n">
-        <v>79714</v>
+        <v>78786</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11703,21 +11703,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11727,10 +11727,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>427082</v>
+        <v>427062</v>
       </c>
       <c r="R104" t="n">
-        <v>6784715</v>
+        <v>6784591</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11762,7 +11762,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11772,7 +11772,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11799,10 +11799,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128407898</v>
+        <v>128409925</v>
       </c>
       <c r="B105" t="n">
-        <v>78881</v>
+        <v>79619</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11810,21 +11810,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11834,10 +11834,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>427062</v>
+        <v>427082</v>
       </c>
       <c r="R105" t="n">
-        <v>6784591</v>
+        <v>6784715</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11869,7 +11869,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11879,7 +11879,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11909,7 +11909,7 @@
         <v>128407848</v>
       </c>
       <c r="B106" t="n">
-        <v>78882</v>
+        <v>78787</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12016,7 +12016,7 @@
         <v>128416606</v>
       </c>
       <c r="B107" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>

--- a/artfynd/A 36371-2025 artfynd.xlsx
+++ b/artfynd/A 36371-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY134"/>
+  <dimension ref="A1:AZ134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -787,6 +792,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128410027</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62161436</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1001,6 +1016,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62161437</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1108,6 +1128,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62161439</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1205,6 +1230,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127170594</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1302,6 +1332,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127170727</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1399,6 +1434,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127171567</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1496,6 +1536,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127172960</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1603,6 +1648,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128404649</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1710,6 +1760,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128408858</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1817,6 +1872,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128408932</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1924,6 +1984,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128410456</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2031,6 +2096,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128410669</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2138,6 +2208,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128410868</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2245,6 +2320,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128411027</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2352,6 +2432,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128412109</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2459,6 +2544,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128412524</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2566,6 +2656,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128412596</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2673,6 +2768,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128413145</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2780,6 +2880,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128413169</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2887,6 +2992,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128413197</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2994,6 +3104,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128413992</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3101,6 +3216,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128414801</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3208,6 +3328,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128414843</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3315,6 +3440,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128415015</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3422,6 +3552,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128415503</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3529,6 +3664,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128415549</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3636,6 +3776,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128415595</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3748,6 +3893,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128416106</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3855,6 +4005,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128416262</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3962,6 +4117,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128416713</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4069,6 +4229,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128417068</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4176,6 +4341,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128417096</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4283,6 +4453,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128417147</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4390,6 +4565,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128417205</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4497,6 +4677,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128417228</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4604,6 +4789,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128417514</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4711,6 +4901,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128417709</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4818,6 +5013,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128418198</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4925,6 +5125,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128418258</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5037,6 +5242,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128418292</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5144,6 +5354,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128418557</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5251,6 +5466,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128418647</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5358,6 +5578,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128418719</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5455,6 +5680,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127170509</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5552,6 +5782,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127170881</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5649,6 +5884,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127170931</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5746,6 +5986,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127171900</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5853,6 +6098,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128406985</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5960,6 +6210,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128407898</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6067,6 +6322,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128408420</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6174,6 +6434,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128408506</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6281,6 +6546,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128413333</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6388,6 +6658,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128414172</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6495,6 +6770,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128415978</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6602,6 +6882,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128416206</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6709,6 +6994,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128416349</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6816,6 +7106,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128416606</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6923,6 +7218,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128418161</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7030,6 +7330,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128418402</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7137,6 +7442,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128418540</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7244,6 +7554,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128418704</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7341,6 +7656,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/59599000</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7438,6 +7758,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/59599021</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7535,6 +7860,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127171905</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7642,6 +7972,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128414481</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7749,6 +8084,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128415393</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7856,6 +8196,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128416385</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7963,6 +8308,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128416596</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8070,6 +8420,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127172169</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8182,6 +8537,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128404878</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8294,6 +8654,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128410625</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8406,6 +8771,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128413310</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8518,6 +8888,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128414306</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8630,6 +9005,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423249</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8745,6 +9125,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128408405</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8852,6 +9237,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/59599002</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8959,6 +9349,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/59599003</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9066,6 +9461,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/59599004</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9173,6 +9573,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/59599005</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9280,6 +9685,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/59599006</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9382,6 +9792,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127172799</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9489,6 +9904,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62161438</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9586,6 +10006,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127170479</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9683,6 +10108,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127170902</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9780,6 +10210,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127173049</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9892,6 +10327,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128404418</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10004,6 +10444,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128404480</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10116,6 +10561,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128404859</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10228,6 +10678,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128405638</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10340,6 +10795,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128406731</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10447,6 +10907,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128407436</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10559,6 +11024,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128407498</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10671,6 +11141,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128408447</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10783,6 +11258,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128408778</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10895,6 +11375,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128409845</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11007,6 +11492,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128410158</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11119,6 +11609,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128410598</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11231,6 +11726,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128410908</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11343,6 +11843,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128413945</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11455,6 +11960,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128414247</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11567,6 +12077,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128414874</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11679,6 +12194,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128415117</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11791,6 +12311,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128415767</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11903,6 +12428,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128416277</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -12015,6 +12545,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128416919</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -12127,6 +12662,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128417436</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12224,6 +12764,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127170657</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12321,6 +12866,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/59598999</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12418,6 +12968,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127170935</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12525,6 +13080,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128406999</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12632,6 +13192,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128407168</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12739,6 +13304,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128407304</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12846,6 +13416,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128407480</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12953,6 +13528,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128407848</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -13060,6 +13640,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128408427</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -13167,6 +13752,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128408594</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -13274,6 +13864,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128409945</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -13381,6 +13976,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128411184</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -13488,6 +14088,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128411569</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -13595,6 +14200,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128413213</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -13702,6 +14312,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128414095</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -13809,6 +14424,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128414155</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -13916,6 +14536,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128414383</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -14023,6 +14648,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128415267</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -14130,6 +14760,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128416502</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -14237,6 +14872,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128416791</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -14344,6 +14984,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128418171</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -14451,6 +15096,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128418215</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -14558,6 +15208,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128418500</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -14655,6 +15310,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/59599001</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -14762,6 +15422,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128409925</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -14869,8 +15534,148 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128411636</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>